--- a/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
+++ b/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project\CampusStay FPT\docs\reports\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FBE6BCE-C7A7-4FC5-BC1A-8D48B0868458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E87C9192-A7AD-46BF-839F-DB818F6BB023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8964" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B957B587-DF1A-41F1-9064-AE18D87BD36B}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{10122E49-63A3-4F49-8814-BF3C2926AB4F}">
       <text>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FE375BB3-478E-4D27-AE84-00F72A5361FD}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C8A6E684-1F35-4027-B73D-7F45EBB4719C}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{D93FB66F-23E5-4304-96A5-990728D1BEC6}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{4662D146-00C4-4720-91F8-637C84AFD700}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A2A32975-4A9D-424E-8C43-4CF950EE2308}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8AC34E88-C1DD-4A76-874B-9D0A14B47BA1}">
       <text>
         <r>
           <rPr>
@@ -250,7 +250,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{1BFC57C8-EF19-47F4-A80F-04782C86BEEB}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CDCE2A14-1E7C-4E79-B89B-FED08BBEFD43}">
       <text>
         <r>
           <rPr>
@@ -273,7 +273,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{407D94B9-7BCA-4E4C-ADF1-F92E71733693}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{98CF15B8-5BAF-4CE3-9178-85F14603172C}">
       <text>
         <r>
           <rPr>
@@ -296,7 +296,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{54A9ED57-02A5-4A44-B0D7-9825A0D67857}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{46C506D5-49B3-41A3-A42D-C54830B99580}">
       <text>
         <r>
           <rPr>
@@ -319,7 +319,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7A3E4992-0B86-432D-9A97-7C72D86CB0D5}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FF637EDE-4DF0-4368-B439-D66CF11D1481}">
       <text>
         <r>
           <rPr>
@@ -342,7 +342,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7DB39E2A-27C8-43B9-A790-898F6A47E708}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A8AF4003-754F-41B7-B540-CE2D4BD181DB}">
       <text>
         <r>
           <rPr>
@@ -365,7 +365,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{BB65B3EE-1516-464F-8305-35FCFAD50237}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E86D8DC2-2FC9-40F7-BD6F-5E104F0BC277}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CB6601DB-B716-4B7A-BF40-EB7804BF9709}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{71BDC6F0-8FA1-495A-A63F-5D87D141E4F2}">
       <text>
         <r>
           <rPr>
@@ -411,7 +411,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E3C1C303-2962-461A-8832-C4DDC05F5BB0}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{D652D157-0F63-4F3A-A1E9-0F87BAA70C4F}">
       <text>
         <r>
           <rPr>
@@ -434,7 +434,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{62D639BF-61C2-420D-B6BC-280232591E6E}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{76C814EC-8ADD-481E-AB2A-69BBF38B7F85}">
       <text>
         <r>
           <rPr>
@@ -457,7 +457,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{20675CEC-3030-45FC-A768-59C8E00AF74C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CE1FD42D-C284-4E08-8BFA-3553E328BC5A}">
       <text>
         <r>
           <rPr>
@@ -480,7 +480,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8AE0C5E1-82D1-46C8-BD43-06D1C9B3DB9F}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E1BD3708-1CBA-409B-81A0-D79CE32EEC47}">
       <text>
         <r>
           <rPr>
@@ -503,7 +503,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A6A89E0C-176B-42B2-B9F2-632333B0994C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{578F86B2-88A3-41DC-9218-160E5E3376DA}">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CAA85B66-2B6E-4AE1-9A5C-8A223F1FC428}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{805857F1-7C00-427B-97B7-C6C7D51E1FC5}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CF27A0B3-0A67-4BE4-9FDF-9677DF6B1024}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{EF306E5C-75BC-4D05-9C35-0F7BD13698BA}">
       <text>
         <r>
           <rPr>
@@ -572,7 +572,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{61554BA1-5947-458E-9450-07DF93436E48}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{818D2B2B-BAD4-438F-98A4-88CE98AD70DA}">
       <text>
         <r>
           <rPr>
@@ -595,7 +595,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C1F49B55-5D33-4591-A958-435CF6BDD979}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A43C5043-7ECF-41B1-B51E-A41E189D7C63}">
       <text>
         <r>
           <rPr>
@@ -618,7 +618,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{44EBD02E-541D-472A-90ED-614CDEB39446}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{2E034527-9227-491E-A3E4-5F0C8388B89A}">
       <text>
         <r>
           <rPr>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="783">
   <si>
     <t>Project Name</t>
   </si>
@@ -2521,6 +2521,24 @@
     <t>TC-ST-42</t>
   </si>
   <si>
+    <t>Invoice: Unpaid -&gt; Paid (FR-BIL-03)</t>
+  </si>
+  <si>
+    <t>Automated (PaymentDeskIT.manualConfirmation): Manager confirms a transfer the student did not claim</t>
+  </si>
+  <si>
+    <t>TC-ST-43</t>
+  </si>
+  <si>
+    <t>Invoice: Overdue -&gt; Paid (FR-BIL-03)</t>
+  </si>
+  <si>
+    <t>Manual on staging: Manager confirms an overdue debt the student did not claim</t>
+  </si>
+  <si>
+    <t>TC-ST-44</t>
+  </si>
+  <si>
     <t>Invoice: Awaiting confirmation -&gt; Unpaid (FR-BIL-03)</t>
   </si>
   <si>
@@ -2530,7 +2548,7 @@
     <t>Status becomes Unpaid</t>
   </si>
   <si>
-    <t>TC-ST-43</t>
+    <t>TC-ST-45</t>
   </si>
   <si>
     <t>Invoice: Awaiting confirmation -&gt; Overdue (FR-BIL-03)</t>
@@ -2542,7 +2560,7 @@
     <t>Status becomes Overdue</t>
   </si>
   <si>
-    <t>TC-ST-44</t>
+    <t>TC-ST-46</t>
   </si>
   <si>
     <t>Invoice: Awaiting confirmation -&gt; Void (FR-BIL-03)</t>
@@ -2554,7 +2572,7 @@
     <t>Status becomes Void</t>
   </si>
   <si>
-    <t>TC-ST-45</t>
+    <t>TC-ST-47</t>
   </si>
   <si>
     <t>Invoice: Unpaid -&gt; Overdue (FR-BIL-05)</t>
@@ -2563,7 +2581,7 @@
     <t>Automated (FinanceIT.overdueAndReminders): Due date passes (Utility, charges)</t>
   </si>
   <si>
-    <t>TC-ST-46</t>
+    <t>TC-ST-48</t>
   </si>
   <si>
     <t>Invoice: Unpaid -&gt; Void (FR-ASG-11, FR-APP-04)</t>
@@ -2572,7 +2590,7 @@
     <t>Automated (ApplicationsIT.cancellationVoidsOrRefunds): Forfeit or cancelled Application</t>
   </si>
   <si>
-    <t>TC-ST-47</t>
+    <t>TC-ST-49</t>
   </si>
   <si>
     <t>Invoice: Overdue -&gt; Void (FR-ASG-06)</t>
@@ -2581,7 +2599,7 @@
     <t>Manual on staging: Overdue Utility settled from the Utility Deposit at check-out</t>
   </si>
   <si>
-    <t>TC-ST-48</t>
+    <t>TC-ST-50</t>
   </si>
   <si>
     <t>Payment claim: (new) -&gt; Claimed (FR-BIL-02)</t>
@@ -2593,7 +2611,7 @@
     <t>Status is Claimed</t>
   </si>
   <si>
-    <t>TC-ST-49</t>
+    <t>TC-ST-51</t>
   </si>
   <si>
     <t>Payment claim: Claimed -&gt; Confirmed (FR-BIL-03)</t>
@@ -2608,7 +2626,19 @@
     <t>Entity in state Claimed</t>
   </si>
   <si>
-    <t>TC-ST-50</t>
+    <t>TC-ST-52</t>
+  </si>
+  <si>
+    <t>Payment claim: (new) -&gt; Confirmed (FR-BIL-03)</t>
+  </si>
+  <si>
+    <t>Automated (PaymentDeskIT.manualConfirmation): Manager confirms a transfer the student did not claim (claim in the Manager's name)</t>
+  </si>
+  <si>
+    <t>Status is Confirmed</t>
+  </si>
+  <si>
+    <t>TC-ST-53</t>
   </si>
   <si>
     <t>Payment claim: Claimed -&gt; Rejected (FR-BIL-03)</t>
@@ -2617,7 +2647,7 @@
     <t>Automated (PaymentClaimIT.rejectionsGiveTimeBackThenCancel): Manager rejects with a reason</t>
   </si>
   <si>
-    <t>TC-ST-51</t>
+    <t>TC-ST-54</t>
   </si>
   <si>
     <t>Maintenance Request: (new) -&gt; Submitted (FR-MNT-01)</t>
@@ -2629,7 +2659,7 @@
     <t>Status is Submitted</t>
   </si>
   <si>
-    <t>TC-ST-52</t>
+    <t>TC-ST-55</t>
   </si>
   <si>
     <t>Maintenance Request: Submitted -&gt; Assigned (FR-REQ-06)</t>
@@ -2641,7 +2671,7 @@
     <t>Status becomes Assigned</t>
   </si>
   <si>
-    <t>TC-ST-53</t>
+    <t>TC-ST-56</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; Submitted (FR-MNT-02)</t>
@@ -2653,7 +2683,7 @@
     <t>Entity in state Assigned</t>
   </si>
   <si>
-    <t>TC-ST-54</t>
+    <t>TC-ST-57</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; In Progress (FR-MNT-02)</t>
@@ -2665,7 +2695,7 @@
     <t>Status becomes In Progress</t>
   </si>
   <si>
-    <t>TC-ST-55</t>
+    <t>TC-ST-58</t>
   </si>
   <si>
     <t>Maintenance Request: In Progress -&gt; Resolved (FR-MNT-02)</t>
@@ -2680,7 +2710,7 @@
     <t>Entity in state In Progress</t>
   </si>
   <si>
-    <t>TC-ST-56</t>
+    <t>TC-ST-59</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; Resolved (FR-MNT-02)</t>
@@ -2689,7 +2719,7 @@
     <t>Manual on staging: Staff fixes it without starting it first</t>
   </si>
   <si>
-    <t>TC-ST-57</t>
+    <t>TC-ST-60</t>
   </si>
   <si>
     <t>Maintenance Request: Resolved -&gt; Closed (FR-MNT-02)</t>
@@ -2704,7 +2734,7 @@
     <t>Entity in state Resolved</t>
   </si>
   <si>
-    <t>TC-ST-58</t>
+    <t>TC-ST-61</t>
   </si>
   <si>
     <t>Maintenance Request: Resolved -&gt; Assigned (FR-MNT-02)</t>
@@ -2713,7 +2743,7 @@
     <t>Automated (MaintenanceIT.staffWorkTheRequest): Reporter reopens (once)</t>
   </si>
   <si>
-    <t>TC-ST-59</t>
+    <t>TC-ST-62</t>
   </si>
   <si>
     <t>Maintenance Request: Submitted -&gt; Closed (FR-MNT-02)</t>
@@ -2722,7 +2752,7 @@
     <t>Manual on staging: Staff closes a duplicate</t>
   </si>
   <si>
-    <t>TC-ST-60</t>
+    <t>TC-ST-63</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; Closed (FR-MNT-02)</t>
@@ -2731,13 +2761,13 @@
     <t>Manual on staging: Staff closes it</t>
   </si>
   <si>
-    <t>TC-ST-61</t>
+    <t>TC-ST-64</t>
   </si>
   <si>
     <t>Maintenance Request: In Progress -&gt; Closed (FR-MNT-02)</t>
   </si>
   <si>
-    <t>TC-ST-62</t>
+    <t>TC-ST-65</t>
   </si>
   <si>
     <t>Invoice: Paid / Void -&gt; (refused) (FR-BIL-02)</t>
@@ -2752,7 +2782,7 @@
     <t>Entity in state Paid / Void</t>
   </si>
   <si>
-    <t>TC-ST-63</t>
+    <t>TC-ST-66</t>
   </si>
   <si>
     <t>Invoice: Void -&gt; (refused) (FR-BIL-03)</t>
@@ -2764,7 +2794,7 @@
     <t>Entity in state Void</t>
   </si>
   <si>
-    <t>TC-ST-64</t>
+    <t>TC-ST-67</t>
   </si>
   <si>
     <t>Invoice: Paid -&gt; (refused) (FR-BIL-03)</t>
@@ -2776,7 +2806,7 @@
     <t>Entity in state Paid</t>
   </si>
   <si>
-    <t>TC-ST-65</t>
+    <t>TC-ST-68</t>
   </si>
   <si>
     <t>Next-Term Allocation: Continuing (fees issued) -&gt; (refused) (FR-ASG-10)</t>
@@ -5136,7 +5166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E5B4AF-66B4-4D88-A095-5620FED4C8D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A28B9E-5074-43BB-B1FC-027D3A178245}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5685,8 +5715,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2CEF4543-2BC4-45EE-8ECA-52B882226A21}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F8B113DD-5FCC-4CF1-93DD-D184ACFCCC02}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{728589D6-ECE2-45B3-A7B4-61785B4101C5}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{68001AF1-2618-4664-A12B-5907817412AB}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5702,7 +5732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFAC4C5-7B38-4F1A-A4DB-249C983B77AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7380326F-EC01-471A-BACF-D4276844D9D6}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6235,8 +6265,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{18A190DA-F763-46C7-A77A-C9047380474C}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{13E4735A-2F72-46D4-8C98-6232518DD808}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{508D039F-294A-4271-ADD7-90E7D747EEC5}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{948C5CA9-6EEF-494F-B49F-6A5D82353F95}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6252,7 +6282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3003146E-4D16-40AC-9247-AF6E582BB056}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94981312-D1E3-4BA8-A1E5-6A60C7F28DD7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6769,8 +6799,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{41F56641-4198-4272-9A4B-86D787E63425}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2667BF63-E4AF-49CC-A72B-276BDC53740E}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CD65D287-2993-488A-815D-19908A395B57}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8D0B1D4C-634C-4DAC-B5BF-2D0CF39C1199}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6786,7 +6816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A7F426-AA6D-442F-BC43-186F33A4207C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88AA035E-4314-420E-B4D9-56B92A4B9332}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7351,8 +7381,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{925BEF88-3972-4B92-A49A-655B01005B0E}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FB773C09-CC68-48D9-874B-CF626F1C3312}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{16FEC855-3456-412C-8A10-0A09CA7E88AC}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{77DBB328-729C-4B3A-B933-AE965274EB2E}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7368,7 +7398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4B63D2-644A-4BA9-B19E-1CC6C5B631CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29C2793-7BC1-43F8-B49B-DDBBCA5FC30D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7933,8 +7963,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{9958EDA7-DEDF-4C66-9CBB-836E0C9C39B2}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{61E16292-4AFB-4BF6-8E13-1F1AFC183966}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7B01A7E1-366A-4F0C-9D1B-C94A7631BE90}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2199A47B-58F3-4134-9B0B-87FFD6ACACDE}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7950,7 +7980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9686CFF7-C2C4-4BE8-B624-39C80D0FF57B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A9E0EA-FFC6-4F22-BB8F-94E223C7C9B4}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8467,8 +8497,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{69B71ABD-FFF9-45FA-B272-CEEBF87E6B47}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0DA0C4B8-7DCD-49DD-BF0E-9198F395961E}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{BA7DF2DE-E963-4CE1-8671-1C7EA16A9305}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{735D9322-C48B-4954-9900-1E2C909381D6}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8484,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9CBB0F-E872-403D-A39D-18E281AA376F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8C0A26-44EE-4AE7-8A2C-558F0BF83032}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9033,8 +9063,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{9FE10CC1-0616-4EE9-87ED-0EE95C38CC42}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{3F5FBE2B-F4D8-4F31-A6B4-D2218721B7D3}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3B53338F-22DC-4F98-B954-D081820C9F3F}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F0EA1F4D-D1DB-4F50-ADB4-AE8F4C41C3B4}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9050,7 +9080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7BBD42A-BA0D-46C2-B8F6-95A10ED8E40D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4AE7C7-84A3-4E3C-9C14-2D87751B5223}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9583,8 +9613,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{C4DED846-A9CD-4AFD-881E-151C6EEA8E13}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E5CF4379-965A-48BD-BA18-4FCBA16E67C7}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{8E145291-59CC-4C77-BBBD-5678032B5B14}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{5E93AE33-5109-424D-B67F-9D305B5794DE}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9600,7 +9630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530DC4AD-2B65-4BC8-A7A0-6BF047009094}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2539B861-34B5-4B85-A71F-64B34073FF42}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10133,8 +10163,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1031B598-2437-4166-851F-4B6A8845FEBB}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{1942F782-8D61-45AA-8BF9-DF75E1C5C726}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{844E9318-C770-4320-9456-375E09CA7C90}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{4B09CE41-4608-448E-A26E-CE2461AF062E}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10150,7 +10180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03DA3BC8-9F25-4CCF-AF25-B6120E5C2120}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A82B2336-37FD-4247-847B-A1536E531F92}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10683,8 +10713,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1F5C1360-7204-4026-B779-5B99622320E8}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BAFD1F67-0304-4A1B-B977-A5BB79AD2EB0}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A22709DE-4D3F-4A99-AEB1-060CA5F1A89B}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{37FEAB38-B771-46A6-A690-7BFC9007B579}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10799,7 +10829,7 @@
         <v>59</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="D9" s="97" t="s">
         <v>60</v>
@@ -10817,7 +10847,7 @@
         <v>80</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="D10" s="97" t="s">
         <v>81</v>
@@ -10835,7 +10865,7 @@
         <v>104</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="D11" s="97" t="s">
         <v>105</v>
@@ -10853,7 +10883,7 @@
         <v>128</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="D12" s="97" t="s">
         <v>129</v>
@@ -10871,7 +10901,7 @@
         <v>152</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>153</v>
@@ -10889,7 +10919,7 @@
         <v>167</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="D14" s="97" t="s">
         <v>168</v>
@@ -10907,7 +10937,7 @@
         <v>190</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="D15" s="97" t="s">
         <v>191</v>
@@ -10925,7 +10955,7 @@
         <v>214</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D16" s="97" t="s">
         <v>215</v>
@@ -10943,7 +10973,7 @@
         <v>233</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="D17" s="97" t="s">
         <v>234</v>
@@ -10961,7 +10991,7 @@
         <v>248</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="D18" s="97" t="s">
         <v>249</v>
@@ -10979,7 +11009,7 @@
         <v>275</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="D19" s="97" t="s">
         <v>276</v>
@@ -10997,7 +11027,7 @@
         <v>302</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="D20" s="97" t="s">
         <v>303</v>
@@ -11015,7 +11045,7 @@
         <v>317</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="D21" s="97" t="s">
         <v>318</v>
@@ -11033,7 +11063,7 @@
         <v>340</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="D22" s="97" t="s">
         <v>341</v>
@@ -11050,7 +11080,7 @@
         <v>359</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="D23" s="97" t="s">
         <v>360</v>
@@ -11067,7 +11097,7 @@
         <v>378</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="D24" s="97" t="s">
         <v>379</v>
@@ -11084,7 +11114,7 @@
         <v>397</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="D25" s="97" t="s">
         <v>398</v>
@@ -11101,7 +11131,7 @@
         <v>416</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="D26" s="97" t="s">
         <v>417</v>
@@ -11118,13 +11148,13 @@
         <v>435</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="D27" s="97" t="s">
         <v>436</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -11135,13 +11165,13 @@
         <v>463</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="D28" s="97" t="s">
         <v>464</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -11149,16 +11179,16 @@
         <v>21</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="D29" s="97" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -11180,7 +11210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E596B6F4-4E3D-446B-A847-F67677A14B90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D538AC-5969-4D57-893A-754D7E98A163}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -11713,8 +11743,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{D79251B8-9C61-4367-9831-7CE7028D1C4C}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{028A309B-3871-4FA3-B8BE-56BE121EF93D}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{567CF4E1-61F3-4588-931B-95A51BA266EF}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FBC3F110-1069-4B32-A3EC-EAFF980D8C2C}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11730,7 +11760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6274D074-201A-45A7-89EF-4487CF9A189F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCA0B04C-C20B-48A0-A80C-CC1A7EBAB3EF}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12263,8 +12293,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{4083F91F-54D6-4111-BDA2-01DA20E9A7A9}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{C3DA65BD-D69F-4279-B077-ADBD91995A7A}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{43745D66-58E1-46C5-992A-BFCD3A1FE22D}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0165B0E3-2EF9-46A8-9EC2-195475D7175B}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12280,7 +12310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0404CAB6-492B-4E15-B7FB-64874ADFE64C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EF45BC1-E045-4AAE-ADE5-003920D9650C}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12809,8 +12839,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{4802C0FA-1B1C-4E0A-B0AA-9B82886AD7FC}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F1B7959F-9D96-4F46-B465-FC55EC12D15E}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{EA655697-0ADB-4CE3-A365-013ADF13734F}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{5444B4F8-151C-4986-8420-CD2F6A1EF162}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12826,11 +12856,11 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77921DEE-F57A-4B59-8583-CD42ED754BF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8BD86F-4EFA-467F-BA13-B2C7CC6BCAE3}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -12913,7 +12943,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -12972,7 +13002,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -12980,7 +13010,7 @@
       </c>
       <c r="D6" s="88">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="94">
         <f t="shared" si="0"/>
@@ -14613,10 +14643,10 @@
         <v>627</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>38</v>
@@ -14638,31 +14668,27 @@
       <c r="Q53" s="42"/>
       <c r="R53" s="43"/>
     </row>
-    <row r="54" spans="1:18" ht="52.8">
+    <row r="54" spans="1:18" ht="39.6">
       <c r="A54" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="B54" s="39" t="s">
         <v>629</v>
       </c>
-      <c r="B54" s="39" t="s">
+      <c r="C54" s="39" t="s">
         <v>630</v>
       </c>
-      <c r="C54" s="39" t="s">
-        <v>631</v>
-      </c>
       <c r="D54" s="40" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G54" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H54" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
       <c r="I54" s="38"/>
       <c r="J54" s="38"/>
       <c r="K54" s="38"/>
@@ -14676,16 +14702,16 @@
     </row>
     <row r="55" spans="1:18" ht="52.8">
       <c r="A55" s="38" t="s">
+        <v>631</v>
+      </c>
+      <c r="B55" s="39" t="s">
+        <v>632</v>
+      </c>
+      <c r="C55" s="39" t="s">
         <v>633</v>
       </c>
-      <c r="B55" s="39" t="s">
+      <c r="D55" s="40" t="s">
         <v>634</v>
-      </c>
-      <c r="C55" s="39" t="s">
-        <v>635</v>
-      </c>
-      <c r="D55" s="40" t="s">
-        <v>636</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>624</v>
@@ -14710,21 +14736,21 @@
       <c r="Q55" s="42"/>
       <c r="R55" s="43"/>
     </row>
-    <row r="56" spans="1:18" ht="39.6">
+    <row r="56" spans="1:18" ht="52.8">
       <c r="A56" s="38" t="s">
+        <v>635</v>
+      </c>
+      <c r="B56" s="39" t="s">
+        <v>636</v>
+      </c>
+      <c r="C56" s="39" t="s">
         <v>637</v>
       </c>
-      <c r="B56" s="39" t="s">
+      <c r="D56" s="40" t="s">
         <v>638</v>
       </c>
-      <c r="C56" s="39" t="s">
-        <v>639</v>
-      </c>
-      <c r="D56" s="40" t="s">
-        <v>632</v>
-      </c>
       <c r="E56" s="40" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>38</v>
@@ -14746,21 +14772,21 @@
       <c r="Q56" s="42"/>
       <c r="R56" s="43"/>
     </row>
-    <row r="57" spans="1:18" ht="39.6">
+    <row r="57" spans="1:18" ht="52.8">
       <c r="A57" s="38" t="s">
+        <v>639</v>
+      </c>
+      <c r="B57" s="39" t="s">
         <v>640</v>
       </c>
-      <c r="B57" s="39" t="s">
+      <c r="C57" s="39" t="s">
         <v>641</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="D57" s="40" t="s">
         <v>642</v>
       </c>
-      <c r="D57" s="40" t="s">
-        <v>636</v>
-      </c>
       <c r="E57" s="40" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>38</v>
@@ -14793,16 +14819,20 @@
         <v>645</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G58" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H58" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I58" s="38"/>
       <c r="J58" s="38"/>
       <c r="K58" s="38"/>
@@ -14814,7 +14844,7 @@
       <c r="Q58" s="42"/>
       <c r="R58" s="43"/>
     </row>
-    <row r="59" spans="1:18" ht="52.8">
+    <row r="59" spans="1:18" ht="39.6">
       <c r="A59" s="38" t="s">
         <v>646</v>
       </c>
@@ -14825,10 +14855,10 @@
         <v>648</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>470</v>
+        <v>615</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>38</v>
@@ -14852,29 +14882,25 @@
     </row>
     <row r="60" spans="1:18" ht="39.6">
       <c r="A60" s="38" t="s">
+        <v>649</v>
+      </c>
+      <c r="B60" s="39" t="s">
         <v>650</v>
       </c>
-      <c r="B60" s="39" t="s">
+      <c r="C60" s="39" t="s">
         <v>651</v>
       </c>
-      <c r="C60" s="39" t="s">
-        <v>652</v>
-      </c>
       <c r="D60" s="40" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>654</v>
+        <v>619</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G60" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H60" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
       <c r="I60" s="38"/>
       <c r="J60" s="38"/>
       <c r="K60" s="38"/>
@@ -14888,19 +14914,19 @@
     </row>
     <row r="61" spans="1:18" ht="52.8">
       <c r="A61" s="38" t="s">
+        <v>652</v>
+      </c>
+      <c r="B61" s="39" t="s">
+        <v>653</v>
+      </c>
+      <c r="C61" s="39" t="s">
+        <v>654</v>
+      </c>
+      <c r="D61" s="40" t="s">
         <v>655</v>
       </c>
-      <c r="B61" s="39" t="s">
-        <v>656</v>
-      </c>
-      <c r="C61" s="39" t="s">
-        <v>657</v>
-      </c>
-      <c r="D61" s="40" t="s">
-        <v>507</v>
-      </c>
       <c r="E61" s="40" t="s">
-        <v>654</v>
+        <v>470</v>
       </c>
       <c r="F61" s="38" t="s">
         <v>38</v>
@@ -14924,19 +14950,19 @@
     </row>
     <row r="62" spans="1:18" ht="39.6">
       <c r="A62" s="38" t="s">
+        <v>656</v>
+      </c>
+      <c r="B62" s="39" t="s">
+        <v>657</v>
+      </c>
+      <c r="C62" s="39" t="s">
         <v>658</v>
       </c>
-      <c r="B62" s="39" t="s">
+      <c r="D62" s="40" t="s">
         <v>659</v>
       </c>
-      <c r="C62" s="39" t="s">
+      <c r="E62" s="40" t="s">
         <v>660</v>
-      </c>
-      <c r="D62" s="40" t="s">
-        <v>661</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>470</v>
       </c>
       <c r="F62" s="38" t="s">
         <v>38</v>
@@ -14958,21 +14984,21 @@
       <c r="Q62" s="42"/>
       <c r="R62" s="43"/>
     </row>
-    <row r="63" spans="1:18" ht="52.8">
+    <row r="63" spans="1:18" ht="66">
       <c r="A63" s="38" t="s">
+        <v>661</v>
+      </c>
+      <c r="B63" s="39" t="s">
         <v>662</v>
       </c>
-      <c r="B63" s="39" t="s">
+      <c r="C63" s="39" t="s">
         <v>663</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="D63" s="40" t="s">
         <v>664</v>
       </c>
-      <c r="D63" s="40" t="s">
-        <v>665</v>
-      </c>
       <c r="E63" s="40" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>38</v>
@@ -14994,27 +15020,31 @@
       <c r="Q63" s="42"/>
       <c r="R63" s="43"/>
     </row>
-    <row r="64" spans="1:18" ht="26.4">
+    <row r="64" spans="1:18" ht="52.8">
       <c r="A64" s="38" t="s">
+        <v>665</v>
+      </c>
+      <c r="B64" s="39" t="s">
         <v>666</v>
       </c>
-      <c r="B64" s="39" t="s">
+      <c r="C64" s="39" t="s">
         <v>667</v>
       </c>
-      <c r="C64" s="39" t="s">
-        <v>668</v>
-      </c>
       <c r="D64" s="40" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="F64" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G64" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H64" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I64" s="38"/>
       <c r="J64" s="38"/>
       <c r="K64" s="38"/>
@@ -15028,19 +15058,19 @@
     </row>
     <row r="65" spans="1:18" ht="39.6">
       <c r="A65" s="38" t="s">
+        <v>668</v>
+      </c>
+      <c r="B65" s="39" t="s">
+        <v>669</v>
+      </c>
+      <c r="C65" s="39" t="s">
         <v>670</v>
       </c>
-      <c r="B65" s="39" t="s">
+      <c r="D65" s="40" t="s">
         <v>671</v>
       </c>
-      <c r="C65" s="39" t="s">
-        <v>672</v>
-      </c>
-      <c r="D65" s="40" t="s">
-        <v>673</v>
-      </c>
       <c r="E65" s="40" t="s">
-        <v>669</v>
+        <v>470</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>38</v>
@@ -15062,21 +15092,21 @@
       <c r="Q65" s="42"/>
       <c r="R65" s="43"/>
     </row>
-    <row r="66" spans="1:18" ht="39.6">
+    <row r="66" spans="1:18" ht="52.8">
       <c r="A66" s="38" t="s">
+        <v>672</v>
+      </c>
+      <c r="B66" s="39" t="s">
+        <v>673</v>
+      </c>
+      <c r="C66" s="39" t="s">
         <v>674</v>
       </c>
-      <c r="B66" s="39" t="s">
+      <c r="D66" s="40" t="s">
         <v>675</v>
       </c>
-      <c r="C66" s="39" t="s">
-        <v>676</v>
-      </c>
-      <c r="D66" s="40" t="s">
-        <v>677</v>
-      </c>
       <c r="E66" s="40" t="s">
-        <v>678</v>
+        <v>495</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>38</v>
@@ -15100,19 +15130,19 @@
     </row>
     <row r="67" spans="1:18" ht="26.4">
       <c r="A67" s="38" t="s">
+        <v>676</v>
+      </c>
+      <c r="B67" s="39" t="s">
+        <v>677</v>
+      </c>
+      <c r="C67" s="39" t="s">
+        <v>678</v>
+      </c>
+      <c r="D67" s="40" t="s">
+        <v>479</v>
+      </c>
+      <c r="E67" s="40" t="s">
         <v>679</v>
-      </c>
-      <c r="B67" s="39" t="s">
-        <v>680</v>
-      </c>
-      <c r="C67" s="39" t="s">
-        <v>681</v>
-      </c>
-      <c r="D67" s="40" t="s">
-        <v>677</v>
-      </c>
-      <c r="E67" s="40" t="s">
-        <v>669</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>37</v>
@@ -15132,19 +15162,19 @@
     </row>
     <row r="68" spans="1:18" ht="39.6">
       <c r="A68" s="38" t="s">
+        <v>680</v>
+      </c>
+      <c r="B68" s="39" t="s">
+        <v>681</v>
+      </c>
+      <c r="C68" s="39" t="s">
         <v>682</v>
       </c>
-      <c r="B68" s="39" t="s">
+      <c r="D68" s="40" t="s">
         <v>683</v>
       </c>
-      <c r="C68" s="39" t="s">
-        <v>684</v>
-      </c>
-      <c r="D68" s="40" t="s">
-        <v>685</v>
-      </c>
       <c r="E68" s="40" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>38</v>
@@ -15168,19 +15198,19 @@
     </row>
     <row r="69" spans="1:18" ht="39.6">
       <c r="A69" s="38" t="s">
+        <v>684</v>
+      </c>
+      <c r="B69" s="39" t="s">
+        <v>685</v>
+      </c>
+      <c r="C69" s="39" t="s">
+        <v>686</v>
+      </c>
+      <c r="D69" s="40" t="s">
         <v>687</v>
       </c>
-      <c r="B69" s="39" t="s">
+      <c r="E69" s="40" t="s">
         <v>688</v>
-      </c>
-      <c r="C69" s="39" t="s">
-        <v>689</v>
-      </c>
-      <c r="D69" s="40" t="s">
-        <v>665</v>
-      </c>
-      <c r="E69" s="40" t="s">
-        <v>686</v>
       </c>
       <c r="F69" s="38" t="s">
         <v>38</v>
@@ -15204,19 +15234,19 @@
     </row>
     <row r="70" spans="1:18" ht="26.4">
       <c r="A70" s="38" t="s">
+        <v>689</v>
+      </c>
+      <c r="B70" s="39" t="s">
         <v>690</v>
       </c>
-      <c r="B70" s="39" t="s">
+      <c r="C70" s="39" t="s">
         <v>691</v>
       </c>
-      <c r="C70" s="39" t="s">
-        <v>692</v>
-      </c>
       <c r="D70" s="40" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E70" s="40" t="s">
-        <v>495</v>
+        <v>679</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>37</v>
@@ -15234,27 +15264,31 @@
       <c r="Q70" s="42"/>
       <c r="R70" s="43"/>
     </row>
-    <row r="71" spans="1:18" ht="26.4">
+    <row r="71" spans="1:18" ht="39.6">
       <c r="A71" s="38" t="s">
+        <v>692</v>
+      </c>
+      <c r="B71" s="39" t="s">
         <v>693</v>
       </c>
-      <c r="B71" s="39" t="s">
+      <c r="C71" s="39" t="s">
         <v>694</v>
       </c>
-      <c r="C71" s="39" t="s">
+      <c r="D71" s="40" t="s">
         <v>695</v>
       </c>
-      <c r="D71" s="40" t="s">
-        <v>685</v>
-      </c>
       <c r="E71" s="40" t="s">
-        <v>669</v>
+        <v>696</v>
       </c>
       <c r="F71" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G71" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I71" s="38"/>
       <c r="J71" s="38"/>
       <c r="K71" s="38"/>
@@ -15266,27 +15300,31 @@
       <c r="Q71" s="42"/>
       <c r="R71" s="43"/>
     </row>
-    <row r="72" spans="1:18" ht="26.4">
+    <row r="72" spans="1:18" ht="39.6">
       <c r="A72" s="38" t="s">
+        <v>697</v>
+      </c>
+      <c r="B72" s="39" t="s">
+        <v>698</v>
+      </c>
+      <c r="C72" s="39" t="s">
+        <v>699</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>675</v>
+      </c>
+      <c r="E72" s="40" t="s">
         <v>696</v>
       </c>
-      <c r="B72" s="39" t="s">
-        <v>697</v>
-      </c>
-      <c r="C72" s="39" t="s">
-        <v>695</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>685</v>
-      </c>
-      <c r="E72" s="40" t="s">
-        <v>678</v>
-      </c>
       <c r="F72" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G72" s="38"/>
-      <c r="H72" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G72" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I72" s="38"/>
       <c r="J72" s="38"/>
       <c r="K72" s="38"/>
@@ -15298,31 +15336,27 @@
       <c r="Q72" s="42"/>
       <c r="R72" s="43"/>
     </row>
-    <row r="73" spans="1:18" ht="52.8">
+    <row r="73" spans="1:18" ht="26.4">
       <c r="A73" s="38" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B73" s="39" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C73" s="39" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G73" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H73" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
       <c r="I73" s="38"/>
       <c r="J73" s="38"/>
       <c r="K73" s="38"/>
@@ -15334,7 +15368,7 @@
       <c r="Q73" s="42"/>
       <c r="R73" s="43"/>
     </row>
-    <row r="74" spans="1:18" ht="39.6">
+    <row r="74" spans="1:18" ht="26.4">
       <c r="A74" s="38" t="s">
         <v>703</v>
       </c>
@@ -15345,20 +15379,16 @@
         <v>705</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>706</v>
+        <v>679</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G74" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H74" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
       <c r="I74" s="38"/>
       <c r="J74" s="38"/>
       <c r="K74" s="38"/>
@@ -15370,31 +15400,27 @@
       <c r="Q74" s="42"/>
       <c r="R74" s="43"/>
     </row>
-    <row r="75" spans="1:18" ht="39.6">
+    <row r="75" spans="1:18" ht="26.4">
       <c r="A75" s="38" t="s">
+        <v>706</v>
+      </c>
+      <c r="B75" s="39" t="s">
         <v>707</v>
       </c>
-      <c r="B75" s="39" t="s">
-        <v>708</v>
-      </c>
       <c r="C75" s="39" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="F75" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G75" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38"/>
       <c r="I75" s="38"/>
       <c r="J75" s="38"/>
       <c r="K75" s="38"/>
@@ -15408,19 +15434,19 @@
     </row>
     <row r="76" spans="1:18" ht="52.8">
       <c r="A76" s="38" t="s">
+        <v>708</v>
+      </c>
+      <c r="B76" s="39" t="s">
+        <v>709</v>
+      </c>
+      <c r="C76" s="39" t="s">
+        <v>710</v>
+      </c>
+      <c r="D76" s="40" t="s">
         <v>711</v>
       </c>
-      <c r="B76" s="39" t="s">
+      <c r="E76" s="40" t="s">
         <v>712</v>
-      </c>
-      <c r="C76" s="39" t="s">
-        <v>713</v>
-      </c>
-      <c r="D76" s="40" t="s">
-        <v>701</v>
-      </c>
-      <c r="E76" s="40" t="s">
-        <v>714</v>
       </c>
       <c r="F76" s="38" t="s">
         <v>38</v>
@@ -15442,6 +15468,114 @@
       <c r="Q76" s="42"/>
       <c r="R76" s="43"/>
     </row>
+    <row r="77" spans="1:18" ht="39.6">
+      <c r="A77" s="38" t="s">
+        <v>713</v>
+      </c>
+      <c r="B77" s="39" t="s">
+        <v>714</v>
+      </c>
+      <c r="C77" s="39" t="s">
+        <v>715</v>
+      </c>
+      <c r="D77" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E77" s="40" t="s">
+        <v>716</v>
+      </c>
+      <c r="F77" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G77" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H77" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="I77" s="38"/>
+      <c r="J77" s="38"/>
+      <c r="K77" s="38"/>
+      <c r="L77" s="38"/>
+      <c r="M77" s="38"/>
+      <c r="N77" s="38"/>
+      <c r="O77" s="41"/>
+      <c r="P77" s="43"/>
+      <c r="Q77" s="42"/>
+      <c r="R77" s="43"/>
+    </row>
+    <row r="78" spans="1:18" ht="39.6">
+      <c r="A78" s="38" t="s">
+        <v>717</v>
+      </c>
+      <c r="B78" s="39" t="s">
+        <v>718</v>
+      </c>
+      <c r="C78" s="39" t="s">
+        <v>719</v>
+      </c>
+      <c r="D78" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E78" s="40" t="s">
+        <v>720</v>
+      </c>
+      <c r="F78" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G78" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="I78" s="38"/>
+      <c r="J78" s="38"/>
+      <c r="K78" s="38"/>
+      <c r="L78" s="38"/>
+      <c r="M78" s="38"/>
+      <c r="N78" s="38"/>
+      <c r="O78" s="41"/>
+      <c r="P78" s="43"/>
+      <c r="Q78" s="42"/>
+      <c r="R78" s="43"/>
+    </row>
+    <row r="79" spans="1:18" ht="52.8">
+      <c r="A79" s="38" t="s">
+        <v>721</v>
+      </c>
+      <c r="B79" s="39" t="s">
+        <v>722</v>
+      </c>
+      <c r="C79" s="39" t="s">
+        <v>723</v>
+      </c>
+      <c r="D79" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E79" s="40" t="s">
+        <v>724</v>
+      </c>
+      <c r="F79" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G79" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="38"/>
+      <c r="M79" s="38"/>
+      <c r="N79" s="38"/>
+      <c r="O79" s="41"/>
+      <c r="P79" s="43"/>
+      <c r="Q79" s="42"/>
+      <c r="R79" s="43"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
@@ -15449,8 +15583,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{04578AE6-8CB5-4B24-9150-78E6C67245C0}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{CC872C72-96C6-49EE-BFB4-DF2F17AF0FC5}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{72986068-D12E-43EE-A627-B20AA97B9248}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BC187267-D2A7-4A55-9910-ECA84D14EDCE}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15466,7 +15600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484FD98-FEF3-4402-A25A-7D19118D0B73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DF2C3E-6042-4832-8BF1-259FF45EA756}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15500,7 +15634,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -15526,7 +15660,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -15766,7 +15900,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -15786,19 +15920,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>37</v>
@@ -15816,19 +15950,19 @@
     </row>
     <row r="13" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -15850,19 +15984,19 @@
     </row>
     <row r="14" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>37</v>
@@ -15880,19 +16014,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>37</v>
@@ -15910,19 +16044,19 @@
     </row>
     <row r="16" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -15944,19 +16078,19 @@
     </row>
     <row r="17" spans="1:17" ht="39.6" outlineLevel="1">
       <c r="A17" s="38" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>37</v>
@@ -16015,8 +16149,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0560E7A5-9293-49CB-8D5A-8457D37317D5}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8EA47727-9D99-4E49-8AD6-B6EECB086947}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7820279D-92A1-4330-AE85-EC4C36FF4A83}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{679E7FD0-B6E3-4B91-BA8B-E56A1F127B4D}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -16102,7 +16236,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="138" t="s">
-        <v>771</v>
+        <v>781</v>
       </c>
       <c r="D5" s="138"/>
       <c r="E5" s="139" t="s">
@@ -16120,7 +16254,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="140" t="s">
-        <v>772</v>
+        <v>782</v>
       </c>
       <c r="D6" s="140"/>
       <c r="E6" s="140"/>
@@ -16742,7 +16876,7 @@
       </c>
       <c r="D30" s="67">
         <f>'State transitions'!B6</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E30" s="67">
         <f>'State transitions'!C6</f>
@@ -16750,7 +16884,7 @@
       </c>
       <c r="F30" s="67">
         <f>'State transitions'!D6</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" s="67">
         <f>'State transitions'!E6</f>
@@ -16758,7 +16892,7 @@
       </c>
       <c r="H30" s="69">
         <f>'State transitions'!B4</f>
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -16767,7 +16901,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="D31" s="67">
         <f>NFRs!B6</f>
@@ -16808,7 +16942,7 @@
       </c>
       <c r="D33" s="72">
         <f>SUM(D9:D32)</f>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E33" s="72">
         <f>SUM(E9:E32)</f>
@@ -16816,7 +16950,7 @@
       </c>
       <c r="F33" s="72">
         <f>SUM(F9:F32)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" s="72">
         <f>SUM(G9:G32)</f>
@@ -16824,7 +16958,7 @@
       </c>
       <c r="H33" s="73">
         <f>SUM(H9:H32)</f>
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -16846,7 +16980,7 @@
       <c r="D35" s="57"/>
       <c r="E35" s="78">
         <f>(D33+E33)*100/(H33-G33)</f>
-        <v>87.741935483870961</v>
+        <v>87.341772151898738</v>
       </c>
       <c r="F35" s="57" t="s">
         <v>32</v>
@@ -16863,7 +16997,7 @@
       <c r="D36" s="57"/>
       <c r="E36" s="78">
         <f>D33*100/(H33-G33)</f>
-        <v>87.741935483870961</v>
+        <v>87.341772151898738</v>
       </c>
       <c r="F36" s="57" t="s">
         <v>32</v>
@@ -16896,7 +17030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4FCAE9-716F-49CC-8DC6-AA837D1749E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8598CCAC-3007-4B54-A9B1-37A1CBB45DD7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17429,8 +17563,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{83080052-7F30-4945-8EF6-53949B3F3582}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FDB3111E-A9F9-4653-85DD-99982DEF5B6D}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{C07998F5-1616-4263-B3C9-314C1DBCFA44}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{A2218C9A-9A66-4EE7-8D5B-FAC23DC04835}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17446,7 +17580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB20375-2B2B-4F86-A374-487CA2330F31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EDAE804-F75F-4756-AA23-9364D76FEA34}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17995,8 +18129,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E2E11E1A-0374-4DAC-8CDC-545B3DC3F056}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{321803B8-04E3-4C6D-BF95-D4BC8B8297E5}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CAC87874-6836-49AC-B7C0-CB738AF0C033}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{340E7CDD-AA68-45F9-A2EF-3A70ADDA4185}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18012,7 +18146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C93EF9E-5573-4BB5-968C-2441EE0A4FFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88795DC0-F1A0-4E2A-AF25-8492FDA747AC}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18561,8 +18695,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{28EC3342-A081-481B-B48E-6E8393930CF0}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FE1CDB95-025D-4B6D-820D-FF218BE17C7A}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0CC13D19-B9AA-4D3F-9349-FDF0C10DE57E}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{47E253DC-0FD5-46B2-A344-9AF0DF395C48}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18578,7 +18712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7969F227-145A-48FC-90C9-EE678293B1D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11B9D7F-71C0-441B-9CC5-E6C9C8337A37}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19127,8 +19261,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7AEFEBEF-557A-4D00-ABAF-07A46245C675}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{639B61D5-EC2C-4669-B141-C501F5D2384A}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{4AD93C8F-F7F4-438A-A050-E29C4BA44A74}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BB0FFCF5-D572-403E-9929-F5A0DE0BFEB3}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19144,7 +19278,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD5BD734-CC0A-4933-852A-0D106F0CDCC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E4943F-2155-47B0-870D-B850CC86D8E5}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19661,8 +19795,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{FBE5EFC9-4646-420E-9F6F-DBDB05767F6D}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D6087386-FE16-4173-A8C6-0B528A4FBFCB}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5C34A90F-A082-4D8F-BE32-6208EB4ADD33}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{A27E7CCA-0686-4417-BC4A-BC542423DAE8}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19678,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBABCA66-BBC9-4246-9F58-766520B36C8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581C73E6-2517-4075-93B4-4ABBB2C48B66}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -20227,8 +20361,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{91987B4C-67B3-4924-A46D-903FB81553FD}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{3E10169C-77BA-49DC-88A0-60B4CEDAD18C}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{006F103B-4B47-4266-B478-00086C27907A}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FDE3E3E1-2E66-4DAB-91B4-8272E4039E25}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
+++ b/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project\CampusStay FPT\docs\reports\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E87C9192-A7AD-46BF-839F-DB818F6BB023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F841DF90-4CA3-476C-8362-9BBED974D119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8964" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{10122E49-63A3-4F49-8814-BF3C2926AB4F}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{742D0B76-D9E9-4252-93BB-B221F23E365C}">
       <text>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C8A6E684-1F35-4027-B73D-7F45EBB4719C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{77D48CCB-D3E9-47C1-8F74-7DC73A84CB1E}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{4662D146-00C4-4720-91F8-637C84AFD700}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{6342FD03-DE80-4622-9502-1CDAF578DE82}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8AC34E88-C1DD-4A76-874B-9D0A14B47BA1}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E3D38773-E8D5-4D23-8F10-D4146DFB4484}">
       <text>
         <r>
           <rPr>
@@ -250,7 +250,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CDCE2A14-1E7C-4E79-B89B-FED08BBEFD43}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7F3F173B-B9C8-4C5D-B7FA-71FABC21C550}">
       <text>
         <r>
           <rPr>
@@ -273,7 +273,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{98CF15B8-5BAF-4CE3-9178-85F14603172C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{813CA870-2990-4457-9E39-2076F9F3DC78}">
       <text>
         <r>
           <rPr>
@@ -296,7 +296,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{46C506D5-49B3-41A3-A42D-C54830B99580}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{3289A8DF-A626-4B40-813F-6D3ABAE02975}">
       <text>
         <r>
           <rPr>
@@ -319,7 +319,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FF637EDE-4DF0-4368-B439-D66CF11D1481}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B0228C50-FCD5-40BF-83B9-4B7C205C2FC2}">
       <text>
         <r>
           <rPr>
@@ -342,7 +342,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A8AF4003-754F-41B7-B540-CE2D4BD181DB}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{14BB6B88-0616-40C8-8A7F-3D596BA2C6E5}">
       <text>
         <r>
           <rPr>
@@ -365,7 +365,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E86D8DC2-2FC9-40F7-BD6F-5E104F0BC277}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F53560C5-1BD2-43FA-8A79-BAE1E962E19E}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{71BDC6F0-8FA1-495A-A63F-5D87D141E4F2}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B5E78964-FB22-4BBC-8DF7-301D1091D99A}">
       <text>
         <r>
           <rPr>
@@ -411,7 +411,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{D652D157-0F63-4F3A-A1E9-0F87BAA70C4F}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8ABF1D58-D546-4BA8-82CB-B9C159FD1A2D}">
       <text>
         <r>
           <rPr>
@@ -434,7 +434,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{76C814EC-8ADD-481E-AB2A-69BBF38B7F85}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C148EF7E-B432-4EC1-9E3B-48B871BD48CA}">
       <text>
         <r>
           <rPr>
@@ -457,7 +457,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CE1FD42D-C284-4E08-8BFA-3553E328BC5A}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{1C0DBC72-A7E3-42FC-9F27-C0F3A88C506A}">
       <text>
         <r>
           <rPr>
@@ -480,7 +480,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E1BD3708-1CBA-409B-81A0-D79CE32EEC47}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{DB32BF34-4647-4CA2-98B1-3B9945B5D815}">
       <text>
         <r>
           <rPr>
@@ -503,7 +503,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{578F86B2-88A3-41DC-9218-160E5E3376DA}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FFE54B6C-4D57-43FE-9EC5-E18CB632DCE5}">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{805857F1-7C00-427B-97B7-C6C7D51E1FC5}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{266A489C-C301-4F2F-89DE-8CF7EC9B220C}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{EF306E5C-75BC-4D05-9C35-0F7BD13698BA}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{37956EE4-89E4-4C64-B25B-568E77175681}">
       <text>
         <r>
           <rPr>
@@ -572,7 +572,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{818D2B2B-BAD4-438F-98A4-88CE98AD70DA}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{96E257DC-6B65-4E11-9DD8-CF26AB62E53A}">
       <text>
         <r>
           <rPr>
@@ -595,7 +595,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A43C5043-7ECF-41B1-B51E-A41E189D7C63}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{AD286E95-66F6-4342-A923-845701168901}">
       <text>
         <r>
           <rPr>
@@ -618,7 +618,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{2E034527-9227-491E-A3E4-5F0C8388B89A}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{07A05EC3-C36E-49F0-AC88-55AE5E010767}">
       <text>
         <r>
           <rPr>
@@ -1063,13 +1063,13 @@
     <t>TC-F04-03</t>
   </si>
   <si>
-    <t>[Rule] Gia hạn (spec §6.6, D-13) is 1 to stay.max_terms, capped by the semesters the student has left (stay.program_semesters); it is kept on the Application and shown to the student and the back office; a student who already holds a Bed for the Term cannot apply (not a continuing resident).</t>
+    <t>[Rule] The stay length (spec §6.6, D-13) is 1 to stay.max_terms, capped by the semesters the student has left (stay.program_semesters); it is kept on the Application and shown to the student and the back office; a student who already holds a Bed for the Term cannot apply (not a continuing resident).</t>
   </si>
   <si>
     <t>Automated (ApplicationsIT.stayTermsOnTheApplication): POST /api/applications; GET /api/applications/eligibility; check the answer and the database</t>
   </si>
   <si>
-    <t>Gia hạn (spec §6.6, D-13) is 1 to stay.max_terms, capped by the semesters the student has left (stay.program_semesters); it is kept on the Application and shown to the student and the back office; a student who already holds a Bed for the Term cannot apply (not a continuing resident).</t>
+    <t>The stay length (spec §6.6, D-13) is 1 to stay.max_terms, capped by the semesters the student has left (stay.program_semesters); it is kept on the Application and shown to the student and the back office; a student who already holds a Bed for the Term cannot apply (not a continuing resident).</t>
   </si>
   <si>
     <t>TC-F04-04</t>
@@ -1963,7 +1963,7 @@
     <t>WF-01 Registration to residence (owner Lê Thành Minh Trung)</t>
   </si>
   <si>
-    <t>1. se220001 applies (4-bed, Standard, Gia hạn 2) and claims the Deposit transfer. 2. manager.a confirms the claim and approves the Application. 3. Stage B: se220004 (assigned, unpaid) claims the Balance; manager.a confirms. 4. staff.a1 confirms the Room code; the release job runs.</t>
+    <t>1. se220001 applies (4-bed, Standard, stay length 2) and claims the Deposit transfer. 2. manager.a confirms the claim and approves the Application. 3. Stage B: se220004 (assigned, unpaid) claims the Balance; manager.a confirms. 4. staff.a1 confirms the Room code; the release job runs.</t>
   </si>
   <si>
     <t>Application Submitted then Approved; se220004 is a resident (orange Bed) and sees the code; each step notified</t>
@@ -5166,7 +5166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A28B9E-5074-43BB-B1FC-027D3A178245}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80EABFC3-DFA3-44AA-85DE-3809F1E8AA5A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5715,8 +5715,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{728589D6-ECE2-45B3-A7B4-61785B4101C5}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{68001AF1-2618-4664-A12B-5907817412AB}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2EEFF69C-173D-4641-B813-01F6B858375E}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{CB65DCEB-8038-4791-B2D7-6FA96FA87FB9}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5732,7 +5732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7380326F-EC01-471A-BACF-D4276844D9D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E8CED1-E2A8-484E-B22C-F7D89E68240E}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6265,8 +6265,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{508D039F-294A-4271-ADD7-90E7D747EEC5}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{948C5CA9-6EEF-494F-B49F-6A5D82353F95}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5CACF4F8-D38C-4EA4-AEC9-3CF8369BC59E}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D327804B-003A-438C-BD84-7A7F59EC9C64}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6282,7 +6282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94981312-D1E3-4BA8-A1E5-6A60C7F28DD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA20CBC9-B510-476E-AD73-679359FC3321}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6799,8 +6799,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CD65D287-2993-488A-815D-19908A395B57}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8D0B1D4C-634C-4DAC-B5BF-2D0CF39C1199}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{6A24320B-B967-4218-9E3E-A1FD13FC57B1}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{495B43FD-E7F8-4796-A2EE-8AD1BF956CC2}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6816,7 +6816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88AA035E-4314-420E-B4D9-56B92A4B9332}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF31D43A-5253-4762-A3F2-4DB926D1C2B8}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7381,8 +7381,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{16FEC855-3456-412C-8A10-0A09CA7E88AC}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{77DBB328-729C-4B3A-B933-AE965274EB2E}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{EC7E90D5-FE49-4C72-80DE-7293B09ADD48}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{CB2F17CC-F786-43C7-AEA5-2273A5B81F50}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7398,7 +7398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29C2793-7BC1-43F8-B49B-DDBBCA5FC30D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A7BEC6-1DE1-4095-AEFE-2910FFBFF619}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7963,8 +7963,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7B01A7E1-366A-4F0C-9D1B-C94A7631BE90}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2199A47B-58F3-4134-9B0B-87FFD6ACACDE}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{9EEE1413-E18A-4BC9-869B-5FA97CBF7EC7}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0335E5A9-1F4C-461B-A205-C79BA44BF984}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7980,7 +7980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A9E0EA-FFC6-4F22-BB8F-94E223C7C9B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81136E9A-6C34-4A6B-83D5-2982B17F5CC3}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8497,8 +8497,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{BA7DF2DE-E963-4CE1-8671-1C7EA16A9305}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{735D9322-C48B-4954-9900-1E2C909381D6}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CEE8E35F-45D9-45CC-A09A-ED108AB1132C}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DBAC367A-C1FC-4199-BF65-D16D2EADE92B}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8514,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8C0A26-44EE-4AE7-8A2C-558F0BF83032}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86909117-6886-4072-AC65-DE46F8BC98BA}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9063,8 +9063,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3B53338F-22DC-4F98-B954-D081820C9F3F}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F0EA1F4D-D1DB-4F50-ADB4-AE8F4C41C3B4}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B0011691-29CF-4ED6-ABE8-F30B50564BF3}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{AFAE9920-BEDB-416A-B59E-03C6FF2EAE25}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9080,7 +9080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4AE7C7-84A3-4E3C-9C14-2D87751B5223}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F74272B-6CC8-43BE-86D0-02B451F60874}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9613,8 +9613,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{8E145291-59CC-4C77-BBBD-5678032B5B14}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{5E93AE33-5109-424D-B67F-9D305B5794DE}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{16C9FEF1-7EC6-4431-A8A6-389788466204}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2B2FE0F2-0D92-43AA-84D1-E105D92F43BB}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9630,7 +9630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2539B861-34B5-4B85-A71F-64B34073FF42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BBAA0D-1F1A-48CF-B032-12CF6A8730D9}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10163,8 +10163,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{844E9318-C770-4320-9456-375E09CA7C90}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{4B09CE41-4608-448E-A26E-CE2461AF062E}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{04A824B1-39D5-42AC-98C6-2877E24BFA07}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{79969EE3-423C-4BBB-902A-BEBC6F9180C6}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10180,7 +10180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A82B2336-37FD-4247-847B-A1536E531F92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01431B1-428E-4B81-B887-744B65ED8411}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10713,8 +10713,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A22709DE-4D3F-4A99-AEB1-060CA5F1A89B}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{37FEAB38-B771-46A6-A690-7BFC9007B579}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{F88E0C04-43C8-4532-BE5F-07C34A860FEC}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{151082F3-9ACF-4B14-8810-6149E4DC58A3}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11210,7 +11210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D538AC-5969-4D57-893A-754D7E98A163}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD876F9-43CB-401A-B4FF-09D1078F95A0}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -11743,8 +11743,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{567CF4E1-61F3-4588-931B-95A51BA266EF}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FBC3F110-1069-4B32-A3EC-EAFF980D8C2C}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{6614050A-4FCB-416B-B66B-164C4F9B468A}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F54728EB-7F11-40D0-9C90-463A041527CB}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11760,7 +11760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCA0B04C-C20B-48A0-A80C-CC1A7EBAB3EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C40307-789D-4E69-807D-0A126C1F8F94}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12293,8 +12293,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{43745D66-58E1-46C5-992A-BFCD3A1FE22D}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0165B0E3-2EF9-46A8-9EC2-195475D7175B}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5F1EC91C-D286-454E-A339-FED29E5974C4}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{ECC1C914-FB75-4A54-8081-A05A1FCCDBE7}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12310,7 +12310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EF45BC1-E045-4AAE-ADE5-003920D9650C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A07663-F36F-466C-9FCE-493785EB4C88}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12839,8 +12839,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{EA655697-0ADB-4CE3-A365-013ADF13734F}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{5444B4F8-151C-4986-8420-CD2F6A1EF162}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B4A9FB70-3BB1-43D2-9C4C-031AD0B04A38}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{3E02C823-2B5C-426E-AE6E-D0F808082F22}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12856,7 +12856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8BD86F-4EFA-467F-BA13-B2C7CC6BCAE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DA4739-4523-4767-84E0-67BB78E8B360}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15583,8 +15583,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{72986068-D12E-43EE-A627-B20AA97B9248}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BC187267-D2A7-4A55-9910-ECA84D14EDCE}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{315F9E3A-6752-4986-9DE3-5A007D0322C7}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BA3F866F-FB8E-43CF-85FC-2AE3B4F4ECAE}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15600,7 +15600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DF2C3E-6042-4832-8BF1-259FF45EA756}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA79DEC3-4F16-4848-9D2E-DBE0F0261379}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -16149,8 +16149,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7820279D-92A1-4330-AE85-EC4C36FF4A83}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{679E7FD0-B6E3-4B91-BA8B-E56A1F127B4D}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{41E55161-1FA5-4843-97F4-FC012A97D686}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E896A19D-D7DE-4785-88E2-054909A40A9D}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17030,7 +17030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8598CCAC-3007-4B54-A9B1-37A1CBB45DD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EA52DB-D958-47E5-84E7-BF2A1AC2E650}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17563,8 +17563,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{C07998F5-1616-4263-B3C9-314C1DBCFA44}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{A2218C9A-9A66-4EE7-8D5B-FAC23DC04835}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3E113A9C-8DF6-4A90-877E-E7E30EE6B5AB}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{32B08A14-3B77-4AD6-963B-C32B2ADB7801}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17580,7 +17580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EDAE804-F75F-4756-AA23-9364D76FEA34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B7354B-348A-42BB-B953-876F74A6C734}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18129,8 +18129,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CAC87874-6836-49AC-B7C0-CB738AF0C033}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{340E7CDD-AA68-45F9-A2EF-3A70ADDA4185}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A5881556-B38F-48C8-9189-2C70ADE9AA3A}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D8232463-BDC4-4A5E-A52B-75D2F4E7EBB4}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18146,7 +18146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88795DC0-F1A0-4E2A-AF25-8492FDA747AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F70B8DE-C3DF-4BB4-9253-EFD3F8EAA273}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18695,8 +18695,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0CC13D19-B9AA-4D3F-9349-FDF0C10DE57E}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{47E253DC-0FD5-46B2-A344-9AF0DF395C48}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{881F5939-668C-4B18-8309-0DDA3085F40E}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{B49B3EB8-8682-4D70-87C9-EBA8319307CA}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18712,7 +18712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11B9D7F-71C0-441B-9CC5-E6C9C8337A37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6E3706-AD40-4A99-9F9B-F5B78F5EDE9F}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19261,8 +19261,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{4AD93C8F-F7F4-438A-A050-E29C4BA44A74}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BB0FFCF5-D572-403E-9929-F5A0DE0BFEB3}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{6815E8F3-AFB1-4571-80AC-D0116F83B2BB}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BF82F414-A6DE-49F7-B0AE-586062A2B522}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19278,7 +19278,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E4943F-2155-47B0-870D-B850CC86D8E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1443F6AA-C17A-43FF-8897-6DF232EDB91F}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19795,8 +19795,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5C34A90F-A082-4D8F-BE32-6208EB4ADD33}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{A27E7CCA-0686-4417-BC4A-BC542423DAE8}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{DFABC16F-3B30-4D75-8FBD-67CB35B316C1}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8AF3B39B-9A8E-45B4-828E-1642E4A41058}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581C73E6-2517-4075-93B4-4ABBB2C48B66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A7B07B-1746-4E9E-8DCA-6AA79DAA4D05}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -20361,8 +20361,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{006F103B-4B47-4266-B478-00086C27907A}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FDE3E3E1-2E66-4DAB-91B4-8272E4039E25}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CC7612E3-F887-477B-B9EF-068B9DC56516}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E8C2B150-D2D7-41B2-890B-5533C20CB978}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
+++ b/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project\CampusStay FPT\docs\reports\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F841DF90-4CA3-476C-8362-9BBED974D119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E745127-1C88-4850-A598-A51329DD8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8964" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{742D0B76-D9E9-4252-93BB-B221F23E365C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{5F7E4F7E-CCFE-4A0C-AF18-E563D21E82B6}">
       <text>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{77D48CCB-D3E9-47C1-8F74-7DC73A84CB1E}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{2DC197E9-C4DB-4299-8AD7-8FAE00D954DB}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{6342FD03-DE80-4622-9502-1CDAF578DE82}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{25D156D7-E603-4BA9-92D9-FE0670ED1D79}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{E3D38773-E8D5-4D23-8F10-D4146DFB4484}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FBF898B3-F204-4D94-96AF-81BFD8B86150}">
       <text>
         <r>
           <rPr>
@@ -250,7 +250,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7F3F173B-B9C8-4C5D-B7FA-71FABC21C550}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FC764BC8-0DA0-4A99-A920-40825E74243D}">
       <text>
         <r>
           <rPr>
@@ -273,7 +273,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{813CA870-2990-4457-9E39-2076F9F3DC78}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{5E2EB953-89E4-40C5-AA92-88996FCB2CD0}">
       <text>
         <r>
           <rPr>
@@ -296,7 +296,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{3289A8DF-A626-4B40-813F-6D3ABAE02975}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{01CFE886-1392-4D77-828F-3968CB4DBFBA}">
       <text>
         <r>
           <rPr>
@@ -319,7 +319,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B0228C50-FCD5-40BF-83B9-4B7C205C2FC2}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{9FCE023D-BEEE-4FAB-B6F5-9C88F45098A7}">
       <text>
         <r>
           <rPr>
@@ -342,7 +342,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{14BB6B88-0616-40C8-8A7F-3D596BA2C6E5}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8A3EF57E-80DA-4FF3-9243-23AB734AC27E}">
       <text>
         <r>
           <rPr>
@@ -365,7 +365,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F53560C5-1BD2-43FA-8A79-BAE1E962E19E}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CEE345FE-B461-4223-931F-08669C9F95BC}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B5E78964-FB22-4BBC-8DF7-301D1091D99A}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A6DA9FAE-D940-4F37-A9C5-30245B20D4C1}">
       <text>
         <r>
           <rPr>
@@ -411,7 +411,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8ABF1D58-D546-4BA8-82CB-B9C159FD1A2D}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7D4657F8-2FA5-417B-BBB9-B7FD864E54B7}">
       <text>
         <r>
           <rPr>
@@ -434,7 +434,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C148EF7E-B432-4EC1-9E3B-48B871BD48CA}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{76BE6D56-E447-4CC4-8182-D4D3D50D497F}">
       <text>
         <r>
           <rPr>
@@ -457,7 +457,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{1C0DBC72-A7E3-42FC-9F27-C0F3A88C506A}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{20A46C1D-02C1-42EE-9E33-CEF0EA013BCD}">
       <text>
         <r>
           <rPr>
@@ -480,7 +480,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{DB32BF34-4647-4CA2-98B1-3B9945B5D815}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B9B4FAC3-4CBA-44AC-9B9C-37391CDDE958}">
       <text>
         <r>
           <rPr>
@@ -503,7 +503,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FFE54B6C-4D57-43FE-9EC5-E18CB632DCE5}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{770224C8-B8B6-40EC-8F5B-8BA4A0E1E61A}">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{266A489C-C301-4F2F-89DE-8CF7EC9B220C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{4071CAB7-F2A5-4F77-8B25-63DE364EE58E}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{37956EE4-89E4-4C64-B25B-568E77175681}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F991CBD9-7D07-4E25-9ACB-DF0871EC15BA}">
       <text>
         <r>
           <rPr>
@@ -572,7 +572,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{96E257DC-6B65-4E11-9DD8-CF26AB62E53A}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F9569ECF-01FE-48F6-9BDB-C09D5105582F}">
       <text>
         <r>
           <rPr>
@@ -595,7 +595,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{AD286E95-66F6-4342-A923-845701168901}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F63B14F5-9EEF-4CB3-9AD1-84A4250DE666}">
       <text>
         <r>
           <rPr>
@@ -618,7 +618,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{07A05EC3-C36E-49F0-AC88-55AE5E010767}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FC3F62B4-2F02-474E-94A8-4F07B4A40FE2}">
       <text>
         <r>
           <rPr>
@@ -1261,13 +1261,13 @@
     <t>TC-F07-04</t>
   </si>
   <si>
-    <t>[Rule] A Balance past its deadline without a claim is forfeited: the Allocation is cancelled, the Balance void, the Application Forfeited, the Deposit kept by the rule "Balance not paid" (a 0 % rule records no refund; a 10 % rule one refund, never two) and the student told; a claim waiting or an approved late check-in still running keeps the Bed.</t>
+    <t>[Rule] A Balance past its deadline without a claim is forfeited: the Allocation is cancelled, the Balance void, the Application Forfeited, the Deposit kept by the rule "Balance not paid" (a 0 % rule records no refund; a 10 % rule one refund, never two) and the student told; a claim waiting keeps the Bed, and so does a later Balance deadline a Manager chose when approving a late check-in, which may not pass the arrival day (the Balance is paid before check-in).</t>
   </si>
   <si>
     <t>Automated (ResidenceIT.unpaidBalanceIsForfeited): GET /api/inventory/rooms; POST /api/late-check-ins/{id}/decision; POST /api/students/me/late-check-in; check the answer and the database</t>
   </si>
   <si>
-    <t>A Balance past its deadline without a claim is forfeited: the Allocation is cancelled, the Balance void, the Application Forfeited, the Deposit kept by the rule "Balance not paid" (a 0 % rule records no refund; a 10 % rule one refund, never two) and the student told; a claim waiting or an approved late check-in still running keeps the Bed.</t>
+    <t>A Balance past its deadline without a claim is forfeited: the Allocation is cancelled, the Balance void, the Application Forfeited, the Deposit kept by the rule "Balance not paid" (a 0 % rule records no refund; a 10 % rule one refund, never two) and the student told; a claim waiting keeps the Bed, and so does a later Balance deadline a Manager chose when approving a late check-in, which may not pass the arrival day (the Balance is paid before check-in).</t>
   </si>
   <si>
     <t>Test seed (2 Blocks, 48 students, 7 back-office users); System (job) signed in</t>
@@ -1354,13 +1354,13 @@
     <t>TC-F09-01</t>
   </si>
   <si>
-    <t>[Main] The student asks online with a reason, the day and an evidence file, up to the check-in end plus late_check_in.max_days; the Managers are told; one request at a time; a Manager approves at most that day.</t>
+    <t>[Main] The student asks online with a reason, the day and an evidence file, up to the check-in end plus late_check_in.max_days; the Managers are told; one request per Term, also after the decision; a Manager approves at most that day.</t>
   </si>
   <si>
     <t>Automated (LateCheckInIT.studentAsksOnline): GET /api/late-check-ins; POST /api/late-check-ins/{id}/decision; GET /api/students/me/late-check-in; POST /api/students/me/late-check-in; check the answer and the database</t>
   </si>
   <si>
-    <t>The student asks online with a reason, the day and an evidence file, up to the check-in end plus late_check_in.max_days; the Managers are told; one request at a time; a Manager approves at most that day.</t>
+    <t>The student asks online with a reason, the day and an evidence file, up to the check-in end plus late_check_in.max_days; the Managers are told; one request per Term, also after the decision; a Manager approves at most that day.</t>
   </si>
   <si>
     <t>TC-F09-02</t>
@@ -1378,13 +1378,13 @@
     <t>TC-F09-03</t>
   </si>
   <si>
-    <t>[Rule] A rejection needs a reason; every Manager sees the request (ADR-19).</t>
+    <t>[Rule] A rejection needs a reason; every Manager sees the request (ADR-19); a student has one late check-in per Term, so the desk cannot record another after the rejection.</t>
   </si>
   <si>
     <t>Automated (LateCheckInIT.rejectedLateCheckIn): GET /api/late-check-ins; POST /api/late-check-ins/{id}/decision; check the answer and the database</t>
   </si>
   <si>
-    <t>A rejection needs a reason; every Manager sees the request (ADR-19).</t>
+    <t>A rejection needs a reason; every Manager sees the request (ADR-19); a student has one late check-in per Term, so the desk cannot record another after the rejection.</t>
   </si>
   <si>
     <t>F-10 Next-Term requests</t>
@@ -5166,7 +5166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80EABFC3-DFA3-44AA-85DE-3809F1E8AA5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65486304-7A84-409D-A1C7-F4BF060B43F9}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5715,8 +5715,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2EEFF69C-173D-4641-B813-01F6B858375E}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{CB65DCEB-8038-4791-B2D7-6FA96FA87FB9}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1F7081CD-14C9-4886-B2EA-B836072D7519}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{4762034D-20C5-4461-903A-DB076A9542DF}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5732,7 +5732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E8CED1-E2A8-484E-B22C-F7D89E68240E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82EFA14-BCFC-40DB-8EE4-34E609012C22}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6265,8 +6265,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5CACF4F8-D38C-4EA4-AEC9-3CF8369BC59E}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D327804B-003A-438C-BD84-7A7F59EC9C64}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{22B5695C-4312-4A0C-AAF3-737929356982}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{EF9B102A-1747-4009-AF65-CC4F739E6844}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6282,7 +6282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA20CBC9-B510-476E-AD73-679359FC3321}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8624025C-9582-40CA-B403-ABCA646C8117}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6799,8 +6799,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{6A24320B-B967-4218-9E3E-A1FD13FC57B1}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{495B43FD-E7F8-4796-A2EE-8AD1BF956CC2}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7C9E8767-2601-4476-BF1B-9F491D7E59E4}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D2D83D38-C9FB-4A54-B904-1942095CFBF4}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6816,7 +6816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF31D43A-5253-4762-A3F2-4DB926D1C2B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B7FC08-25EC-44BA-AFD7-15B9ED858F6D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7381,8 +7381,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{EC7E90D5-FE49-4C72-80DE-7293B09ADD48}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{CB2F17CC-F786-43C7-AEA5-2273A5B81F50}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{DE4FEA56-B968-4B20-9D37-779F8B9E6DA2}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{7CA51216-6222-48BC-A2A4-3B379F769BEA}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7398,7 +7398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A7BEC6-1DE1-4095-AEFE-2910FFBFF619}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{591A2B2C-9BC5-4615-8B30-0CCFF0FD00FA}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7963,8 +7963,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{9EEE1413-E18A-4BC9-869B-5FA97CBF7EC7}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0335E5A9-1F4C-461B-A205-C79BA44BF984}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E498EA6E-9CF6-4C38-B1F9-E9F4A6169CB0}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{402B7B64-F40D-498D-A609-742325044519}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7980,7 +7980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81136E9A-6C34-4A6B-83D5-2982B17F5CC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF3D8EAA-B2AE-4D9C-BE20-208F5BB74A1B}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8497,8 +8497,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CEE8E35F-45D9-45CC-A09A-ED108AB1132C}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DBAC367A-C1FC-4199-BF65-D16D2EADE92B}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E6DBD8FE-D7CC-4FB2-BA9D-6328B95A5B10}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{00AF9777-9D4B-4524-AD70-5DAA334A54EB}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8514,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86909117-6886-4072-AC65-DE46F8BC98BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988850E9-72B2-4364-85A9-BD09CADB86EB}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9063,8 +9063,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B0011691-29CF-4ED6-ABE8-F30B50564BF3}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{AFAE9920-BEDB-416A-B59E-03C6FF2EAE25}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{06FA7C63-4715-4BA2-AA9E-0E05C8C5BF6B}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{9862B406-6658-4245-833E-694712061D20}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9080,7 +9080,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F74272B-6CC8-43BE-86D0-02B451F60874}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172583E2-41DF-424C-A80A-F987B8999404}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9613,8 +9613,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{16C9FEF1-7EC6-4431-A8A6-389788466204}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2B2FE0F2-0D92-43AA-84D1-E105D92F43BB}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{61B345D9-1497-4D32-887E-1EF95CF43C38}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{29B3AE1F-13F1-4820-9CBA-8D8CA30E73B0}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9630,7 +9630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BBAA0D-1F1A-48CF-B032-12CF6A8730D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6CD453-F10B-43A8-A31B-6CB72698B65D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10163,8 +10163,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{04A824B1-39D5-42AC-98C6-2877E24BFA07}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{79969EE3-423C-4BBB-902A-BEBC6F9180C6}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B57C0C73-3B5A-4D69-A5B3-FE125D00A551}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{C124D0E2-EFCE-42CF-9586-1527BC586A65}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10180,7 +10180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01431B1-428E-4B81-B887-744B65ED8411}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9712E3FE-B2F6-4E6B-B158-AC2FDE6492D5}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10713,8 +10713,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{F88E0C04-43C8-4532-BE5F-07C34A860FEC}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{151082F3-9ACF-4B14-8810-6149E4DC58A3}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{D7876EA0-1F3E-435B-8535-149950BA6762}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D4C76800-8C55-48A3-8688-A927ECCEBE8F}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11210,7 +11210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD876F9-43CB-401A-B4FF-09D1078F95A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4A0EC1-A252-4872-BEFA-83586DA8B9D0}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -11743,8 +11743,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{6614050A-4FCB-416B-B66B-164C4F9B468A}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F54728EB-7F11-40D0-9C90-463A041527CB}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{15E932BC-4B3E-4F32-A1D1-59ED7D52365B}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{91CEAE32-7305-4C32-9FF8-D22B8F93F522}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11760,7 +11760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C40307-789D-4E69-807D-0A126C1F8F94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C3AC79-B84E-46E6-A01F-DCE8D5D0F3CE}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12293,8 +12293,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5F1EC91C-D286-454E-A339-FED29E5974C4}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{ECC1C914-FB75-4A54-8081-A05A1FCCDBE7}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1CDE9635-B4AD-485E-89D3-E5CA138792BB}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{13C6AF75-DD01-4FE8-912C-C07B82564397}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12310,7 +12310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A07663-F36F-466C-9FCE-493785EB4C88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16264B07-897F-45D0-99D3-203CE7057492}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12839,8 +12839,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B4A9FB70-3BB1-43D2-9C4C-031AD0B04A38}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{3E02C823-2B5C-426E-AE6E-D0F808082F22}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{C72A0513-06E4-4619-B425-BE563C6CEAED}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BECD9D40-91D0-41BA-83C9-EFC5C8F5373B}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12856,7 +12856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DA4739-4523-4767-84E0-67BB78E8B360}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DDA32C-7DB1-413F-8D85-1048754B6713}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15583,8 +15583,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{315F9E3A-6752-4986-9DE3-5A007D0322C7}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BA3F866F-FB8E-43CF-85FC-2AE3B4F4ECAE}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2148B239-66D3-4DFA-B18B-EA3103800452}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{6A234ECF-3238-451B-96BD-B56A5E2BBDB8}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15600,7 +15600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA79DEC3-4F16-4848-9D2E-DBE0F0261379}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0A1AB9E-B3F7-422D-A09A-EDDF15B91871}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -16149,8 +16149,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{41E55161-1FA5-4843-97F4-FC012A97D686}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E896A19D-D7DE-4785-88E2-054909A40A9D}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{D434F867-C3D7-476F-8E5E-CEB83E588BAF}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{4088698F-F2FF-456C-A16E-E3BF6E3EAF5E}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17030,7 +17030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EA52DB-D958-47E5-84E7-BF2A1AC2E650}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF3BECC-6591-4F99-912E-1ECC0F22D8B4}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17563,8 +17563,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3E113A9C-8DF6-4A90-877E-E7E30EE6B5AB}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{32B08A14-3B77-4AD6-963B-C32B2ADB7801}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{C54E14F7-D5D9-4533-804D-16DF9CC7D3A2}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FD07EFD9-7910-4B40-88E1-3A42487BCAD4}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17580,7 +17580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B7354B-348A-42BB-B953-876F74A6C734}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268B29FB-5749-4753-A0A0-7CAD1855E92C}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18129,8 +18129,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A5881556-B38F-48C8-9189-2C70ADE9AA3A}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D8232463-BDC4-4A5E-A52B-75D2F4E7EBB4}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2A38DCBA-F40C-4E11-AD24-C081EEF1D5FE}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0BE8EA35-3689-413E-8515-2AC688CA2414}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18146,7 +18146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F70B8DE-C3DF-4BB4-9253-EFD3F8EAA273}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FA166E-A8D7-474B-B237-EAF485B1776D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18695,8 +18695,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{881F5939-668C-4B18-8309-0DDA3085F40E}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{B49B3EB8-8682-4D70-87C9-EBA8319307CA}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{69488AF4-6EA2-4E4B-8FD2-B9752CA42B8E}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{102D5ABF-7302-4AB2-8E72-363D23A4D724}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18712,7 +18712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6E3706-AD40-4A99-9F9B-F5B78F5EDE9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F40EC4-885D-4AC1-81F3-95808F4D4D15}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19261,8 +19261,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{6815E8F3-AFB1-4571-80AC-D0116F83B2BB}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BF82F414-A6DE-49F7-B0AE-586062A2B522}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{12D364AF-0AB6-43BA-B18D-F5CDFC04AA44}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{B23E5F76-CF03-4F0E-9C4C-C34041120E3A}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19278,7 +19278,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1443F6AA-C17A-43FF-8897-6DF232EDB91F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7F7B4A-6301-4AFB-ACDF-F2BE9D45E8FD}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19795,8 +19795,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{DFABC16F-3B30-4D75-8FBD-67CB35B316C1}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8AF3B39B-9A8E-45B4-828E-1642E4A41058}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7A86D257-5679-463D-8D4D-44D6251F9136}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{67925E4C-F883-44D5-9062-0E44E39068F4}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19812,7 +19812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A7B07B-1746-4E9E-8DCA-6AA79DAA4D05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A03B5D-B526-4A84-B542-3E8BE842842E}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -20361,8 +20361,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{CC7612E3-F887-477B-B9EF-068B9DC56516}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E8C2B150-D2D7-41B2-890B-5533C20CB978}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0DB253B7-AF48-49A9-A29A-9602B42EFE3A}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{1E9021B3-D347-464B-8977-FC10F2739D5F}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
+++ b/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project\CampusStay FPT\docs\reports\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E745127-1C88-4850-A598-A51329DD8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48D0CDBE-A24D-4BBF-ABB7-31C55C989479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8964" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="9" r:id="rId1"/>
@@ -158,7 +158,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{5F7E4F7E-CCFE-4A0C-AF18-E563D21E82B6}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{189667BC-2595-48C4-9AD1-BDF52ADB2758}">
       <text>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{2DC197E9-C4DB-4299-8AD7-8FAE00D954DB}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{08C2A745-2D7D-4446-8D90-7912C14FF7DF}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{25D156D7-E603-4BA9-92D9-FE0670ED1D79}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{1500F5D2-3D77-4CDA-9CF9-89627F84E6B2}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FBF898B3-F204-4D94-96AF-81BFD8B86150}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8B9E9093-3881-4CC5-9CB0-A3BDC372FD8D}">
       <text>
         <r>
           <rPr>
@@ -250,7 +250,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FC764BC8-0DA0-4A99-A920-40825E74243D}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7921D5D2-E6D1-4074-8968-BEBBC1102AD0}">
       <text>
         <r>
           <rPr>
@@ -273,7 +273,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{5E2EB953-89E4-40C5-AA92-88996FCB2CD0}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A75DB742-DBBC-4E50-9633-0A9D3F37E152}">
       <text>
         <r>
           <rPr>
@@ -296,7 +296,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{01CFE886-1392-4D77-828F-3968CB4DBFBA}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F291DF54-A2B1-4E82-8BF1-9C616847E18A}">
       <text>
         <r>
           <rPr>
@@ -319,7 +319,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{9FCE023D-BEEE-4FAB-B6F5-9C88F45098A7}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CCD145D2-17EF-40E4-9FD4-B1F331C9C144}">
       <text>
         <r>
           <rPr>
@@ -342,7 +342,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8A3EF57E-80DA-4FF3-9243-23AB734AC27E}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{0E82DFEC-1DA9-41D9-8B8F-57919B3CC1C0}">
       <text>
         <r>
           <rPr>
@@ -365,7 +365,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CEE345FE-B461-4223-931F-08669C9F95BC}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{19C939B5-9826-4821-AB25-D5D9CF6BC714}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A6DA9FAE-D940-4F37-A9C5-30245B20D4C1}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8E09E732-F97C-457E-9E11-94C558D58C1B}">
       <text>
         <r>
           <rPr>
@@ -411,7 +411,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7D4657F8-2FA5-417B-BBB9-B7FD864E54B7}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8A9D1F32-07B0-4328-BE00-88CD772026F0}">
       <text>
         <r>
           <rPr>
@@ -434,7 +434,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{76BE6D56-E447-4CC4-8182-D4D3D50D497F}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{D7E4D51B-1402-4754-A140-E63835411E4E}">
       <text>
         <r>
           <rPr>
@@ -457,7 +457,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{20A46C1D-02C1-42EE-9E33-CEF0EA013BCD}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{75E6E526-792C-46D4-8E8C-DB8E25BA0E1C}">
       <text>
         <r>
           <rPr>
@@ -480,7 +480,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B9B4FAC3-4CBA-44AC-9B9C-37391CDDE958}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{3B9A6DE3-0DA1-4E01-8BBE-3E0A538CD086}">
       <text>
         <r>
           <rPr>
@@ -503,7 +503,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{770224C8-B8B6-40EC-8F5B-8BA4A0E1E61A}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{4AD458CC-DFE5-43EE-97CB-44EF3A375A99}">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{4071CAB7-F2A5-4F77-8B25-63DE364EE58E}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{0F67B725-BF3B-4557-9D45-0C3CFE1AB1B9}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F991CBD9-7D07-4E25-9ACB-DF0871EC15BA}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{2E2F7760-3782-4618-B248-403E6C2D7D3B}">
       <text>
         <r>
           <rPr>
@@ -572,7 +572,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F9569ECF-01FE-48F6-9BDB-C09D5105582F}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FD108C75-EC2B-4B20-A8C0-1A0A7537EB8C}">
       <text>
         <r>
           <rPr>
@@ -595,7 +595,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F63B14F5-9EEF-4CB3-9AD1-84A4250DE666}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CE2E8B1D-BFB9-4299-9309-6B1AF9BAE2D0}">
       <text>
         <r>
           <rPr>
@@ -618,7 +618,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FC3F62B4-2F02-474E-94A8-4F07B4A40FE2}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F210A92B-C0A5-4117-9B05-D8A90AAE0F58}">
       <text>
         <r>
           <rPr>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="819">
   <si>
     <t>Project Name</t>
   </si>
@@ -802,7 +802,7 @@
     <t>Võ Minh Luân</t>
   </si>
   <si>
-    <t>28/10/2026</t>
+    <t>30/10/2026</t>
   </si>
   <si>
     <t>1.0</t>
@@ -946,6 +946,18 @@
     <t>TC-F02-05</t>
   </si>
   <si>
+    <t>[Rule] A major is read from its code, its English label or its Vietnamese name, the other FPT majors are in the list (V61), and a student-code prefix such as SS put in the major column gets an error that says so; the file is the XLSX the template writer makes.</t>
+  </si>
+  <si>
+    <t>Automated (StudentImportIT.readsMajorsByCodeOrNameAndExplainsCodePrefixes): run the scenario and check the result</t>
+  </si>
+  <si>
+    <t>A major is read from its code, its English label or its Vietnamese name, the other FPT majors are in the list (V61), and a student-code prefix such as SS put in the major column gets an error that says so; the file is the XLSX the template writer makes.</t>
+  </si>
+  <si>
+    <t>TC-F02-06</t>
+  </si>
+  <si>
     <t>[Exception] Only a verified account may apply: a pending one sees why and is refused (ADR-26).</t>
   </si>
   <si>
@@ -1123,6 +1135,18 @@
     <t>TC-F05-02</t>
   </si>
   <si>
+    <t>[Main] A student reads and saves their refund account; the number keeps its digits only, each field is checked, and only students have one.</t>
+  </si>
+  <si>
+    <t>Automated (RefundAccountIT.studentKeepsTheirRefundAccount): GET /api/students/me/refund-account; PUT /api/students/me/refund-account; check the answer and the database</t>
+  </si>
+  <si>
+    <t>A student reads and saves their refund account; the number keeps its digits only, each field is checked, and only students have one.</t>
+  </si>
+  <si>
+    <t>TC-F05-03</t>
+  </si>
+  <si>
     <t>[Rule] A rejection needs a reason; the Invoice is Unpaid again and the deadline continues with the time that was left (at least payment.rejected_claim_min_hours); the student is told; a second rejection cancels the Deposit and the Application expires.</t>
   </si>
   <si>
@@ -1132,7 +1156,7 @@
     <t>A rejection needs a reason; the Invoice is Unpaid again and the deadline continues with the time that was left (at least payment.rejected_claim_min_hours); the student is told; a second rejection cancels the Deposit and the Application expires.</t>
   </si>
   <si>
-    <t>TC-F05-03</t>
+    <t>TC-F05-04</t>
   </si>
   <si>
     <t>[Exception] One claim at a time; a paid or void Invoice and a Deposit past its deadline cannot be claimed; a student cannot cancel while a claim waits; only Managers see the queue and decide; an empty selection is refused; Invoices without a claim are skipped.</t>
@@ -1144,13 +1168,13 @@
     <t>One claim at a time; a paid or void Invoice and a Deposit past its deadline cannot be claimed; a student cannot cancel while a claim waits; only Managers see the queue and decide; an empty selection is refused; Invoices without a claim are skipped.</t>
   </si>
   <si>
-    <t>F-06 Review and assignment</t>
-  </si>
-  <si>
-    <t>Review and assignment (FR-APP-05, FR-ASG-01..03); actors: Manager</t>
-  </si>
-  <si>
-    <t>FR-APP-05, FR-ASG-01..03</t>
+    <t>F-06 Review, assignment and Round 2</t>
+  </si>
+  <si>
+    <t>Review, assignment and Round 2 (FR-APP-05, 07, FR-ASG-01..03); actors: Manager, Student, System</t>
+  </si>
+  <si>
+    <t>FR-APP-05, 07, FR-ASG-01..03</t>
   </si>
   <si>
     <t>TC-F06-01</t>
@@ -1168,6 +1192,30 @@
     <t>TC-F06-02</t>
   </si>
   <si>
+    <t>[Main] A Manager runs Round 2 (M8): the Waitlisted students without an open offer get held options on the Term's free Beds, by the rules of the offers made when a Block is approved; students may not run it. The Manager's list shows who is waiting without an offer, then who got one with its options (A-58).</t>
+  </si>
+  <si>
+    <t>Automated (Round2IT.managerRunsRound2): GET /api/round2; POST /api/round2/run; GET /api/round2/offers; check the answer and the database</t>
+  </si>
+  <si>
+    <t>A Manager runs Round 2 (M8): the Waitlisted students without an open offer get held options on the Term's free Beds, by the rules of the offers made when a Block is approved; students may not run it. The Manager's list shows who is waiting without an offer, then who got one with its options (A-58).</t>
+  </si>
+  <si>
+    <t>TC-F06-03</t>
+  </si>
+  <si>
+    <t>[Main] A waitlisted student sees the open offer, the day the waitlist ends and the refund; withdrawing closes the offer, releases its Beds, cancels the Application and asks a Manager to refund the whole Deposit, whose list shows the student's bank account (A-61, A-62). A plain cancel is refused, and only one's own waitlisted Application can be withdrawn.</t>
+  </si>
+  <si>
+    <t>Automated (Round2IT.waitlistedStudentWithdraws): POST /api/applications/{id}/withdraw; PUT /api/students/me/refund-account; check the answer and the database</t>
+  </si>
+  <si>
+    <t>A waitlisted student sees the open offer, the day the waitlist ends and the refund; withdrawing closes the offer, releases its Beds, cancels the Application and asks a Manager to refund the whole Deposit, whose list shows the student's bank account (A-61, A-62). A plain cancel is refused, and only one's own waitlisted Application can be withdrawn.</t>
+  </si>
+  <si>
+    <t>TC-F06-04</t>
+  </si>
+  <si>
     <t>[Rule] The queue, the review view (opening it starts the review), rejection needs a note, once only.</t>
   </si>
   <si>
@@ -1177,7 +1225,7 @@
     <t>The queue, the review view (opening it starts the review), rejection needs a note, once only.</t>
   </si>
   <si>
-    <t>TC-F06-03</t>
+    <t>TC-F06-05</t>
   </si>
   <si>
     <t>[Rule] The priority group goes first; the same input gives the same proposal.</t>
@@ -1189,7 +1237,22 @@
     <t>The priority group goes first; the same input gives the same proposal.</t>
   </si>
   <si>
-    <t>TC-F06-04</t>
+    <t>TC-F06-06</t>
+  </si>
+  <si>
+    <t>[Rule] When the Term's check-in starts, a waitlisted Application without an open offer is cancelled with the whole Deposit to refund and the student is told; one with an open offer keeps it until it is answered.</t>
+  </si>
+  <si>
+    <t>Automated (Round2IT.waitlistEndsWhenCheckInStarts): run the scenario and check the result</t>
+  </si>
+  <si>
+    <t>When the Term's check-in starts, a waitlisted Application without an open offer is cancelled with the whole Deposit to refund and the student is told; one with an open offer keeps it until it is answered.</t>
+  </si>
+  <si>
+    <t>Test seed (2 Blocks, 48 students, 7 back-office users); System (job) signed in</t>
+  </si>
+  <si>
+    <t>TC-F06-07</t>
   </si>
   <si>
     <t>[Exception] A dry run is a preview; students and Staff cannot use runs (ADR-19).</t>
@@ -1201,7 +1264,7 @@
     <t>A dry run is a preview; students and Staff cannot use runs (ADR-19).</t>
   </si>
   <si>
-    <t>TC-F06-05</t>
+    <t>TC-F06-08</t>
   </si>
   <si>
     <t>[Exception] Every Manager sees every Block's Applications (ADR-19); Staff and students cannot review.</t>
@@ -1270,9 +1333,6 @@
     <t>A Balance past its deadline without a claim is forfeited: the Allocation is cancelled, the Balance void, the Application Forfeited, the Deposit kept by the rule "Balance not paid" (a 0 % rule records no refund; a 10 % rule one refund, never two) and the student told; a claim waiting keeps the Bed, and so does a later Balance deadline a Manager chose when approving a late check-in, which may not pass the arrival day (the Balance is paid before check-in).</t>
   </si>
   <si>
-    <t>Test seed (2 Blocks, 48 students, 7 back-office users); System (job) signed in</t>
-  </si>
-  <si>
     <t>TC-F07-05</t>
   </si>
   <si>
@@ -1321,6 +1381,18 @@
     <t>TC-F08-03</t>
   </si>
   <si>
+    <t>[Main] The desk enters the final meter readings Room by Room, typed or from the XLSX template, before the leavers come: each Room's reading goes to the check-out drafts of its leavers; a Room without leavers in the user's Blocks or a reading below the Room's last one is reported and not saved.</t>
+  </si>
+  <si>
+    <t>Automated (DeskIT.finalReadingsRoomByRoom): GET /api/check-out/readings; PUT /api/check-out/readings; GET /api/check-out/readings/template; check the answer and the database</t>
+  </si>
+  <si>
+    <t>The desk enters the final meter readings Room by Room, typed or from the XLSX template, before the leavers come: each Room's reading goes to the check-out drafts of its leavers; a Room without leavers in the user's Blocks or a reading below the Room's last one is reported and not saved.</t>
+  </si>
+  <si>
+    <t>TC-F08-04</t>
+  </si>
+  <si>
     <t>[Rule] Check-out records the damage of each furniture item of the Room (spec §6.16): the damage charge is their sum, a damaged item becomes Broken with the reason in its history, an item of another Room is refused; the list shows the Term's check-out date and whether a leaver is past it.</t>
   </si>
   <si>
@@ -1330,7 +1402,7 @@
     <t>Check-out records the damage of each furniture item of the Room (spec §6.16): the damage charge is their sum, a damaged item becomes Broken with the reason in its history, an item of another Room is refused; the list shows the Term's check-out date and whether a leaver is past it.</t>
   </si>
   <si>
-    <t>TC-F08-04</t>
+    <t>TC-F08-05</t>
   </si>
   <si>
     <t>[Exception] Another Block's Staff do not find the student, every Manager does (ADR-19); students and the Admin have no desk.</t>
@@ -1630,6 +1702,18 @@
     <t>TC-F13-03</t>
   </si>
   <si>
+    <t>[Main] A Staff member reads their own duty, request types and workload, and starts or ends their shift (A-60); the change is audited, and students may not use it.</t>
+  </si>
+  <si>
+    <t>Automated (BlockStaffIT.staffStartAndEndTheirShift): GET /api/block-staff/me; PUT /api/block-staff/me/duty; check the answer and the database</t>
+  </si>
+  <si>
+    <t>A Staff member reads their own duty, request types and workload, and starts or ends their shift (A-60); the change is audited, and students may not use it.</t>
+  </si>
+  <si>
+    <t>TC-F13-04</t>
+  </si>
+  <si>
     <t>[Rule] A new Maintenance Request gets its SLA deadline from the Block's timer (urgent sooner than normal) and may name a furniture item of the Room, which the queue and the detail show; the item's history keeps the repair, reported and resolved; an item of another Room is refused.</t>
   </si>
   <si>
@@ -1639,7 +1723,19 @@
     <t>A new Maintenance Request gets its SLA deadline from the Block's timer (urgent sooner than normal) and may name a furniture item of the Room, which the queue and the detail show; the item's history keeps the repair, reported and resolved; an item of another Room is refused.</t>
   </si>
   <si>
-    <t>TC-F13-04</t>
+    <t>TC-F13-05</t>
+  </si>
+  <si>
+    <t>[Rule] Only the person in charge changes the status; another Staff member of the Block takes the request over first (recorded in its history), and a Manager may act on any request.</t>
+  </si>
+  <si>
+    <t>Automated (MaintenanceIT.personInChargeChangesTheStatus): PATCH /api/maintenance-requests/{id}; check the answer and the database</t>
+  </si>
+  <si>
+    <t>Only the person in charge changes the status; another Staff member of the Block takes the request over first (recorded in its history), and a Manager may act on any request.</t>
+  </si>
+  <si>
+    <t>TC-F13-06</t>
   </si>
   <si>
     <t>[Rule] An unassigned request escalates, then passes its timer; the Manager reassigns it once.</t>
@@ -1651,7 +1747,7 @@
     <t>An unassigned request escalates, then passes its timer; the Manager reassigns it once.</t>
   </si>
   <si>
-    <t>TC-F13-05</t>
+    <t>TC-F13-07</t>
   </si>
   <si>
     <t>[Exception] The queue is scoped: another Block's Staff neither see nor count the request; Managers do (ADR-19).</t>
@@ -2251,6 +2347,18 @@
     <t>TC-ST-18</t>
   </si>
   <si>
+    <t>Automated (Round2IT.waitlistedStudentWithdraws): Student withdraws from the waitlist (whole Deposit refunded)</t>
+  </si>
+  <si>
+    <t>TC-ST-19</t>
+  </si>
+  <si>
+    <t>Automated (Round2IT.waitlistEndsWhenCheckInStarts): Check-in starts with no open offer (waitlist ends, Deposit refunded)</t>
+  </si>
+  <si>
+    <t>TC-ST-20</t>
+  </si>
+  <si>
     <t>Application: Allocated -&gt; Forfeited (FR-ASG-11)</t>
   </si>
   <si>
@@ -2263,7 +2371,7 @@
     <t>Entity in state Allocated</t>
   </si>
   <si>
-    <t>TC-ST-19</t>
+    <t>TC-ST-21</t>
   </si>
   <si>
     <t>Application: Allocated -&gt; Rejected (FR-AUTH-08)</t>
@@ -2272,7 +2380,7 @@
     <t>Manual on staging: Not enrolled before moving in</t>
   </si>
   <si>
-    <t>TC-ST-20</t>
+    <t>TC-ST-22</t>
   </si>
   <si>
     <t>Allocation: (new) -&gt; Assigned – unpaid (FR-ASG-03)</t>
@@ -2284,7 +2392,7 @@
     <t>Status is Assigned – unpaid</t>
   </si>
   <si>
-    <t>TC-ST-21</t>
+    <t>TC-ST-23</t>
   </si>
   <si>
     <t>Allocation: Assigned – unpaid -&gt; Paid – waiting for the code (FR-BIL-03)</t>
@@ -2299,7 +2407,7 @@
     <t>Entity in state Assigned – unpaid</t>
   </si>
   <si>
-    <t>TC-ST-22</t>
+    <t>TC-ST-24</t>
   </si>
   <si>
     <t>Allocation: Assigned – unpaid -&gt; Cancelled (FR-ASG-11)</t>
@@ -2308,7 +2416,7 @@
     <t>Automated (ResidenceIT.unpaidBalanceIsForfeited): Balance past its deadline (forfeit)</t>
   </si>
   <si>
-    <t>TC-ST-23</t>
+    <t>TC-ST-25</t>
   </si>
   <si>
     <t>Allocation: Assigned – unpaid -&gt; Cancelled (FR-BIL-03)</t>
@@ -2317,7 +2425,7 @@
     <t>Automated (ResidenceIT.rejectedClaimsCancelTheBalance): Balance claim rejected twice</t>
   </si>
   <si>
-    <t>TC-ST-24</t>
+    <t>TC-ST-26</t>
   </si>
   <si>
     <t>Allocation: Paid – waiting for the code -&gt; Cancelled (FR-AUTH-08)</t>
@@ -2326,7 +2434,7 @@
     <t>Entity in state Paid – waiting for the code</t>
   </si>
   <si>
-    <t>TC-ST-25</t>
+    <t>TC-ST-27</t>
   </si>
   <si>
     <t>Allocation: Paid – waiting for the code -&gt; Resident (FR-ASG-04)</t>
@@ -2338,13 +2446,13 @@
     <t>Status becomes Resident</t>
   </si>
   <si>
-    <t>TC-ST-26</t>
+    <t>TC-ST-28</t>
   </si>
   <si>
     <t>Automated (DeskIT.checkInNeedsBalanceAndUtilityDeposit): Checked in at the desk</t>
   </si>
   <si>
-    <t>TC-ST-27</t>
+    <t>TC-ST-29</t>
   </si>
   <si>
     <t>Allocation: Resident -&gt; Ended (FR-ASG-06)</t>
@@ -2359,7 +2467,7 @@
     <t>Entity in state Resident</t>
   </si>
   <si>
-    <t>TC-ST-28</t>
+    <t>TC-ST-30</t>
   </si>
   <si>
     <t>Allocation: Resident -&gt; Ended (FR-ASG-10)</t>
@@ -2368,13 +2476,13 @@
     <t>Automated (OperationalMoveIT.staffMoveAResident): Moved to another Bed</t>
   </si>
   <si>
-    <t>TC-ST-29</t>
+    <t>TC-ST-31</t>
   </si>
   <si>
     <t>Automated (RenewalIT.turnover): The next Term starts for a continuing resident</t>
   </si>
   <si>
-    <t>TC-ST-30</t>
+    <t>TC-ST-32</t>
   </si>
   <si>
     <t>Next-Term Allocation: (new) -&gt; Continuing (FR-ASG-07)</t>
@@ -2386,7 +2494,7 @@
     <t>Status is Continuing</t>
   </si>
   <si>
-    <t>TC-ST-31</t>
+    <t>TC-ST-33</t>
   </si>
   <si>
     <t>Next-Term Allocation: (new) -&gt; Awaiting extension (FR-ASG-07)</t>
@@ -2398,7 +2506,7 @@
     <t>Status is Awaiting extension</t>
   </si>
   <si>
-    <t>TC-ST-32</t>
+    <t>TC-ST-34</t>
   </si>
   <si>
     <t>Next-Term Allocation: Awaiting extension -&gt; Continuing (FR-REQ-04)</t>
@@ -2413,7 +2521,7 @@
     <t>Entity in state Awaiting extension</t>
   </si>
   <si>
-    <t>TC-ST-33</t>
+    <t>TC-ST-35</t>
   </si>
   <si>
     <t>Next-Term Allocation: Awaiting extension -&gt; Cancelled (FR-ASG-07)</t>
@@ -2422,7 +2530,7 @@
     <t>Automated (RenewalIT.notExtendedAtTheDeadline): Not extended by M3</t>
   </si>
   <si>
-    <t>TC-ST-34</t>
+    <t>TC-ST-36</t>
   </si>
   <si>
     <t>Next-Term Allocation: Continuing -&gt; Continuing (other Bed) (FR-REQ-01, 02)</t>
@@ -2437,7 +2545,7 @@
     <t>Entity in state Continuing</t>
   </si>
   <si>
-    <t>TC-ST-35</t>
+    <t>TC-ST-37</t>
   </si>
   <si>
     <t>Next-Term Allocation: Continuing -&gt; Cancelled (FR-REQ-04, FR-AUTH-08)</t>
@@ -2446,7 +2554,7 @@
     <t>Automated (ReconciliationIT.resolveItems): End of stay or not enrolled</t>
   </si>
   <si>
-    <t>TC-ST-36</t>
+    <t>TC-ST-38</t>
   </si>
   <si>
     <t>Next-Term Allocation: Continuing -&gt; Cancelled (FR-ASG-08)</t>
@@ -2455,7 +2563,7 @@
     <t>Automated (RenewalIT.unpaidFeesReleaseTheBed): Next-Term fee unpaid at M7</t>
   </si>
   <si>
-    <t>TC-ST-37</t>
+    <t>TC-ST-39</t>
   </si>
   <si>
     <t>Next-Term Allocation: Continuing -&gt; Resident (FR-ASG-08)</t>
@@ -2464,7 +2572,7 @@
     <t>Automated (RenewalIT.turnover): Fee paid and the new Term starts</t>
   </si>
   <si>
-    <t>TC-ST-38</t>
+    <t>TC-ST-40</t>
   </si>
   <si>
     <t>Invoice: (new) -&gt; Unpaid (FR-APP-02, FR-BIL-04)</t>
@@ -2476,7 +2584,7 @@
     <t>Status is Unpaid</t>
   </si>
   <si>
-    <t>TC-ST-39</t>
+    <t>TC-ST-41</t>
   </si>
   <si>
     <t>Invoice: Unpaid -&gt; Awaiting confirmation (FR-BIL-02)</t>
@@ -2491,7 +2599,7 @@
     <t>Entity in state Unpaid</t>
   </si>
   <si>
-    <t>TC-ST-40</t>
+    <t>TC-ST-42</t>
   </si>
   <si>
     <t>Invoice: Overdue -&gt; Awaiting confirmation (FR-BIL-02)</t>
@@ -2503,7 +2611,7 @@
     <t>Entity in state Overdue</t>
   </si>
   <si>
-    <t>TC-ST-41</t>
+    <t>TC-ST-43</t>
   </si>
   <si>
     <t>Invoice: Awaiting confirmation -&gt; Paid (FR-BIL-03)</t>
@@ -2518,7 +2626,7 @@
     <t>Entity in state Awaiting confirmation</t>
   </si>
   <si>
-    <t>TC-ST-42</t>
+    <t>TC-ST-44</t>
   </si>
   <si>
     <t>Invoice: Unpaid -&gt; Paid (FR-BIL-03)</t>
@@ -2527,7 +2635,7 @@
     <t>Automated (PaymentDeskIT.manualConfirmation): Manager confirms a transfer the student did not claim</t>
   </si>
   <si>
-    <t>TC-ST-43</t>
+    <t>TC-ST-45</t>
   </si>
   <si>
     <t>Invoice: Overdue -&gt; Paid (FR-BIL-03)</t>
@@ -2536,7 +2644,7 @@
     <t>Manual on staging: Manager confirms an overdue debt the student did not claim</t>
   </si>
   <si>
-    <t>TC-ST-44</t>
+    <t>TC-ST-46</t>
   </si>
   <si>
     <t>Invoice: Awaiting confirmation -&gt; Unpaid (FR-BIL-03)</t>
@@ -2548,7 +2656,7 @@
     <t>Status becomes Unpaid</t>
   </si>
   <si>
-    <t>TC-ST-45</t>
+    <t>TC-ST-47</t>
   </si>
   <si>
     <t>Invoice: Awaiting confirmation -&gt; Overdue (FR-BIL-03)</t>
@@ -2560,7 +2668,7 @@
     <t>Status becomes Overdue</t>
   </si>
   <si>
-    <t>TC-ST-46</t>
+    <t>TC-ST-48</t>
   </si>
   <si>
     <t>Invoice: Awaiting confirmation -&gt; Void (FR-BIL-03)</t>
@@ -2572,7 +2680,7 @@
     <t>Status becomes Void</t>
   </si>
   <si>
-    <t>TC-ST-47</t>
+    <t>TC-ST-49</t>
   </si>
   <si>
     <t>Invoice: Unpaid -&gt; Overdue (FR-BIL-05)</t>
@@ -2581,7 +2689,7 @@
     <t>Automated (FinanceIT.overdueAndReminders): Due date passes (Utility, charges)</t>
   </si>
   <si>
-    <t>TC-ST-48</t>
+    <t>TC-ST-50</t>
   </si>
   <si>
     <t>Invoice: Unpaid -&gt; Void (FR-ASG-11, FR-APP-04)</t>
@@ -2590,7 +2698,7 @@
     <t>Automated (ApplicationsIT.cancellationVoidsOrRefunds): Forfeit or cancelled Application</t>
   </si>
   <si>
-    <t>TC-ST-49</t>
+    <t>TC-ST-51</t>
   </si>
   <si>
     <t>Invoice: Overdue -&gt; Void (FR-ASG-06)</t>
@@ -2599,7 +2707,7 @@
     <t>Manual on staging: Overdue Utility settled from the Utility Deposit at check-out</t>
   </si>
   <si>
-    <t>TC-ST-50</t>
+    <t>TC-ST-52</t>
   </si>
   <si>
     <t>Payment claim: (new) -&gt; Claimed (FR-BIL-02)</t>
@@ -2611,7 +2719,7 @@
     <t>Status is Claimed</t>
   </si>
   <si>
-    <t>TC-ST-51</t>
+    <t>TC-ST-53</t>
   </si>
   <si>
     <t>Payment claim: Claimed -&gt; Confirmed (FR-BIL-03)</t>
@@ -2626,7 +2734,7 @@
     <t>Entity in state Claimed</t>
   </si>
   <si>
-    <t>TC-ST-52</t>
+    <t>TC-ST-54</t>
   </si>
   <si>
     <t>Payment claim: (new) -&gt; Confirmed (FR-BIL-03)</t>
@@ -2638,7 +2746,7 @@
     <t>Status is Confirmed</t>
   </si>
   <si>
-    <t>TC-ST-53</t>
+    <t>TC-ST-55</t>
   </si>
   <si>
     <t>Payment claim: Claimed -&gt; Rejected (FR-BIL-03)</t>
@@ -2647,7 +2755,7 @@
     <t>Automated (PaymentClaimIT.rejectionsGiveTimeBackThenCancel): Manager rejects with a reason</t>
   </si>
   <si>
-    <t>TC-ST-54</t>
+    <t>TC-ST-56</t>
   </si>
   <si>
     <t>Maintenance Request: (new) -&gt; Submitted (FR-MNT-01)</t>
@@ -2659,7 +2767,7 @@
     <t>Status is Submitted</t>
   </si>
   <si>
-    <t>TC-ST-55</t>
+    <t>TC-ST-57</t>
   </si>
   <si>
     <t>Maintenance Request: Submitted -&gt; Assigned (FR-REQ-06)</t>
@@ -2671,7 +2779,7 @@
     <t>Status becomes Assigned</t>
   </si>
   <si>
-    <t>TC-ST-56</t>
+    <t>TC-ST-58</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; Submitted (FR-MNT-02)</t>
@@ -2683,7 +2791,7 @@
     <t>Entity in state Assigned</t>
   </si>
   <si>
-    <t>TC-ST-57</t>
+    <t>TC-ST-59</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; In Progress (FR-MNT-02)</t>
@@ -2695,7 +2803,7 @@
     <t>Status becomes In Progress</t>
   </si>
   <si>
-    <t>TC-ST-58</t>
+    <t>TC-ST-60</t>
   </si>
   <si>
     <t>Maintenance Request: In Progress -&gt; Resolved (FR-MNT-02)</t>
@@ -2710,7 +2818,7 @@
     <t>Entity in state In Progress</t>
   </si>
   <si>
-    <t>TC-ST-59</t>
+    <t>TC-ST-61</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; Resolved (FR-MNT-02)</t>
@@ -2719,7 +2827,7 @@
     <t>Manual on staging: Staff fixes it without starting it first</t>
   </si>
   <si>
-    <t>TC-ST-60</t>
+    <t>TC-ST-62</t>
   </si>
   <si>
     <t>Maintenance Request: Resolved -&gt; Closed (FR-MNT-02)</t>
@@ -2734,7 +2842,7 @@
     <t>Entity in state Resolved</t>
   </si>
   <si>
-    <t>TC-ST-61</t>
+    <t>TC-ST-63</t>
   </si>
   <si>
     <t>Maintenance Request: Resolved -&gt; Assigned (FR-MNT-02)</t>
@@ -2743,7 +2851,7 @@
     <t>Automated (MaintenanceIT.staffWorkTheRequest): Reporter reopens (once)</t>
   </si>
   <si>
-    <t>TC-ST-62</t>
+    <t>TC-ST-64</t>
   </si>
   <si>
     <t>Maintenance Request: Submitted -&gt; Closed (FR-MNT-02)</t>
@@ -2752,7 +2860,7 @@
     <t>Manual on staging: Staff closes a duplicate</t>
   </si>
   <si>
-    <t>TC-ST-63</t>
+    <t>TC-ST-65</t>
   </si>
   <si>
     <t>Maintenance Request: Assigned -&gt; Closed (FR-MNT-02)</t>
@@ -2761,13 +2869,13 @@
     <t>Manual on staging: Staff closes it</t>
   </si>
   <si>
-    <t>TC-ST-64</t>
+    <t>TC-ST-66</t>
   </si>
   <si>
     <t>Maintenance Request: In Progress -&gt; Closed (FR-MNT-02)</t>
   </si>
   <si>
-    <t>TC-ST-65</t>
+    <t>TC-ST-67</t>
   </si>
   <si>
     <t>Invoice: Paid / Void -&gt; (refused) (FR-BIL-02)</t>
@@ -2782,7 +2890,7 @@
     <t>Entity in state Paid / Void</t>
   </si>
   <si>
-    <t>TC-ST-66</t>
+    <t>TC-ST-68</t>
   </si>
   <si>
     <t>Invoice: Void -&gt; (refused) (FR-BIL-03)</t>
@@ -2794,7 +2902,7 @@
     <t>Entity in state Void</t>
   </si>
   <si>
-    <t>TC-ST-67</t>
+    <t>TC-ST-69</t>
   </si>
   <si>
     <t>Invoice: Paid -&gt; (refused) (FR-BIL-03)</t>
@@ -2806,7 +2914,7 @@
     <t>Entity in state Paid</t>
   </si>
   <si>
-    <t>TC-ST-68</t>
+    <t>TC-ST-70</t>
   </si>
   <si>
     <t>Next-Term Allocation: Continuing (fees issued) -&gt; (refused) (FR-ASG-10)</t>
@@ -5166,7 +5274,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65486304-7A84-409D-A1C7-F4BF060B43F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A9C8723-1445-435F-A85A-3ECC11C77B7C}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5200,7 +5308,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -5226,7 +5334,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -5466,7 +5574,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -5486,16 +5594,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>66</v>
@@ -5520,19 +5628,19 @@
     </row>
     <row r="13" spans="1:18" ht="92.4" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -5554,16 +5662,16 @@
     </row>
     <row r="14" spans="1:18" ht="92.4" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>66</v>
@@ -5588,19 +5696,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -5622,19 +5730,19 @@
     </row>
     <row r="16" spans="1:18" ht="92.4" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -5715,8 +5823,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1F7081CD-14C9-4886-B2EA-B836072D7519}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{4762034D-20C5-4461-903A-DB076A9542DF}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{4AF124D5-864E-4F77-A925-19C1B2C8BEC9}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{C909F16E-32F0-4404-8D93-2F5B7EC6B05E}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5732,7 +5840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82EFA14-BCFC-40DB-8EE4-34E609012C22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5AF1FB3-A191-4918-A704-CE0E9D3595D7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5766,7 +5874,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -5792,7 +5900,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -5819,7 +5927,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -5878,7 +5986,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -6032,7 +6140,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -6052,19 +6160,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -6086,19 +6194,19 @@
     </row>
     <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -6120,19 +6228,19 @@
     </row>
     <row r="14" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -6154,19 +6262,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -6186,15 +6294,31 @@
       <c r="O15" s="36"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="1:18" outlineLevel="1">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
+    <row r="16" spans="1:18" ht="79.2" outlineLevel="1">
+      <c r="A16" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I16" s="38"/>
       <c r="J16" s="38"/>
       <c r="K16" s="38"/>
@@ -6265,8 +6389,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{22B5695C-4312-4A0C-AAF3-737929356982}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{EF9B102A-1747-4009-AF65-CC4F739E6844}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{19EE30C2-368C-4146-8D9A-5B6FD73529DE}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{CB17540F-BE3A-4F87-AD63-3CD18B551798}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6282,7 +6406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8624025C-9582-40CA-B403-ABCA646C8117}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E6F362-E093-4986-A8B5-4AF74F234D70}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6316,7 +6440,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -6342,7 +6466,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -6582,7 +6706,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -6602,16 +6726,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>66</v>
@@ -6636,19 +6760,19 @@
     </row>
     <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -6670,16 +6794,16 @@
     </row>
     <row r="14" spans="1:18" ht="66" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>91</v>
@@ -6799,8 +6923,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7C9E8767-2601-4476-BF1B-9F491D7E59E4}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D2D83D38-C9FB-4A54-B904-1942095CFBF4}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3D1CC096-7A45-4BE6-89B0-B3E0A1031AA2}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DAA99E4B-5214-4217-9C25-56CDF6827116}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6816,7 +6940,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B7FC08-25EC-44BA-AFD7-15B9ED858F6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADB2BB8-A69A-4EC7-A71A-C9D8EEDF6AD0}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6850,7 +6974,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -6876,7 +7000,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -7116,7 +7240,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -7136,19 +7260,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -7170,16 +7294,16 @@
     </row>
     <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="E13" s="44" t="s">
         <v>66</v>
@@ -7204,19 +7328,19 @@
     </row>
     <row r="14" spans="1:18" ht="118.8" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -7238,16 +7362,16 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="E15" s="148" t="s">
         <v>66</v>
@@ -7272,16 +7396,16 @@
     </row>
     <row r="16" spans="1:18" ht="118.8" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="E16" s="38" t="s">
         <v>66</v>
@@ -7306,19 +7430,19 @@
     </row>
     <row r="17" spans="1:17" ht="66" outlineLevel="1">
       <c r="A17" s="38" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>38</v>
@@ -7381,8 +7505,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{DE4FEA56-B968-4B20-9D37-779F8B9E6DA2}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{7CA51216-6222-48BC-A2A4-3B379F769BEA}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{9FE352B1-A389-4922-96B5-3D6313BCA7C7}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E3829186-7F52-4951-8921-3D8FC0D023AE}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7398,7 +7522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{591A2B2C-9BC5-4615-8B30-0CCFF0FD00FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37707201-657C-410F-8786-A545A885DFD7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7432,7 +7556,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -7458,7 +7582,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -7698,7 +7822,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -7718,19 +7842,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -7752,19 +7876,19 @@
     </row>
     <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -7786,16 +7910,16 @@
     </row>
     <row r="14" spans="1:18" ht="145.19999999999999" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>91</v>
@@ -7820,16 +7944,16 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="E15" s="148" t="s">
         <v>91</v>
@@ -7854,16 +7978,16 @@
     </row>
     <row r="16" spans="1:18" ht="171.6" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="E16" s="38" t="s">
         <v>91</v>
@@ -7888,19 +8012,19 @@
     </row>
     <row r="17" spans="1:17" ht="66" outlineLevel="1">
       <c r="A17" s="38" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>38</v>
@@ -7963,8 +8087,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E498EA6E-9CF6-4C38-B1F9-E9F4A6169CB0}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{402B7B64-F40D-498D-A609-742325044519}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A31C3F60-7714-44DF-AB4F-210952FDEA37}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{5959A374-349A-45F4-90BF-F28FF538CBFE}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7980,7 +8104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF3D8EAA-B2AE-4D9C-BE20-208F5BB74A1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E877A6E9-31DF-4D02-BDA8-3DB1099E209A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8014,7 +8138,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -8040,7 +8164,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -8280,7 +8404,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -8300,19 +8424,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -8334,19 +8458,19 @@
     </row>
     <row r="13" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -8368,19 +8492,19 @@
     </row>
     <row r="14" spans="1:18" ht="92.4" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -8497,8 +8621,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E6DBD8FE-D7CC-4FB2-BA9D-6328B95A5B10}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{00AF9777-9D4B-4524-AD70-5DAA334A54EB}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{785E06C0-0EFA-4384-B195-2C0068779A4F}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{1CA536BF-A70A-4430-B52C-097F7F1D7267}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8514,7 +8638,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988850E9-72B2-4364-85A9-BD09CADB86EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965E21D4-BAC1-4875-A35A-C54DBC92A502}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8548,7 +8672,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -8574,7 +8698,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -8601,7 +8725,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -8660,7 +8784,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -8814,7 +8938,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -8834,16 +8958,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>66</v>
@@ -8868,19 +8992,19 @@
     </row>
     <row r="13" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -8900,21 +9024,21 @@
       <c r="O13" s="41"/>
       <c r="Q13" s="42"/>
     </row>
-    <row r="14" spans="1:18" ht="105.6" outlineLevel="1">
+    <row r="14" spans="1:18" ht="66" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -8936,19 +9060,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -8968,21 +9092,21 @@
       <c r="O15" s="36"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="1:18" ht="52.8" outlineLevel="1">
+    <row r="16" spans="1:18" ht="66" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -9002,15 +9126,31 @@
       <c r="O16" s="41"/>
       <c r="Q16" s="42"/>
     </row>
-    <row r="17" spans="1:17" outlineLevel="1">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
+    <row r="17" spans="1:17" ht="66" outlineLevel="1">
+      <c r="A17" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>367</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="149" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="149" t="s">
+        <v>67</v>
+      </c>
       <c r="I17" s="38"/>
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
@@ -9021,14 +9161,30 @@
       <c r="Q17" s="47"/>
     </row>
     <row r="18" spans="1:17" s="28" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
+      <c r="A18" s="146" t="s">
+        <v>368</v>
+      </c>
+      <c r="B18" s="147" t="s">
+        <v>369</v>
+      </c>
+      <c r="C18" s="148" t="s">
+        <v>370</v>
+      </c>
+      <c r="D18" s="148" t="s">
+        <v>371</v>
+      </c>
+      <c r="E18" s="148" t="s">
+        <v>155</v>
+      </c>
+      <c r="F18" s="148" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="148" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="148" t="s">
+        <v>67</v>
+      </c>
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
       <c r="K18" s="35"/>
@@ -9063,8 +9219,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{06FA7C63-4715-4BA2-AA9E-0E05C8C5BF6B}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{9862B406-6658-4245-833E-694712061D20}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3FD8834C-05D2-4F2F-BDCF-DEA719B80912}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{A0076A54-1173-4862-B13B-FCAB82324E01}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9080,7 +9236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172583E2-41DF-424C-A80A-F987B8999404}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4287F-1215-4788-972E-E98C413A1AD0}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9114,7 +9270,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -9140,7 +9296,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -9380,7 +9536,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -9400,19 +9556,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -9434,19 +9590,19 @@
     </row>
     <row r="13" spans="1:18" ht="66" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -9468,19 +9624,19 @@
     </row>
     <row r="14" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -9502,19 +9658,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -9613,8 +9769,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{61B345D9-1497-4D32-887E-1EF95CF43C38}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{29B3AE1F-13F1-4820-9CBA-8D8CA30E73B0}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{667FC44C-6955-4FF9-9C43-FA7B0E74A47F}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F7B399FA-30F3-463C-8FE1-49CE4CFA40FC}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9630,7 +9786,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6CD453-F10B-43A8-A31B-6CB72698B65D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6406964-E510-427D-85ED-DFBF473204D3}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9664,7 +9820,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -9690,7 +9846,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -9930,7 +10086,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -9950,19 +10106,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -9984,16 +10140,16 @@
     </row>
     <row r="13" spans="1:18" ht="118.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="E13" s="44" t="s">
         <v>91</v>
@@ -10018,19 +10174,19 @@
     </row>
     <row r="14" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -10052,19 +10208,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -10163,8 +10319,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B57C0C73-3B5A-4D69-A5B3-FE125D00A551}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{C124D0E2-EFCE-42CF-9586-1527BC586A65}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{07E41508-994D-44D4-B1E5-8F6674A27B94}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{003F4564-CBF7-411C-A9B2-1219082BC898}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10180,7 +10336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9712E3FE-B2F6-4E6B-B158-AC2FDE6492D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECD826F-0849-43A4-859D-225BE2DF98DC}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10214,7 +10370,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -10240,7 +10396,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -10480,7 +10636,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -10500,16 +10656,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>91</v>
@@ -10534,19 +10690,19 @@
     </row>
     <row r="13" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -10568,16 +10724,16 @@
     </row>
     <row r="14" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>91</v>
@@ -10602,16 +10758,16 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="E15" s="148" t="s">
         <v>66</v>
@@ -10713,8 +10869,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{D7876EA0-1F3E-435B-8535-149950BA6762}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{D4C76800-8C55-48A3-8688-A927ECCEBE8F}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{08C20DB5-E34E-4B89-97C6-4D3B5A559F40}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{023BADDE-D0FD-4206-8CD8-A31C0FC1BAAE}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10829,7 +10985,7 @@
         <v>59</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>757</v>
+        <v>793</v>
       </c>
       <c r="D9" s="97" t="s">
         <v>60</v>
@@ -10847,7 +11003,7 @@
         <v>80</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>758</v>
+        <v>794</v>
       </c>
       <c r="D10" s="97" t="s">
         <v>81</v>
@@ -10862,13 +11018,13 @@
         <v>3</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="D11" s="97" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>91</v>
@@ -10880,13 +11036,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>760</v>
+        <v>796</v>
       </c>
       <c r="D12" s="97" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>66</v>
@@ -10898,13 +11054,13 @@
         <v>5</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>761</v>
+        <v>797</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>66</v>
@@ -10916,13 +11072,13 @@
         <v>6</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>762</v>
+        <v>798</v>
       </c>
       <c r="D14" s="97" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E14" s="22" t="s">
         <v>91</v>
@@ -10934,13 +11090,13 @@
         <v>7</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="D15" s="97" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>66</v>
@@ -10952,16 +11108,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>764</v>
+        <v>800</v>
       </c>
       <c r="D16" s="97" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F16" s="23"/>
     </row>
@@ -10970,13 +11126,13 @@
         <v>9</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>765</v>
+        <v>801</v>
       </c>
       <c r="D17" s="97" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="E17" s="22" t="s">
         <v>66</v>
@@ -10988,16 +11144,16 @@
         <v>10</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>766</v>
+        <v>802</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F18" s="23"/>
     </row>
@@ -11006,16 +11162,16 @@
         <v>11</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>767</v>
+        <v>803</v>
       </c>
       <c r="D19" s="97" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F19" s="23"/>
     </row>
@@ -11024,16 +11180,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>768</v>
+        <v>804</v>
       </c>
       <c r="D20" s="97" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F20" s="23"/>
     </row>
@@ -11042,13 +11198,13 @@
         <v>13</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>769</v>
+        <v>805</v>
       </c>
       <c r="D21" s="97" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="E21" s="22" t="s">
         <v>66</v>
@@ -11060,16 +11216,16 @@
         <v>14</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>770</v>
+        <v>806</v>
       </c>
       <c r="D22" s="97" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -11077,16 +11233,16 @@
         <v>15</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>771</v>
+        <v>807</v>
       </c>
       <c r="D23" s="97" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -11094,13 +11250,13 @@
         <v>16</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>772</v>
+        <v>808</v>
       </c>
       <c r="D24" s="97" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>91</v>
@@ -11111,16 +11267,16 @@
         <v>17</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>773</v>
+        <v>809</v>
       </c>
       <c r="D25" s="97" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -11128,13 +11284,13 @@
         <v>18</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>774</v>
+        <v>810</v>
       </c>
       <c r="D26" s="97" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="E26" s="22" t="s">
         <v>91</v>
@@ -11145,16 +11301,16 @@
         <v>19</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>775</v>
+        <v>811</v>
       </c>
       <c r="D27" s="97" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>776</v>
+        <v>812</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -11162,16 +11318,16 @@
         <v>20</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>777</v>
+        <v>813</v>
       </c>
       <c r="D28" s="97" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>778</v>
+        <v>814</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -11179,16 +11335,16 @@
         <v>21</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>725</v>
+        <v>761</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>779</v>
+        <v>815</v>
       </c>
       <c r="D29" s="97" t="s">
-        <v>726</v>
+        <v>762</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>780</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>
@@ -11210,7 +11366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4A0EC1-A252-4872-BEFA-83586DA8B9D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AF5A54-EA16-471B-8DA2-86BB2BC9234C}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -11244,7 +11400,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -11270,7 +11426,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -11510,7 +11666,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -11530,19 +11686,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -11564,19 +11720,19 @@
     </row>
     <row r="13" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -11598,19 +11754,19 @@
     </row>
     <row r="14" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -11632,16 +11788,16 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="E15" s="148" t="s">
         <v>66</v>
@@ -11743,8 +11899,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{15E932BC-4B3E-4F32-A1D1-59ED7D52365B}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{91CEAE32-7305-4C32-9FF8-D22B8F93F522}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{D7859F83-EF3E-4ED7-8F3B-44BBA6DAC522}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2C823100-0D47-4982-9F27-D5536141AC22}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11760,7 +11916,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C3AC79-B84E-46E6-A01F-DCE8D5D0F3CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F702F0A7-65EA-4627-AF1B-1068D706E7D2}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -11794,7 +11950,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -11820,7 +11976,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -12060,7 +12216,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -12080,16 +12236,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>91</v>
@@ -12114,16 +12270,16 @@
     </row>
     <row r="13" spans="1:18" ht="92.4" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="E13" s="44" t="s">
         <v>91</v>
@@ -12148,16 +12304,16 @@
     </row>
     <row r="14" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>91</v>
@@ -12182,19 +12338,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -12293,8 +12449,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1CDE9635-B4AD-485E-89D3-E5CA138792BB}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{13C6AF75-DD01-4FE8-912C-C07B82564397}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{8BE3E15A-0146-44B2-9E75-41CCD5AD3C53}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{54667F08-803D-40C9-A144-4707B28C5F18}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12310,7 +12466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16264B07-897F-45D0-99D3-203CE7057492}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0C1982-93FC-420E-AD21-9DA398C1E014}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12344,7 +12500,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -12370,7 +12526,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -12610,7 +12766,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -12630,19 +12786,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>37</v>
@@ -12660,19 +12816,19 @@
     </row>
     <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>37</v>
@@ -12690,19 +12846,19 @@
     </row>
     <row r="14" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>37</v>
@@ -12720,19 +12876,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>37</v>
@@ -12750,19 +12906,19 @@
     </row>
     <row r="16" spans="1:18" ht="66" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>37</v>
@@ -12839,8 +12995,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{C72A0513-06E4-4619-B425-BE563C6CEAED}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{BECD9D40-91D0-41BA-83C9-EFC5C8F5373B}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5A02A180-E651-4BC0-8C1E-AF0E33F4DE97}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DE323199-8DF8-44D6-A42D-5B384CD849C7}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12856,11 +13012,11 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DDA32C-7DB1-413F-8D85-1048754B6713}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9618037-23D5-4536-863E-242F3F45084B}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R79"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -12890,7 +13046,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -12916,7 +13072,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -12943,7 +13099,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -13002,7 +13158,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -13156,7 +13312,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -13176,19 +13332,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -13210,19 +13366,19 @@
     </row>
     <row r="13" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -13246,19 +13402,19 @@
     </row>
     <row r="14" spans="1:18" ht="66" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -13282,19 +13438,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="38" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>38</v>
@@ -13318,19 +13474,19 @@
     </row>
     <row r="16" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -13354,19 +13510,19 @@
     </row>
     <row r="17" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A17" s="38" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>38</v>
@@ -13390,19 +13546,19 @@
     </row>
     <row r="18" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>38</v>
@@ -13426,19 +13582,19 @@
     </row>
     <row r="19" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A19" s="38" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>38</v>
@@ -13462,19 +13618,19 @@
     </row>
     <row r="20" spans="1:18" ht="26.4">
       <c r="A20" s="38" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>37</v>
@@ -13494,19 +13650,19 @@
     </row>
     <row r="21" spans="1:18" ht="39.6">
       <c r="A21" s="38" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>38</v>
@@ -13530,19 +13686,19 @@
     </row>
     <row r="22" spans="1:18" ht="26.4">
       <c r="A22" s="38" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>37</v>
@@ -13562,19 +13718,19 @@
     </row>
     <row r="23" spans="1:18" ht="52.8">
       <c r="A23" s="38" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>38</v>
@@ -13598,19 +13754,19 @@
     </row>
     <row r="24" spans="1:18" ht="39.6">
       <c r="A24" s="38" t="s">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>38</v>
@@ -13634,19 +13790,19 @@
     </row>
     <row r="25" spans="1:18" ht="52.8">
       <c r="A25" s="38" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>38</v>
@@ -13670,19 +13826,19 @@
     </row>
     <row r="26" spans="1:18" ht="52.8">
       <c r="A26" s="38" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>38</v>
@@ -13706,19 +13862,19 @@
     </row>
     <row r="27" spans="1:18" ht="39.6">
       <c r="A27" s="38" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>38</v>
@@ -13742,19 +13898,19 @@
     </row>
     <row r="28" spans="1:18" ht="39.6">
       <c r="A28" s="38" t="s">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>38</v>
@@ -13776,21 +13932,21 @@
       <c r="Q28" s="42"/>
       <c r="R28" s="43"/>
     </row>
-    <row r="29" spans="1:18" ht="39.6">
+    <row r="29" spans="1:18" ht="52.8">
       <c r="A29" s="38" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>536</v>
+        <v>565</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>38</v>
@@ -13812,27 +13968,31 @@
       <c r="Q29" s="42"/>
       <c r="R29" s="43"/>
     </row>
-    <row r="30" spans="1:18" ht="26.4">
+    <row r="30" spans="1:18" ht="52.8">
       <c r="A30" s="38" t="s">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="D30" s="40" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I30" s="38"/>
       <c r="J30" s="38"/>
       <c r="K30" s="38"/>
@@ -13846,19 +14006,19 @@
     </row>
     <row r="31" spans="1:18" ht="39.6">
       <c r="A31" s="38" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>38</v>
@@ -13880,31 +14040,27 @@
       <c r="Q31" s="42"/>
       <c r="R31" s="43"/>
     </row>
-    <row r="32" spans="1:18" ht="52.8">
+    <row r="32" spans="1:18" ht="26.4">
       <c r="A32" s="38" t="s">
-        <v>547</v>
+        <v>576</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>548</v>
+        <v>577</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>549</v>
+        <v>578</v>
       </c>
       <c r="D32" s="40" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
       <c r="I32" s="38"/>
       <c r="J32" s="38"/>
       <c r="K32" s="38"/>
@@ -13918,19 +14074,19 @@
     </row>
     <row r="33" spans="1:18" ht="39.6">
       <c r="A33" s="38" t="s">
-        <v>552</v>
+        <v>579</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>553</v>
+        <v>580</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>554</v>
+        <v>581</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>514</v>
+        <v>582</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>551</v>
+        <v>502</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>38</v>
@@ -13954,19 +14110,19 @@
     </row>
     <row r="34" spans="1:18" ht="52.8">
       <c r="A34" s="38" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>551</v>
+        <v>587</v>
       </c>
       <c r="F34" s="38" t="s">
         <v>38</v>
@@ -13988,27 +14144,31 @@
       <c r="Q34" s="42"/>
       <c r="R34" s="43"/>
     </row>
-    <row r="35" spans="1:18" ht="26.4">
+    <row r="35" spans="1:18" ht="39.6">
       <c r="A35" s="38" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>542</v>
+        <v>590</v>
       </c>
       <c r="D35" s="40" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I35" s="38"/>
       <c r="J35" s="38"/>
       <c r="K35" s="38"/>
@@ -14022,19 +14182,19 @@
     </row>
     <row r="36" spans="1:18" ht="52.8">
       <c r="A36" s="38" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
       <c r="F36" s="38" t="s">
         <v>38</v>
@@ -14056,31 +14216,27 @@
       <c r="Q36" s="42"/>
       <c r="R36" s="43"/>
     </row>
-    <row r="37" spans="1:18" ht="39.6">
+    <row r="37" spans="1:18" ht="26.4">
       <c r="A37" s="38" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>562</v>
+        <v>595</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G37" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H37" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
       <c r="I37" s="38"/>
       <c r="J37" s="38"/>
       <c r="K37" s="38"/>
@@ -14092,21 +14248,21 @@
       <c r="Q37" s="42"/>
       <c r="R37" s="43"/>
     </row>
-    <row r="38" spans="1:18" ht="39.6">
+    <row r="38" spans="1:18" ht="52.8">
       <c r="A38" s="38" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="D38" s="40" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="F38" s="38" t="s">
         <v>38</v>
@@ -14130,19 +14286,19 @@
     </row>
     <row r="39" spans="1:18" ht="39.6">
       <c r="A39" s="38" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>38</v>
@@ -14166,19 +14322,19 @@
     </row>
     <row r="40" spans="1:18" ht="39.6">
       <c r="A40" s="38" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>573</v>
+        <v>604</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>570</v>
+        <v>606</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>571</v>
+        <v>607</v>
       </c>
       <c r="F40" s="38" t="s">
         <v>38</v>
@@ -14202,19 +14358,19 @@
     </row>
     <row r="41" spans="1:18" ht="39.6">
       <c r="A41" s="38" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>578</v>
+        <v>609</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>579</v>
+        <v>610</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>470</v>
+        <v>607</v>
       </c>
       <c r="F41" s="38" t="s">
         <v>38</v>
@@ -14238,19 +14394,19 @@
     </row>
     <row r="42" spans="1:18" ht="39.6">
       <c r="A42" s="38" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>583</v>
+        <v>612</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>470</v>
+        <v>607</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>38</v>
@@ -14274,19 +14430,19 @@
     </row>
     <row r="43" spans="1:18" ht="39.6">
       <c r="A43" s="38" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="C43" s="39" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>589</v>
+        <v>502</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>38</v>
@@ -14310,19 +14466,19 @@
     </row>
     <row r="44" spans="1:18" ht="39.6">
       <c r="A44" s="38" t="s">
-        <v>590</v>
+        <v>617</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>591</v>
+        <v>618</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>592</v>
+        <v>619</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>514</v>
+        <v>620</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>589</v>
+        <v>502</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>38</v>
@@ -14346,19 +14502,19 @@
     </row>
     <row r="45" spans="1:18" ht="39.6">
       <c r="A45" s="38" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="C45" s="39" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>38</v>
@@ -14382,19 +14538,19 @@
     </row>
     <row r="46" spans="1:18" ht="39.6">
       <c r="A46" s="38" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>600</v>
+        <v>628</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F46" s="38" t="s">
         <v>38</v>
@@ -14418,19 +14574,19 @@
     </row>
     <row r="47" spans="1:18" ht="39.6">
       <c r="A47" s="38" t="s">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>602</v>
+        <v>630</v>
       </c>
       <c r="C47" s="39" t="s">
-        <v>603</v>
+        <v>631</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>514</v>
+        <v>632</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>597</v>
+        <v>633</v>
       </c>
       <c r="F47" s="38" t="s">
         <v>38</v>
@@ -14454,19 +14610,19 @@
     </row>
     <row r="48" spans="1:18" ht="39.6">
       <c r="A48" s="38" t="s">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>605</v>
+        <v>635</v>
       </c>
       <c r="C48" s="39" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="D48" s="40" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>597</v>
+        <v>633</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>38</v>
@@ -14488,21 +14644,21 @@
       <c r="Q48" s="42"/>
       <c r="R48" s="43"/>
     </row>
-    <row r="49" spans="1:18" ht="52.8">
+    <row r="49" spans="1:18" ht="39.6">
       <c r="A49" s="38" t="s">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>608</v>
+        <v>638</v>
       </c>
       <c r="C49" s="39" t="s">
-        <v>609</v>
+        <v>639</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>610</v>
+        <v>546</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>470</v>
+        <v>633</v>
       </c>
       <c r="F49" s="38" t="s">
         <v>38</v>
@@ -14524,21 +14680,21 @@
       <c r="Q49" s="42"/>
       <c r="R49" s="43"/>
     </row>
-    <row r="50" spans="1:18" ht="52.8">
+    <row r="50" spans="1:18" ht="39.6">
       <c r="A50" s="38" t="s">
-        <v>611</v>
+        <v>640</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>612</v>
+        <v>641</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>615</v>
+        <v>633</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>38</v>
@@ -14560,21 +14716,21 @@
       <c r="Q50" s="42"/>
       <c r="R50" s="43"/>
     </row>
-    <row r="51" spans="1:18" ht="39.6">
+    <row r="51" spans="1:18" ht="52.8">
       <c r="A51" s="38" t="s">
-        <v>616</v>
+        <v>643</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>617</v>
+        <v>644</v>
       </c>
       <c r="C51" s="39" t="s">
-        <v>618</v>
+        <v>645</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>619</v>
+        <v>502</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>38</v>
@@ -14596,21 +14752,21 @@
       <c r="Q51" s="42"/>
       <c r="R51" s="43"/>
     </row>
-    <row r="52" spans="1:18" ht="39.6">
+    <row r="52" spans="1:18" ht="52.8">
       <c r="A52" s="38" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>622</v>
+        <v>649</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>624</v>
+        <v>651</v>
       </c>
       <c r="F52" s="38" t="s">
         <v>38</v>
@@ -14632,21 +14788,21 @@
       <c r="Q52" s="42"/>
       <c r="R52" s="43"/>
     </row>
-    <row r="53" spans="1:18" ht="52.8">
+    <row r="53" spans="1:18" ht="39.6">
       <c r="A53" s="38" t="s">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>626</v>
+        <v>653</v>
       </c>
       <c r="C53" s="39" t="s">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>615</v>
+        <v>655</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>38</v>
@@ -14670,25 +14826,29 @@
     </row>
     <row r="54" spans="1:18" ht="39.6">
       <c r="A54" s="38" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="B54" s="39" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>623</v>
+        <v>659</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>619</v>
+        <v>660</v>
       </c>
       <c r="F54" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G54" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H54" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I54" s="38"/>
       <c r="J54" s="38"/>
       <c r="K54" s="38"/>
@@ -14702,19 +14862,19 @@
     </row>
     <row r="55" spans="1:18" ht="52.8">
       <c r="A55" s="38" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="B55" s="39" t="s">
-        <v>632</v>
+        <v>662</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>624</v>
+        <v>651</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>38</v>
@@ -14736,31 +14896,27 @@
       <c r="Q55" s="42"/>
       <c r="R55" s="43"/>
     </row>
-    <row r="56" spans="1:18" ht="52.8">
+    <row r="56" spans="1:18" ht="39.6">
       <c r="A56" s="38" t="s">
-        <v>635</v>
+        <v>664</v>
       </c>
       <c r="B56" s="39" t="s">
-        <v>636</v>
+        <v>665</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>637</v>
+        <v>666</v>
       </c>
       <c r="D56" s="40" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G56" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H56" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
       <c r="I56" s="38"/>
       <c r="J56" s="38"/>
       <c r="K56" s="38"/>
@@ -14774,19 +14930,19 @@
     </row>
     <row r="57" spans="1:18" ht="52.8">
       <c r="A57" s="38" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="B57" s="39" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="C57" s="39" t="s">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>38</v>
@@ -14808,21 +14964,21 @@
       <c r="Q57" s="42"/>
       <c r="R57" s="43"/>
     </row>
-    <row r="58" spans="1:18" ht="39.6">
+    <row r="58" spans="1:18" ht="52.8">
       <c r="A58" s="38" t="s">
-        <v>643</v>
+        <v>671</v>
       </c>
       <c r="B58" s="39" t="s">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>638</v>
+        <v>674</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>615</v>
+        <v>660</v>
       </c>
       <c r="F58" s="38" t="s">
         <v>38</v>
@@ -14844,21 +15000,21 @@
       <c r="Q58" s="42"/>
       <c r="R58" s="43"/>
     </row>
-    <row r="59" spans="1:18" ht="39.6">
+    <row r="59" spans="1:18" ht="52.8">
       <c r="A59" s="38" t="s">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="B59" s="39" t="s">
-        <v>647</v>
+        <v>676</v>
       </c>
       <c r="C59" s="39" t="s">
-        <v>648</v>
+        <v>677</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>642</v>
+        <v>678</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>615</v>
+        <v>660</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>38</v>
@@ -14882,25 +15038,29 @@
     </row>
     <row r="60" spans="1:18" ht="39.6">
       <c r="A60" s="38" t="s">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="B60" s="39" t="s">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="C60" s="39" t="s">
+        <v>681</v>
+      </c>
+      <c r="D60" s="40" t="s">
+        <v>674</v>
+      </c>
+      <c r="E60" s="40" t="s">
         <v>651</v>
       </c>
-      <c r="D60" s="40" t="s">
-        <v>642</v>
-      </c>
-      <c r="E60" s="40" t="s">
-        <v>619</v>
-      </c>
       <c r="F60" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G60" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H60" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I60" s="38"/>
       <c r="J60" s="38"/>
       <c r="K60" s="38"/>
@@ -14912,21 +15072,21 @@
       <c r="Q60" s="42"/>
       <c r="R60" s="43"/>
     </row>
-    <row r="61" spans="1:18" ht="52.8">
+    <row r="61" spans="1:18" ht="39.6">
       <c r="A61" s="38" t="s">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="B61" s="39" t="s">
-        <v>653</v>
+        <v>683</v>
       </c>
       <c r="C61" s="39" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>470</v>
+        <v>651</v>
       </c>
       <c r="F61" s="38" t="s">
         <v>38</v>
@@ -14950,29 +15110,25 @@
     </row>
     <row r="62" spans="1:18" ht="39.6">
       <c r="A62" s="38" t="s">
-        <v>656</v>
+        <v>685</v>
       </c>
       <c r="B62" s="39" t="s">
-        <v>657</v>
+        <v>686</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>658</v>
+        <v>687</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F62" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G62" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H62" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
       <c r="I62" s="38"/>
       <c r="J62" s="38"/>
       <c r="K62" s="38"/>
@@ -14984,21 +15140,21 @@
       <c r="Q62" s="42"/>
       <c r="R62" s="43"/>
     </row>
-    <row r="63" spans="1:18" ht="66">
+    <row r="63" spans="1:18" ht="52.8">
       <c r="A63" s="38" t="s">
-        <v>661</v>
+        <v>688</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>662</v>
+        <v>689</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="D63" s="40" t="s">
-        <v>664</v>
+        <v>691</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>38</v>
@@ -15020,21 +15176,21 @@
       <c r="Q63" s="42"/>
       <c r="R63" s="43"/>
     </row>
-    <row r="64" spans="1:18" ht="52.8">
+    <row r="64" spans="1:18" ht="39.6">
       <c r="A64" s="38" t="s">
-        <v>665</v>
+        <v>692</v>
       </c>
       <c r="B64" s="39" t="s">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="C64" s="39" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>507</v>
+        <v>695</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>660</v>
+        <v>696</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>38</v>
@@ -15056,21 +15212,21 @@
       <c r="Q64" s="42"/>
       <c r="R64" s="43"/>
     </row>
-    <row r="65" spans="1:18" ht="39.6">
+    <row r="65" spans="1:18" ht="66">
       <c r="A65" s="38" t="s">
-        <v>668</v>
+        <v>697</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>669</v>
+        <v>698</v>
       </c>
       <c r="C65" s="39" t="s">
-        <v>670</v>
+        <v>699</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>671</v>
+        <v>700</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>38</v>
@@ -15094,19 +15250,19 @@
     </row>
     <row r="66" spans="1:18" ht="52.8">
       <c r="A66" s="38" t="s">
-        <v>672</v>
+        <v>701</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>673</v>
+        <v>702</v>
       </c>
       <c r="C66" s="39" t="s">
-        <v>674</v>
+        <v>703</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>675</v>
+        <v>539</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>495</v>
+        <v>696</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>38</v>
@@ -15128,27 +15284,31 @@
       <c r="Q66" s="42"/>
       <c r="R66" s="43"/>
     </row>
-    <row r="67" spans="1:18" ht="26.4">
+    <row r="67" spans="1:18" ht="39.6">
       <c r="A67" s="38" t="s">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="B67" s="39" t="s">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="C67" s="39" t="s">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>479</v>
+        <v>707</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>679</v>
+        <v>502</v>
       </c>
       <c r="F67" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G67" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H67" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
       <c r="K67" s="38"/>
@@ -15160,21 +15320,21 @@
       <c r="Q67" s="42"/>
       <c r="R67" s="43"/>
     </row>
-    <row r="68" spans="1:18" ht="39.6">
+    <row r="68" spans="1:18" ht="52.8">
       <c r="A68" s="38" t="s">
-        <v>680</v>
+        <v>708</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>681</v>
+        <v>709</v>
       </c>
       <c r="C68" s="39" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="D68" s="40" t="s">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>679</v>
+        <v>527</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>38</v>
@@ -15196,31 +15356,27 @@
       <c r="Q68" s="42"/>
       <c r="R68" s="43"/>
     </row>
-    <row r="69" spans="1:18" ht="39.6">
+    <row r="69" spans="1:18" ht="26.4">
       <c r="A69" s="38" t="s">
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>685</v>
+        <v>713</v>
       </c>
       <c r="C69" s="39" t="s">
-        <v>686</v>
+        <v>714</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>687</v>
+        <v>511</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G69" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H69" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
       <c r="I69" s="38"/>
       <c r="J69" s="38"/>
       <c r="K69" s="38"/>
@@ -15232,27 +15388,31 @@
       <c r="Q69" s="42"/>
       <c r="R69" s="43"/>
     </row>
-    <row r="70" spans="1:18" ht="26.4">
+    <row r="70" spans="1:18" ht="39.6">
       <c r="A70" s="38" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="B70" s="39" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="C70" s="39" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="D70" s="40" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="E70" s="40" t="s">
-        <v>679</v>
+        <v>715</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G70" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H70" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I70" s="38"/>
       <c r="J70" s="38"/>
       <c r="K70" s="38"/>
@@ -15266,19 +15426,19 @@
     </row>
     <row r="71" spans="1:18" ht="39.6">
       <c r="A71" s="38" t="s">
-        <v>692</v>
+        <v>720</v>
       </c>
       <c r="B71" s="39" t="s">
-        <v>693</v>
+        <v>721</v>
       </c>
       <c r="C71" s="39" t="s">
-        <v>694</v>
+        <v>722</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>696</v>
+        <v>724</v>
       </c>
       <c r="F71" s="38" t="s">
         <v>38</v>
@@ -15300,31 +15460,27 @@
       <c r="Q71" s="42"/>
       <c r="R71" s="43"/>
     </row>
-    <row r="72" spans="1:18" ht="39.6">
+    <row r="72" spans="1:18" ht="26.4">
       <c r="A72" s="38" t="s">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="B72" s="39" t="s">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="C72" s="39" t="s">
-        <v>699</v>
+        <v>727</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>675</v>
+        <v>723</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G72" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H72" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
       <c r="I72" s="38"/>
       <c r="J72" s="38"/>
       <c r="K72" s="38"/>
@@ -15336,27 +15492,31 @@
       <c r="Q72" s="42"/>
       <c r="R72" s="43"/>
     </row>
-    <row r="73" spans="1:18" ht="26.4">
+    <row r="73" spans="1:18" ht="39.6">
       <c r="A73" s="38" t="s">
-        <v>700</v>
+        <v>728</v>
       </c>
       <c r="B73" s="39" t="s">
-        <v>701</v>
+        <v>729</v>
       </c>
       <c r="C73" s="39" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>695</v>
+        <v>731</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="F73" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G73" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I73" s="38"/>
       <c r="J73" s="38"/>
       <c r="K73" s="38"/>
@@ -15368,27 +15528,31 @@
       <c r="Q73" s="42"/>
       <c r="R73" s="43"/>
     </row>
-    <row r="74" spans="1:18" ht="26.4">
+    <row r="74" spans="1:18" ht="39.6">
       <c r="A74" s="38" t="s">
-        <v>703</v>
+        <v>733</v>
       </c>
       <c r="B74" s="39" t="s">
-        <v>704</v>
+        <v>734</v>
       </c>
       <c r="C74" s="39" t="s">
-        <v>705</v>
+        <v>735</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>679</v>
+        <v>732</v>
       </c>
       <c r="F74" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
+        <v>38</v>
+      </c>
+      <c r="G74" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I74" s="38"/>
       <c r="J74" s="38"/>
       <c r="K74" s="38"/>
@@ -15402,19 +15566,19 @@
     </row>
     <row r="75" spans="1:18" ht="26.4">
       <c r="A75" s="38" t="s">
-        <v>706</v>
+        <v>736</v>
       </c>
       <c r="B75" s="39" t="s">
-        <v>707</v>
+        <v>737</v>
       </c>
       <c r="C75" s="39" t="s">
-        <v>705</v>
+        <v>738</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>695</v>
+        <v>731</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>688</v>
+        <v>527</v>
       </c>
       <c r="F75" s="38" t="s">
         <v>37</v>
@@ -15432,31 +15596,27 @@
       <c r="Q75" s="42"/>
       <c r="R75" s="43"/>
     </row>
-    <row r="76" spans="1:18" ht="52.8">
+    <row r="76" spans="1:18" ht="26.4">
       <c r="A76" s="38" t="s">
-        <v>708</v>
+        <v>739</v>
       </c>
       <c r="B76" s="39" t="s">
-        <v>709</v>
+        <v>740</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>710</v>
+        <v>741</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F76" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G76" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H76" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38"/>
       <c r="I76" s="38"/>
       <c r="J76" s="38"/>
       <c r="K76" s="38"/>
@@ -15468,31 +15628,27 @@
       <c r="Q76" s="42"/>
       <c r="R76" s="43"/>
     </row>
-    <row r="77" spans="1:18" ht="39.6">
+    <row r="77" spans="1:18" ht="26.4">
       <c r="A77" s="38" t="s">
-        <v>713</v>
+        <v>742</v>
       </c>
       <c r="B77" s="39" t="s">
-        <v>714</v>
+        <v>743</v>
       </c>
       <c r="C77" s="39" t="s">
-        <v>715</v>
+        <v>741</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="F77" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G77" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H77" s="38" t="s">
-        <v>67</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
       <c r="I77" s="38"/>
       <c r="J77" s="38"/>
       <c r="K77" s="38"/>
@@ -15504,21 +15660,21 @@
       <c r="Q77" s="42"/>
       <c r="R77" s="43"/>
     </row>
-    <row r="78" spans="1:18" ht="39.6">
+    <row r="78" spans="1:18" ht="52.8">
       <c r="A78" s="38" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="B78" s="39" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="C78" s="39" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>711</v>
+        <v>747</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>720</v>
+        <v>748</v>
       </c>
       <c r="F78" s="38" t="s">
         <v>38</v>
@@ -15540,21 +15696,21 @@
       <c r="Q78" s="42"/>
       <c r="R78" s="43"/>
     </row>
-    <row r="79" spans="1:18" ht="52.8">
+    <row r="79" spans="1:18" ht="39.6">
       <c r="A79" s="38" t="s">
-        <v>721</v>
+        <v>749</v>
       </c>
       <c r="B79" s="39" t="s">
-        <v>722</v>
+        <v>750</v>
       </c>
       <c r="C79" s="39" t="s">
-        <v>723</v>
+        <v>751</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>711</v>
+        <v>747</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>724</v>
+        <v>752</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>38</v>
@@ -15576,6 +15732,78 @@
       <c r="Q79" s="42"/>
       <c r="R79" s="43"/>
     </row>
+    <row r="80" spans="1:18" ht="39.6">
+      <c r="A80" s="38" t="s">
+        <v>753</v>
+      </c>
+      <c r="B80" s="39" t="s">
+        <v>754</v>
+      </c>
+      <c r="C80" s="39" t="s">
+        <v>755</v>
+      </c>
+      <c r="D80" s="40" t="s">
+        <v>747</v>
+      </c>
+      <c r="E80" s="40" t="s">
+        <v>756</v>
+      </c>
+      <c r="F80" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G80" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="I80" s="38"/>
+      <c r="J80" s="38"/>
+      <c r="K80" s="38"/>
+      <c r="L80" s="38"/>
+      <c r="M80" s="38"/>
+      <c r="N80" s="38"/>
+      <c r="O80" s="41"/>
+      <c r="P80" s="43"/>
+      <c r="Q80" s="42"/>
+      <c r="R80" s="43"/>
+    </row>
+    <row r="81" spans="1:18" ht="52.8">
+      <c r="A81" s="38" t="s">
+        <v>757</v>
+      </c>
+      <c r="B81" s="39" t="s">
+        <v>758</v>
+      </c>
+      <c r="C81" s="39" t="s">
+        <v>759</v>
+      </c>
+      <c r="D81" s="40" t="s">
+        <v>747</v>
+      </c>
+      <c r="E81" s="40" t="s">
+        <v>760</v>
+      </c>
+      <c r="F81" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G81" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+      <c r="K81" s="38"/>
+      <c r="L81" s="38"/>
+      <c r="M81" s="38"/>
+      <c r="N81" s="38"/>
+      <c r="O81" s="41"/>
+      <c r="P81" s="43"/>
+      <c r="Q81" s="42"/>
+      <c r="R81" s="43"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
@@ -15583,8 +15811,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2148B239-66D3-4DFA-B18B-EA3103800452}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{6A234ECF-3238-451B-96BD-B56A5E2BBDB8}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2BADCB2A-B15D-4F26-B7FD-3A74D8AC1A78}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F0BBF01D-EC65-45F1-9097-43DBEF791EBF}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15600,7 +15828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0A1AB9E-B3F7-422D-A09A-EDDF15B91871}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB693B2E-8A43-496C-8EC5-5F695A05BC33}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15634,7 +15862,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>725</v>
+        <v>761</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -15660,7 +15888,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>726</v>
+        <v>762</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -15900,7 +16128,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>727</v>
+        <v>763</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -15920,19 +16148,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>728</v>
+        <v>764</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>729</v>
+        <v>765</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>730</v>
+        <v>766</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>731</v>
+        <v>767</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>732</v>
+        <v>768</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>37</v>
@@ -15950,19 +16178,19 @@
     </row>
     <row r="13" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>733</v>
+        <v>769</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>734</v>
+        <v>770</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>735</v>
+        <v>771</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>736</v>
+        <v>772</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>737</v>
+        <v>773</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -15984,19 +16212,19 @@
     </row>
     <row r="14" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>738</v>
+        <v>774</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>739</v>
+        <v>775</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>740</v>
+        <v>776</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>741</v>
+        <v>777</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>742</v>
+        <v>778</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>37</v>
@@ -16014,19 +16242,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>743</v>
+        <v>779</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>744</v>
+        <v>780</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>745</v>
+        <v>781</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>746</v>
+        <v>782</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>747</v>
+        <v>783</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>37</v>
@@ -16044,19 +16272,19 @@
     </row>
     <row r="16" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>748</v>
+        <v>784</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>749</v>
+        <v>785</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>750</v>
+        <v>786</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>736</v>
+        <v>772</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -16078,19 +16306,19 @@
     </row>
     <row r="17" spans="1:17" ht="39.6" outlineLevel="1">
       <c r="A17" s="38" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>753</v>
+        <v>789</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>754</v>
+        <v>790</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>756</v>
+        <v>792</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>37</v>
@@ -16149,8 +16377,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{D434F867-C3D7-476F-8E5E-CEB83E588BAF}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{4088698F-F2FF-456C-A16E-E3BF6E3EAF5E}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0128A1D6-7853-4DFE-9599-E3D5B31E9DD8}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2F20B551-F7DD-4EBD-828F-EBDC61BE220C}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -16236,7 +16464,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="138" t="s">
-        <v>781</v>
+        <v>817</v>
       </c>
       <c r="D5" s="138"/>
       <c r="E5" s="139" t="s">
@@ -16254,7 +16482,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="140" t="s">
-        <v>782</v>
+        <v>818</v>
       </c>
       <c r="D6" s="140"/>
       <c r="E6" s="140"/>
@@ -16354,7 +16582,7 @@
       </c>
       <c r="D12" s="67">
         <f>'F-02'!B6</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="67">
         <f>'F-02'!C6</f>
@@ -16370,7 +16598,7 @@
       </c>
       <c r="H12" s="69">
         <f>'F-02'!B4</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -16379,7 +16607,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D13" s="67">
         <f>'F-03'!B6</f>
@@ -16408,7 +16636,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D14" s="67">
         <f>'F-04'!B6</f>
@@ -16437,11 +16665,11 @@
         <v>5</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D15" s="67">
         <f>'F-05'!B6</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="67">
         <f>'F-05'!C6</f>
@@ -16457,7 +16685,7 @@
       </c>
       <c r="H15" s="69">
         <f>'F-05'!B4</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -16466,11 +16694,11 @@
         <v>6</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D16" s="67">
         <f>'F-06'!B6</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="67">
         <f>'F-06'!C6</f>
@@ -16486,7 +16714,7 @@
       </c>
       <c r="H16" s="69">
         <f>'F-06'!B4</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -16495,7 +16723,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="D17" s="67">
         <f>'F-07'!B6</f>
@@ -16524,11 +16752,11 @@
         <v>8</v>
       </c>
       <c r="C18" s="66" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="D18" s="67">
         <f>'F-08'!B6</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="67">
         <f>'F-08'!C6</f>
@@ -16544,7 +16772,7 @@
       </c>
       <c r="H18" s="69">
         <f>'F-08'!B4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -16553,7 +16781,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="66" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="D19" s="67">
         <f>'F-09'!B6</f>
@@ -16582,7 +16810,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="66" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="D20" s="67">
         <f>'F-10'!B6</f>
@@ -16611,7 +16839,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="66" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="D21" s="67">
         <f>'F-11'!B6</f>
@@ -16640,7 +16868,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="66" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="D22" s="67">
         <f>'F-12'!B6</f>
@@ -16669,11 +16897,11 @@
         <v>13</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="D23" s="67">
         <f>'F-13'!B6</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" s="67">
         <f>'F-13'!C6</f>
@@ -16689,7 +16917,7 @@
       </c>
       <c r="H23" s="69">
         <f>'F-13'!B4</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -16698,7 +16926,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="D24" s="67">
         <f>'F-14'!B6</f>
@@ -16727,7 +16955,7 @@
         <v>15</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="D25" s="67">
         <f>'F-15'!B6</f>
@@ -16756,7 +16984,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="D26" s="67">
         <f>'F-16'!B6</f>
@@ -16785,7 +17013,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="D27" s="67">
         <f>'F-17'!B6</f>
@@ -16814,7 +17042,7 @@
         <v>18</v>
       </c>
       <c r="C28" s="66" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="D28" s="67">
         <f>'F-18'!B6</f>
@@ -16843,7 +17071,7 @@
         <v>19</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="D29" s="67">
         <f>Workflows!B6</f>
@@ -16872,11 +17100,11 @@
         <v>20</v>
       </c>
       <c r="C30" s="66" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="D30" s="67">
         <f>'State transitions'!B6</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E30" s="67">
         <f>'State transitions'!C6</f>
@@ -16892,7 +17120,7 @@
       </c>
       <c r="H30" s="69">
         <f>'State transitions'!B4</f>
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -16901,7 +17129,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>725</v>
+        <v>761</v>
       </c>
       <c r="D31" s="67">
         <f>NFRs!B6</f>
@@ -16942,7 +17170,7 @@
       </c>
       <c r="D33" s="72">
         <f>SUM(D9:D32)</f>
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E33" s="72">
         <f>SUM(E9:E32)</f>
@@ -16958,7 +17186,7 @@
       </c>
       <c r="H33" s="73">
         <f>SUM(H9:H32)</f>
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -16980,7 +17208,7 @@
       <c r="D35" s="57"/>
       <c r="E35" s="78">
         <f>(D33+E33)*100/(H33-G33)</f>
-        <v>87.341772151898738</v>
+        <v>88.095238095238102</v>
       </c>
       <c r="F35" s="57" t="s">
         <v>32</v>
@@ -16997,7 +17225,7 @@
       <c r="D36" s="57"/>
       <c r="E36" s="78">
         <f>D33*100/(H33-G33)</f>
-        <v>87.341772151898738</v>
+        <v>88.095238095238102</v>
       </c>
       <c r="F36" s="57" t="s">
         <v>32</v>
@@ -17030,7 +17258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF3BECC-6591-4F99-912E-1ECC0F22D8B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65046C1-AEDC-4601-ABE6-50D0620A57CB}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17563,8 +17791,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{C54E14F7-D5D9-4533-804D-16DF9CC7D3A2}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{FD07EFD9-7910-4B40-88E1-3A42487BCAD4}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3E5727E3-83F9-461A-BDAB-74EB2500FEC7}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{72274148-639E-4F92-BE1A-F924F8A4B130}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17580,7 +17808,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268B29FB-5749-4753-A0A0-7CAD1855E92C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B1D2F4-559D-4B0C-A9EE-D8B2AA8E4FAE}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17667,7 +17895,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -17726,7 +17954,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -18034,7 +18262,7 @@
       <c r="O15" s="36"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="1:18" ht="66" outlineLevel="1">
+    <row r="16" spans="1:18" ht="92.4" outlineLevel="1">
       <c r="A16" s="38" t="s">
         <v>100</v>
       </c>
@@ -18048,7 +18276,7 @@
         <v>103</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -18068,15 +18296,31 @@
       <c r="O16" s="41"/>
       <c r="Q16" s="42"/>
     </row>
-    <row r="17" spans="1:17" outlineLevel="1">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
+    <row r="17" spans="1:17" ht="66" outlineLevel="1">
+      <c r="A17" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="149" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="149" t="s">
+        <v>67</v>
+      </c>
       <c r="I17" s="38"/>
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
@@ -18129,8 +18373,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2A38DCBA-F40C-4E11-AD24-C081EEF1D5FE}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0BE8EA35-3689-413E-8515-2AC688CA2414}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{77EBECE8-783C-4052-8036-38D189331400}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DD4381F0-31A0-49D5-9C88-F40DBF070903}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18146,7 +18390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FA166E-A8D7-474B-B237-EAF485B1776D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B37E75-7915-4CFC-B5DD-F18E53AAA0F7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18180,7 +18424,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -18206,7 +18450,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -18446,7 +18690,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -18466,16 +18710,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>91</v>
@@ -18500,19 +18744,19 @@
     </row>
     <row r="13" spans="1:18" ht="118.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -18534,19 +18778,19 @@
     </row>
     <row r="14" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D14" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="44" t="s">
         <v>119</v>
-      </c>
-      <c r="E14" s="44" t="s">
-        <v>115</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -18568,19 +18812,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -18602,16 +18846,16 @@
     </row>
     <row r="16" spans="1:18" ht="66" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E16" s="38" t="s">
         <v>91</v>
@@ -18695,8 +18939,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{69488AF4-6EA2-4E4B-8FD2-B9752CA42B8E}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{102D5ABF-7302-4AB2-8E72-363D23A4D724}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A132BA27-C31A-46D7-9B15-A326059E1BBF}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{32798AEB-2AD1-41B0-B5B9-C39966DFC863}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18712,7 +18956,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F40EC4-885D-4AC1-81F3-95808F4D4D15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBEA2CF9-A371-444A-9A0E-622740B07CA1}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18746,7 +18990,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -18772,7 +19016,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -19012,7 +19256,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -19032,16 +19276,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>66</v>
@@ -19066,16 +19310,16 @@
     </row>
     <row r="13" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E13" s="44" t="s">
         <v>66</v>
@@ -19100,16 +19344,16 @@
     </row>
     <row r="14" spans="1:18" ht="118.8" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>66</v>
@@ -19134,16 +19378,16 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E15" s="148" t="s">
         <v>66</v>
@@ -19168,19 +19412,19 @@
     </row>
     <row r="16" spans="1:18" ht="92.4" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -19261,8 +19505,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{12D364AF-0AB6-43BA-B18D-F5CDFC04AA44}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{B23E5F76-CF03-4F0E-9C4C-C34041120E3A}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E725B495-42B3-4434-8212-D4C0F28191CB}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F4078083-7E2A-469B-9E17-4958A8AB5356}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19278,7 +19522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7F7B4A-6301-4AFB-ACDF-F2BE9D45E8FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3ED9A9-CB17-489E-9B52-7B89AEC579B6}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19312,7 +19556,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -19338,7 +19582,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -19365,7 +19609,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -19424,7 +19668,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -19578,7 +19822,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -19598,16 +19842,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>66</v>
@@ -19630,21 +19874,21 @@
       <c r="O12" s="41"/>
       <c r="Q12" s="42"/>
     </row>
-    <row r="13" spans="1:18" ht="105.6" outlineLevel="1">
+    <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -19664,21 +19908,21 @@
       <c r="O13" s="41"/>
       <c r="Q13" s="42"/>
     </row>
-    <row r="14" spans="1:18" ht="92.4" outlineLevel="1">
+    <row r="14" spans="1:18" ht="105.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -19699,14 +19943,30 @@
       <c r="Q14" s="42"/>
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A15" s="82"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
+      <c r="A15" s="146" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="147" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="148" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="148" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="148" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="148" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="148" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="148" t="s">
+        <v>67</v>
+      </c>
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
       <c r="K15" s="35"/>
@@ -19795,8 +20055,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7A86D257-5679-463D-8D4D-44D6251F9136}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{67925E4C-F883-44D5-9062-0E44E39068F4}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{92ACEC7D-C7FE-41B8-BB58-A7D818D62522}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8BFA14D0-3F28-4CD4-82BB-7870641DF960}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19812,7 +20072,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A03B5D-B526-4A84-B542-3E8BE842842E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3AC68-D69B-44B7-ADCE-4B2A4F641540}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19846,7 +20106,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -19872,7 +20132,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -19899,7 +20159,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -19958,7 +20218,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -20112,7 +20372,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -20132,16 +20392,16 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>91</v>
@@ -20164,18 +20424,18 @@
       <c r="O12" s="41"/>
       <c r="Q12" s="42"/>
     </row>
-    <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
+    <row r="13" spans="1:18" ht="118.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E13" s="44" t="s">
         <v>91</v>
@@ -20198,21 +20458,21 @@
       <c r="O13" s="41"/>
       <c r="Q13" s="42"/>
     </row>
-    <row r="14" spans="1:18" ht="66" outlineLevel="1">
+    <row r="14" spans="1:18" ht="132" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -20234,19 +20494,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -20266,21 +20526,21 @@
       <c r="O15" s="36"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="1:18" ht="79.2" outlineLevel="1">
+    <row r="16" spans="1:18" ht="66" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -20300,15 +20560,31 @@
       <c r="O16" s="41"/>
       <c r="Q16" s="42"/>
     </row>
-    <row r="17" spans="1:17" outlineLevel="1">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
+    <row r="17" spans="1:17" ht="79.2" outlineLevel="1">
+      <c r="A17" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="149" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="149" t="s">
+        <v>67</v>
+      </c>
       <c r="I17" s="38"/>
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
@@ -20319,14 +20595,30 @@
       <c r="Q17" s="47"/>
     </row>
     <row r="18" spans="1:17" s="28" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
+      <c r="A18" s="146" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="147" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="148" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="148" t="s">
+        <v>206</v>
+      </c>
+      <c r="E18" s="148" t="s">
+        <v>155</v>
+      </c>
+      <c r="F18" s="148" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="148" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="148" t="s">
+        <v>67</v>
+      </c>
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
       <c r="K18" s="35"/>
@@ -20336,15 +20628,31 @@
       <c r="O18" s="36"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="1:17" outlineLevel="1">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
+    <row r="19" spans="1:17" ht="79.2" outlineLevel="1">
+      <c r="A19" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I19" s="38"/>
       <c r="J19" s="38"/>
       <c r="K19" s="38"/>
@@ -20361,8 +20669,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0DB253B7-AF48-49A9-A29A-9602B42EFE3A}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{1E9021B3-D347-464B-8977-FC10F2739D5F}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{EAD0E251-818D-42AD-B2C8-460C595ABEBB}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{9E1189CA-B09B-4C0D-AC3C-138FAB4D1E06}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
+++ b/docs/reports/out/SWP490_FA26SE260_R2_Report5_TestReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project\CampusStay FPT\docs\reports\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48D0CDBE-A24D-4BBF-ABB7-31C55C989479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06FDF473-21AB-4ACB-A844-5037DA60DF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{189667BC-2595-48C4-9AD1-BDF52ADB2758}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{36F0DF60-ACDB-4740-9668-051E9C10FD2A}">
       <text>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{08C2A745-2D7D-4446-8D90-7912C14FF7DF}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{03CE35DD-4B50-4E10-A632-D344F6CB7862}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{1500F5D2-3D77-4CDA-9CF9-89627F84E6B2}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C1DFB34A-8AFD-4074-A327-D9541772561B}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8B9E9093-3881-4CC5-9CB0-A3BDC372FD8D}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{9331A222-AB0F-451B-915D-9F51661BC6DB}">
       <text>
         <r>
           <rPr>
@@ -250,7 +250,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{7921D5D2-E6D1-4074-8968-BEBBC1102AD0}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{55025306-9A7E-40A1-B07A-D03AD986D15F}">
       <text>
         <r>
           <rPr>
@@ -273,7 +273,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A75DB742-DBBC-4E50-9633-0A9D3F37E152}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{62C397F0-5C7A-40B1-81F4-EF6F27B9C769}">
       <text>
         <r>
           <rPr>
@@ -296,7 +296,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F291DF54-A2B1-4E82-8BF1-9C616847E18A}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C2BDC550-12DB-4505-B259-460D1B956394}">
       <text>
         <r>
           <rPr>
@@ -319,7 +319,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CCD145D2-17EF-40E4-9FD4-B1F331C9C144}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F2AB64BB-DF7B-40AA-AD50-AE8CB281B76A}">
       <text>
         <r>
           <rPr>
@@ -342,7 +342,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{0E82DFEC-1DA9-41D9-8B8F-57919B3CC1C0}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{820D1ED8-FC55-41F9-89C4-16BD06725172}">
       <text>
         <r>
           <rPr>
@@ -365,7 +365,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{19C939B5-9826-4821-AB25-D5D9CF6BC714}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8A97270A-6811-4E8D-AFD9-8A4096252C6F}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8E09E732-F97C-457E-9E11-94C558D58C1B}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C91E08FD-4FC4-495C-AFBE-C27C35D02167}">
       <text>
         <r>
           <rPr>
@@ -411,7 +411,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8A9D1F32-07B0-4328-BE00-88CD772026F0}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{12F7F7C2-2B78-422D-BB7D-1B4602BD71F0}">
       <text>
         <r>
           <rPr>
@@ -434,7 +434,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{D7E4D51B-1402-4754-A140-E63835411E4E}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{5976CDA1-F903-4C4F-AD0E-ADFA0CF70C45}">
       <text>
         <r>
           <rPr>
@@ -457,7 +457,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{75E6E526-792C-46D4-8E8C-DB8E25BA0E1C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{1E6EFFAB-AB11-4C7C-91FC-7976F5B52773}">
       <text>
         <r>
           <rPr>
@@ -480,7 +480,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{3B9A6DE3-0DA1-4E01-8BBE-3E0A538CD086}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C513CDA1-A914-4520-81F3-B674CA087297}">
       <text>
         <r>
           <rPr>
@@ -503,7 +503,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{4AD458CC-DFE5-43EE-97CB-44EF3A375A99}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{77EB6625-6732-4C91-A6AB-77CC67147733}">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{0F67B725-BF3B-4557-9D45-0C3CFE1AB1B9}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{AC0107D1-A48A-4621-AF7E-89BB22FBD5DF}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{2E2F7760-3782-4618-B248-403E6C2D7D3B}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{91A51053-4CBE-453E-9BF6-7BA58DB3F731}">
       <text>
         <r>
           <rPr>
@@ -572,7 +572,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{FD108C75-EC2B-4B20-A8C0-1A0A7537EB8C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{1F1F155A-7B7A-4211-A5F6-B5871BB44371}">
       <text>
         <r>
           <rPr>
@@ -595,7 +595,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CE2E8B1D-BFB9-4299-9309-6B1AF9BAE2D0}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{95A0F7B3-E302-4D30-B4A3-0605CE19158F}">
       <text>
         <r>
           <rPr>
@@ -618,7 +618,7 @@
     <author>tqsang</author>
   </authors>
   <commentList>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{F210A92B-C0A5-4117-9B05-D8A90AAE0F58}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A057B462-0971-4FCF-892A-F8A58FBA280F}">
       <text>
         <r>
           <rPr>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="823">
   <si>
     <t>Project Name</t>
   </si>
@@ -2033,6 +2033,18 @@
   </si>
   <si>
     <t>TC-F18-04</t>
+  </si>
+  <si>
+    <t>[Rule] The Manager's and the Admin's dashboards report the money of Collections and refunds (a paid Deposit without a Bed included) with what is still owed, residents apart from held Beds, the continuing residents the funnel leaves out, the Staff work a Manager decides, and the values of each attention line.</t>
+  </si>
+  <si>
+    <t>Automated (ReportIT.dashboardsAgreeWithFinance): GET /api/dashboards/admin; GET /api/dashboards/manager; GET /api/dashboards/staff; check the answer and the database</t>
+  </si>
+  <si>
+    <t>The Manager's and the Admin's dashboards report the money of Collections and refunds (a paid Deposit without a Bed included) with what is still owed, residents apart from held Beds, the continuing residents the funnel leaves out, the Staff work a Manager decides, and the values of each attention line.</t>
+  </si>
+  <si>
+    <t>TC-F18-05</t>
   </si>
   <si>
     <t>[Exception] The back-office search finds students by code or name, Rooms with or without the dash and request codes inside the user's Blocks; Staff of another Block find neither the Room nor its resident; short queries find nothing and students may not search.</t>
@@ -5274,7 +5286,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A9C8723-1445-435F-A85A-3ECC11C77B7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B74E5E8-8236-4A57-98DF-5FF673085023}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5823,8 +5835,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{4AF124D5-864E-4F77-A925-19C1B2C8BEC9}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{C909F16E-32F0-4404-8D93-2F5B7EC6B05E}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{F3A7E2B1-BB27-4A7C-A8FC-7E3B9B7FF082}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F3E9BFFB-8751-42D8-886C-0BBB954705A5}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5840,7 +5852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5AF1FB3-A191-4918-A704-CE0E9D3595D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D31847B-7C0E-4353-BDF5-687FA7E44887}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6389,8 +6401,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{19EE30C2-368C-4146-8D9A-5B6FD73529DE}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{CB17540F-BE3A-4F87-AD63-3CD18B551798}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{362618B2-B9AE-4EC4-AFF7-A01A2CD0231D}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{6C174298-5FC5-4A3F-AFE4-41EA12A833CC}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6406,7 +6418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E6F362-E093-4986-A8B5-4AF74F234D70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA813C15-28D0-48D3-8F09-FE0496E665CC}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -6923,8 +6935,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3D1CC096-7A45-4BE6-89B0-B3E0A1031AA2}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DAA99E4B-5214-4217-9C25-56CDF6827116}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{465F0AAC-5482-440F-96B5-090EAC0561FF}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{5429CF11-CEDF-491E-B983-C93DA2694956}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6940,7 +6952,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADB2BB8-A69A-4EC7-A71A-C9D8EEDF6AD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B97237E1-E696-4DD6-AE61-10D05ADC47C6}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -7505,8 +7517,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{9FE352B1-A389-4922-96B5-3D6313BCA7C7}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E3829186-7F52-4951-8921-3D8FC0D023AE}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{70BA7428-00E8-4550-9E35-B6406977E792}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{036DDD7E-752F-4BF3-A119-EB307FF99C37}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7522,7 +7534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37707201-657C-410F-8786-A545A885DFD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F98338E9-178E-4872-8CC1-2B1ED37C8CA7}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8087,8 +8099,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A31C3F60-7714-44DF-AB4F-210952FDEA37}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{5959A374-349A-45F4-90BF-F28FF538CBFE}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7BF128B6-6FB8-4333-A9C7-010F9F86C22A}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{4AAA3A43-7E57-4331-BF82-D1D6CC3D7CC0}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8104,7 +8116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E877A6E9-31DF-4D02-BDA8-3DB1099E209A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EFDD1EF-B275-4040-B1A1-94D91A0CCD0B}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -8621,8 +8633,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{785E06C0-0EFA-4384-B195-2C0068779A4F}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{1CA536BF-A70A-4430-B52C-097F7F1D7267}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0DA4CE8C-A4DF-46DE-B58A-C9F03E539B71}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{73124023-E398-43CB-931B-F140379BD67A}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8638,7 +8650,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965E21D4-BAC1-4875-A35A-C54DBC92A502}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670C5615-C00F-4261-BF08-D83D170CBED6}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9219,8 +9231,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3FD8834C-05D2-4F2F-BDCF-DEA719B80912}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{A0076A54-1173-4862-B13B-FCAB82324E01}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B0E096D0-E70D-40C4-BE31-E07B350BCF97}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{B86F8423-6678-4B39-A34E-17A2C4652529}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9236,7 +9248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4287F-1215-4788-972E-E98C413A1AD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548B8DFB-9477-4B7D-90EC-45DECB50C46F}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9769,8 +9781,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{667FC44C-6955-4FF9-9C43-FA7B0E74A47F}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F7B399FA-30F3-463C-8FE1-49CE4CFA40FC}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{636634BE-C484-408F-B14F-DC362925C9D2}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8F0E1EAE-FC0A-44C9-8BBD-12BE9A5A524D}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9786,7 +9798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6406964-E510-427D-85ED-DFBF473204D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D969364-6CBE-4D32-AEDD-F8914BD897DA}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10319,8 +10331,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{07E41508-994D-44D4-B1E5-8F6674A27B94}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{003F4564-CBF7-411C-A9B2-1219082BC898}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{381F0B4F-BBC4-4217-AF3B-ACFBE1119325}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{21FDB746-F8A9-4D5B-A869-718A936B6484}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10336,7 +10348,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECD826F-0849-43A4-859D-225BE2DF98DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9008A6A-26EB-4BC1-858D-70E96BD29C5A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -10869,8 +10881,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{08C20DB5-E34E-4B89-97C6-4D3B5A559F40}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{023BADDE-D0FD-4206-8CD8-A31C0FC1BAAE}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E7BF2ACF-F4BF-4137-A836-615F4150C648}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2F32F65C-727C-45E7-843F-7635EDB0A9F7}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10985,7 +10997,7 @@
         <v>59</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D9" s="97" t="s">
         <v>60</v>
@@ -11003,7 +11015,7 @@
         <v>80</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D10" s="97" t="s">
         <v>81</v>
@@ -11021,7 +11033,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D11" s="97" t="s">
         <v>109</v>
@@ -11039,7 +11051,7 @@
         <v>132</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D12" s="97" t="s">
         <v>133</v>
@@ -11057,7 +11069,7 @@
         <v>156</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D13" s="97" t="s">
         <v>157</v>
@@ -11075,7 +11087,7 @@
         <v>175</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D14" s="97" t="s">
         <v>176</v>
@@ -11093,7 +11105,7 @@
         <v>211</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D15" s="97" t="s">
         <v>212</v>
@@ -11111,7 +11123,7 @@
         <v>234</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D16" s="97" t="s">
         <v>235</v>
@@ -11129,7 +11141,7 @@
         <v>257</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D17" s="97" t="s">
         <v>258</v>
@@ -11147,7 +11159,7 @@
         <v>272</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D18" s="97" t="s">
         <v>273</v>
@@ -11165,7 +11177,7 @@
         <v>299</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D19" s="97" t="s">
         <v>300</v>
@@ -11183,7 +11195,7 @@
         <v>326</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D20" s="97" t="s">
         <v>327</v>
@@ -11201,7 +11213,7 @@
         <v>341</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D21" s="97" t="s">
         <v>342</v>
@@ -11219,7 +11231,7 @@
         <v>372</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="D22" s="97" t="s">
         <v>373</v>
@@ -11236,7 +11248,7 @@
         <v>391</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D23" s="97" t="s">
         <v>392</v>
@@ -11253,7 +11265,7 @@
         <v>410</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="D24" s="97" t="s">
         <v>411</v>
@@ -11270,7 +11282,7 @@
         <v>429</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D25" s="97" t="s">
         <v>430</v>
@@ -11287,7 +11299,7 @@
         <v>448</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D26" s="97" t="s">
         <v>449</v>
@@ -11301,16 +11313,16 @@
         <v>19</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D27" s="97" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -11318,16 +11330,16 @@
         <v>20</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D28" s="97" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -11335,16 +11347,16 @@
         <v>21</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D29" s="97" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -11366,7 +11378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AF5A54-EA16-471B-8DA2-86BB2BC9234C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF85EB28-BEBC-498F-B1D1-3BA0874DAC15}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -11899,8 +11911,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{D7859F83-EF3E-4ED7-8F3B-44BBA6DAC522}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2C823100-0D47-4982-9F27-D5536141AC22}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1E121D7D-963B-4079-B449-B400BEDDBF08}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{01294F64-2A52-4146-913C-216A2FE3EDE4}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -11916,7 +11928,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F702F0A7-65EA-4627-AF1B-1068D706E7D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B25CD193-E05D-482F-8AE2-C92500673F6A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12003,7 +12015,7 @@
       </c>
       <c r="B4" s="144">
         <f>COUNTA(A12:A1000)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
@@ -12062,7 +12074,7 @@
       </c>
       <c r="B6" s="88">
         <f>COUNTIF($F10:$F998,B5)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="88">
         <f t="shared" ref="C6:E6" si="0">COUNTIF($F10:$F998,C5)</f>
@@ -12350,7 +12362,7 @@
         <v>466</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>38</v>
@@ -12370,15 +12382,31 @@
       <c r="O15" s="36"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="1:18" outlineLevel="1">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
+    <row r="16" spans="1:18" ht="92.4" outlineLevel="1">
+      <c r="A16" s="38" t="s">
+        <v>467</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>468</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>469</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>470</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>67</v>
+      </c>
       <c r="I16" s="38"/>
       <c r="J16" s="38"/>
       <c r="K16" s="38"/>
@@ -12449,8 +12477,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{8BE3E15A-0146-44B2-9E75-41CCD5AD3C53}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{54667F08-803D-40C9-A144-4707B28C5F18}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{B942C591-995F-4C05-B4C3-69AD8D8875B2}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{0E1AD987-E63A-4952-807A-0A7EB9BDEF2C}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12466,7 +12494,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0C1982-93FC-420E-AD21-9DA398C1E014}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D10582-B21C-49BC-B32C-A93F55A07614}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12500,7 +12528,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -12526,7 +12554,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -12766,7 +12794,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -12786,19 +12814,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>37</v>
@@ -12816,19 +12844,19 @@
     </row>
     <row r="13" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>37</v>
@@ -12846,19 +12874,19 @@
     </row>
     <row r="14" spans="1:18" ht="79.2" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>37</v>
@@ -12876,19 +12904,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>37</v>
@@ -12906,19 +12934,19 @@
     </row>
     <row r="16" spans="1:18" ht="66" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>37</v>
@@ -12995,8 +13023,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{5A02A180-E651-4BC0-8C1E-AF0E33F4DE97}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DE323199-8DF8-44D6-A42D-5B384CD849C7}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{71421476-7A35-4F19-8F2D-69B45E8E72F6}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{6FBE7371-C1C1-4F2C-827D-D3B55332EA50}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -13012,7 +13040,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9618037-23D5-4536-863E-242F3F45084B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EE1647-EBF9-46CD-958C-F31FC7C6A4B8}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -13046,7 +13074,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -13072,7 +13100,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -13312,7 +13340,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -13332,19 +13360,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>38</v>
@@ -13366,19 +13394,19 @@
     </row>
     <row r="13" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -13402,19 +13430,19 @@
     </row>
     <row r="14" spans="1:18" ht="66" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>38</v>
@@ -13438,19 +13466,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="38" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>519</v>
+      </c>
+      <c r="D15" s="40" t="s">
         <v>515</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="E15" s="40" t="s">
         <v>511</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>507</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>38</v>
@@ -13474,19 +13502,19 @@
     </row>
     <row r="16" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -13510,19 +13538,19 @@
     </row>
     <row r="17" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A17" s="38" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>38</v>
@@ -13546,19 +13574,19 @@
     </row>
     <row r="18" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>38</v>
@@ -13582,19 +13610,19 @@
     </row>
     <row r="19" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A19" s="38" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D19" s="40" t="s">
+        <v>535</v>
+      </c>
+      <c r="E19" s="40" t="s">
         <v>531</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>527</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>38</v>
@@ -13618,19 +13646,19 @@
     </row>
     <row r="20" spans="1:18" ht="26.4">
       <c r="A20" s="38" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>37</v>
@@ -13650,19 +13678,19 @@
     </row>
     <row r="21" spans="1:18" ht="39.6">
       <c r="A21" s="38" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D21" s="40" t="s">
+        <v>543</v>
+      </c>
+      <c r="E21" s="40" t="s">
         <v>539</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>535</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>38</v>
@@ -13686,19 +13714,19 @@
     </row>
     <row r="22" spans="1:18" ht="26.4">
       <c r="A22" s="38" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>37</v>
@@ -13718,19 +13746,19 @@
     </row>
     <row r="23" spans="1:18" ht="52.8">
       <c r="A23" s="38" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>38</v>
@@ -13754,19 +13782,19 @@
     </row>
     <row r="24" spans="1:18" ht="39.6">
       <c r="A24" s="38" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>38</v>
@@ -13790,19 +13818,19 @@
     </row>
     <row r="25" spans="1:18" ht="52.8">
       <c r="A25" s="38" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>38</v>
@@ -13826,19 +13854,19 @@
     </row>
     <row r="26" spans="1:18" ht="52.8">
       <c r="A26" s="38" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D26" s="40" t="s">
+        <v>563</v>
+      </c>
+      <c r="E26" s="40" t="s">
         <v>559</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>555</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>38</v>
@@ -13862,19 +13890,19 @@
     </row>
     <row r="27" spans="1:18" ht="39.6">
       <c r="A27" s="38" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>38</v>
@@ -13898,19 +13926,19 @@
     </row>
     <row r="28" spans="1:18" ht="39.6">
       <c r="A28" s="38" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>38</v>
@@ -13934,19 +13962,19 @@
     </row>
     <row r="29" spans="1:18" ht="52.8">
       <c r="A29" s="38" t="s">
+        <v>571</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>569</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>572</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>550</v>
+      </c>
+      <c r="E29" s="40" t="s">
         <v>567</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>565</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>568</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>546</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>563</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>38</v>
@@ -13970,19 +13998,19 @@
     </row>
     <row r="30" spans="1:18" ht="52.8">
       <c r="A30" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="B30" s="39" t="s">
         <v>569</v>
       </c>
-      <c r="B30" s="39" t="s">
-        <v>565</v>
-      </c>
       <c r="C30" s="39" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D30" s="40" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>38</v>
@@ -14006,19 +14034,19 @@
     </row>
     <row r="31" spans="1:18" ht="39.6">
       <c r="A31" s="38" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>38</v>
@@ -14042,19 +14070,19 @@
     </row>
     <row r="32" spans="1:18" ht="26.4">
       <c r="A32" s="38" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D32" s="40" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>37</v>
@@ -14074,19 +14102,19 @@
     </row>
     <row r="33" spans="1:18" ht="39.6">
       <c r="A33" s="38" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>38</v>
@@ -14110,19 +14138,19 @@
     </row>
     <row r="34" spans="1:18" ht="52.8">
       <c r="A34" s="38" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F34" s="38" t="s">
         <v>38</v>
@@ -14146,19 +14174,19 @@
     </row>
     <row r="35" spans="1:18" ht="39.6">
       <c r="A35" s="38" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D35" s="40" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F35" s="38" t="s">
         <v>38</v>
@@ -14182,19 +14210,19 @@
     </row>
     <row r="36" spans="1:18" ht="52.8">
       <c r="A36" s="38" t="s">
+        <v>595</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>596</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>597</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>550</v>
+      </c>
+      <c r="E36" s="40" t="s">
         <v>591</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>592</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>593</v>
-      </c>
-      <c r="D36" s="40" t="s">
-        <v>546</v>
-      </c>
-      <c r="E36" s="40" t="s">
-        <v>587</v>
       </c>
       <c r="F36" s="38" t="s">
         <v>38</v>
@@ -14218,19 +14246,19 @@
     </row>
     <row r="37" spans="1:18" ht="26.4">
       <c r="A37" s="38" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F37" s="38" t="s">
         <v>37</v>
@@ -14250,19 +14278,19 @@
     </row>
     <row r="38" spans="1:18" ht="52.8">
       <c r="A38" s="38" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D38" s="40" t="s">
+        <v>604</v>
+      </c>
+      <c r="E38" s="40" t="s">
         <v>600</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>596</v>
       </c>
       <c r="F38" s="38" t="s">
         <v>38</v>
@@ -14286,19 +14314,19 @@
     </row>
     <row r="39" spans="1:18" ht="39.6">
       <c r="A39" s="38" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D39" s="40" t="s">
+        <v>604</v>
+      </c>
+      <c r="E39" s="40" t="s">
         <v>600</v>
-      </c>
-      <c r="E39" s="40" t="s">
-        <v>596</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>38</v>
@@ -14322,19 +14350,19 @@
     </row>
     <row r="40" spans="1:18" ht="39.6">
       <c r="A40" s="38" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F40" s="38" t="s">
         <v>38</v>
@@ -14358,19 +14386,19 @@
     </row>
     <row r="41" spans="1:18" ht="39.6">
       <c r="A41" s="38" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C41" s="39" t="s">
+        <v>614</v>
+      </c>
+      <c r="D41" s="40" t="s">
         <v>610</v>
       </c>
-      <c r="D41" s="40" t="s">
-        <v>606</v>
-      </c>
       <c r="E41" s="40" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F41" s="38" t="s">
         <v>38</v>
@@ -14394,19 +14422,19 @@
     </row>
     <row r="42" spans="1:18" ht="39.6">
       <c r="A42" s="38" t="s">
+        <v>615</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>613</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>616</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>610</v>
+      </c>
+      <c r="E42" s="40" t="s">
         <v>611</v>
-      </c>
-      <c r="B42" s="39" t="s">
-        <v>609</v>
-      </c>
-      <c r="C42" s="39" t="s">
-        <v>612</v>
-      </c>
-      <c r="D42" s="40" t="s">
-        <v>606</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>607</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>38</v>
@@ -14430,19 +14458,19 @@
     </row>
     <row r="43" spans="1:18" ht="39.6">
       <c r="A43" s="38" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C43" s="39" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>38</v>
@@ -14466,19 +14494,19 @@
     </row>
     <row r="44" spans="1:18" ht="39.6">
       <c r="A44" s="38" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>38</v>
@@ -14502,19 +14530,19 @@
     </row>
     <row r="45" spans="1:18" ht="39.6">
       <c r="A45" s="38" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C45" s="39" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>38</v>
@@ -14538,19 +14566,19 @@
     </row>
     <row r="46" spans="1:18" ht="39.6">
       <c r="A46" s="38" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F46" s="38" t="s">
         <v>38</v>
@@ -14574,19 +14602,19 @@
     </row>
     <row r="47" spans="1:18" ht="39.6">
       <c r="A47" s="38" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C47" s="39" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="F47" s="38" t="s">
         <v>38</v>
@@ -14610,19 +14638,19 @@
     </row>
     <row r="48" spans="1:18" ht="39.6">
       <c r="A48" s="38" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C48" s="39" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D48" s="40" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>38</v>
@@ -14646,19 +14674,19 @@
     </row>
     <row r="49" spans="1:18" ht="39.6">
       <c r="A49" s="38" t="s">
+        <v>641</v>
+      </c>
+      <c r="B49" s="39" t="s">
+        <v>642</v>
+      </c>
+      <c r="C49" s="39" t="s">
+        <v>643</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>550</v>
+      </c>
+      <c r="E49" s="40" t="s">
         <v>637</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>638</v>
-      </c>
-      <c r="C49" s="39" t="s">
-        <v>639</v>
-      </c>
-      <c r="D49" s="40" t="s">
-        <v>546</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>633</v>
       </c>
       <c r="F49" s="38" t="s">
         <v>38</v>
@@ -14682,19 +14710,19 @@
     </row>
     <row r="50" spans="1:18" ht="39.6">
       <c r="A50" s="38" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>38</v>
@@ -14718,19 +14746,19 @@
     </row>
     <row r="51" spans="1:18" ht="52.8">
       <c r="A51" s="38" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C51" s="39" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>38</v>
@@ -14754,19 +14782,19 @@
     </row>
     <row r="52" spans="1:18" ht="52.8">
       <c r="A52" s="38" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="F52" s="38" t="s">
         <v>38</v>
@@ -14790,19 +14818,19 @@
     </row>
     <row r="53" spans="1:18" ht="39.6">
       <c r="A53" s="38" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C53" s="39" t="s">
+        <v>658</v>
+      </c>
+      <c r="D53" s="40" t="s">
         <v>654</v>
       </c>
-      <c r="D53" s="40" t="s">
-        <v>650</v>
-      </c>
       <c r="E53" s="40" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>38</v>
@@ -14826,19 +14854,19 @@
     </row>
     <row r="54" spans="1:18" ht="39.6">
       <c r="A54" s="38" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B54" s="39" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="F54" s="38" t="s">
         <v>38</v>
@@ -14862,19 +14890,19 @@
     </row>
     <row r="55" spans="1:18" ht="52.8">
       <c r="A55" s="38" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B55" s="39" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C55" s="39" t="s">
+        <v>667</v>
+      </c>
+      <c r="D55" s="40" t="s">
         <v>663</v>
       </c>
-      <c r="D55" s="40" t="s">
-        <v>659</v>
-      </c>
       <c r="E55" s="40" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>38</v>
@@ -14898,19 +14926,19 @@
     </row>
     <row r="56" spans="1:18" ht="39.6">
       <c r="A56" s="38" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B56" s="39" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D56" s="40" t="s">
+        <v>663</v>
+      </c>
+      <c r="E56" s="40" t="s">
         <v>659</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>655</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>37</v>
@@ -14930,19 +14958,19 @@
     </row>
     <row r="57" spans="1:18" ht="52.8">
       <c r="A57" s="38" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B57" s="39" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C57" s="39" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>38</v>
@@ -14966,19 +14994,19 @@
     </row>
     <row r="58" spans="1:18" ht="52.8">
       <c r="A58" s="38" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B58" s="39" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="F58" s="38" t="s">
         <v>38</v>
@@ -15002,19 +15030,19 @@
     </row>
     <row r="59" spans="1:18" ht="52.8">
       <c r="A59" s="38" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B59" s="39" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C59" s="39" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>38</v>
@@ -15038,19 +15066,19 @@
     </row>
     <row r="60" spans="1:18" ht="39.6">
       <c r="A60" s="38" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B60" s="39" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C60" s="39" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="F60" s="38" t="s">
         <v>38</v>
@@ -15074,19 +15102,19 @@
     </row>
     <row r="61" spans="1:18" ht="39.6">
       <c r="A61" s="38" t="s">
+        <v>686</v>
+      </c>
+      <c r="B61" s="39" t="s">
+        <v>687</v>
+      </c>
+      <c r="C61" s="39" t="s">
+        <v>688</v>
+      </c>
+      <c r="D61" s="40" t="s">
         <v>682</v>
       </c>
-      <c r="B61" s="39" t="s">
-        <v>683</v>
-      </c>
-      <c r="C61" s="39" t="s">
-        <v>684</v>
-      </c>
-      <c r="D61" s="40" t="s">
-        <v>678</v>
-      </c>
       <c r="E61" s="40" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="F61" s="38" t="s">
         <v>38</v>
@@ -15110,19 +15138,19 @@
     </row>
     <row r="62" spans="1:18" ht="39.6">
       <c r="A62" s="38" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B62" s="39" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="F62" s="38" t="s">
         <v>37</v>
@@ -15142,19 +15170,19 @@
     </row>
     <row r="63" spans="1:18" ht="52.8">
       <c r="A63" s="38" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D63" s="40" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>38</v>
@@ -15178,19 +15206,19 @@
     </row>
     <row r="64" spans="1:18" ht="39.6">
       <c r="A64" s="38" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B64" s="39" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C64" s="39" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>38</v>
@@ -15214,19 +15242,19 @@
     </row>
     <row r="65" spans="1:18" ht="66">
       <c r="A65" s="38" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C65" s="39" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>38</v>
@@ -15250,19 +15278,19 @@
     </row>
     <row r="66" spans="1:18" ht="52.8">
       <c r="A66" s="38" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C66" s="39" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>38</v>
@@ -15286,19 +15314,19 @@
     </row>
     <row r="67" spans="1:18" ht="39.6">
       <c r="A67" s="38" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B67" s="39" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C67" s="39" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>38</v>
@@ -15322,19 +15350,19 @@
     </row>
     <row r="68" spans="1:18" ht="52.8">
       <c r="A68" s="38" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C68" s="39" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D68" s="40" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>38</v>
@@ -15358,19 +15386,19 @@
     </row>
     <row r="69" spans="1:18" ht="26.4">
       <c r="A69" s="38" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C69" s="39" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="F69" s="38" t="s">
         <v>37</v>
@@ -15390,19 +15418,19 @@
     </row>
     <row r="70" spans="1:18" ht="39.6">
       <c r="A70" s="38" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B70" s="39" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C70" s="39" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D70" s="40" t="s">
+        <v>723</v>
+      </c>
+      <c r="E70" s="40" t="s">
         <v>719</v>
-      </c>
-      <c r="E70" s="40" t="s">
-        <v>715</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>38</v>
@@ -15426,19 +15454,19 @@
     </row>
     <row r="71" spans="1:18" ht="39.6">
       <c r="A71" s="38" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B71" s="39" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C71" s="39" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F71" s="38" t="s">
         <v>38</v>
@@ -15462,19 +15490,19 @@
     </row>
     <row r="72" spans="1:18" ht="26.4">
       <c r="A72" s="38" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B72" s="39" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C72" s="39" t="s">
+        <v>731</v>
+      </c>
+      <c r="D72" s="40" t="s">
         <v>727</v>
       </c>
-      <c r="D72" s="40" t="s">
-        <v>723</v>
-      </c>
       <c r="E72" s="40" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>37</v>
@@ -15494,19 +15522,19 @@
     </row>
     <row r="73" spans="1:18" ht="39.6">
       <c r="A73" s="38" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B73" s="39" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C73" s="39" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="F73" s="38" t="s">
         <v>38</v>
@@ -15530,19 +15558,19 @@
     </row>
     <row r="74" spans="1:18" ht="39.6">
       <c r="A74" s="38" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B74" s="39" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C74" s="39" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="F74" s="38" t="s">
         <v>38</v>
@@ -15566,19 +15594,19 @@
     </row>
     <row r="75" spans="1:18" ht="26.4">
       <c r="A75" s="38" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B75" s="39" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C75" s="39" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F75" s="38" t="s">
         <v>37</v>
@@ -15598,19 +15626,19 @@
     </row>
     <row r="76" spans="1:18" ht="26.4">
       <c r="A76" s="38" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B76" s="39" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="F76" s="38" t="s">
         <v>37</v>
@@ -15630,19 +15658,19 @@
     </row>
     <row r="77" spans="1:18" ht="26.4">
       <c r="A77" s="38" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B77" s="39" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C77" s="39" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F77" s="38" t="s">
         <v>37</v>
@@ -15662,19 +15690,19 @@
     </row>
     <row r="78" spans="1:18" ht="52.8">
       <c r="A78" s="38" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B78" s="39" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C78" s="39" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="F78" s="38" t="s">
         <v>38</v>
@@ -15698,19 +15726,19 @@
     </row>
     <row r="79" spans="1:18" ht="39.6">
       <c r="A79" s="38" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B79" s="39" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C79" s="39" t="s">
+        <v>755</v>
+      </c>
+      <c r="D79" s="40" t="s">
         <v>751</v>
       </c>
-      <c r="D79" s="40" t="s">
-        <v>747</v>
-      </c>
       <c r="E79" s="40" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>38</v>
@@ -15734,19 +15762,19 @@
     </row>
     <row r="80" spans="1:18" ht="39.6">
       <c r="A80" s="38" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B80" s="39" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="F80" s="38" t="s">
         <v>38</v>
@@ -15770,19 +15798,19 @@
     </row>
     <row r="81" spans="1:18" ht="52.8">
       <c r="A81" s="38" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B81" s="39" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C81" s="39" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="F81" s="38" t="s">
         <v>38</v>
@@ -15811,8 +15839,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2BADCB2A-B15D-4F26-B7FD-3A74D8AC1A78}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F0BBF01D-EC65-45F1-9097-43DBEF791EBF}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{60647E9A-D56C-488E-9575-AF8B3BBF91B4}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{76C85621-3883-4960-909B-0AC27E3879F4}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15828,7 +15856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB693B2E-8A43-496C-8EC5-5F695A05BC33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F813F3-23FB-4E6C-93A4-4A0CF1BC95D8}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15862,7 +15890,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="142" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -15888,7 +15916,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="144" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C3" s="144"/>
       <c r="D3" s="144"/>
@@ -16128,7 +16156,7 @@
     </row>
     <row r="11" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="83"/>
@@ -16148,19 +16176,19 @@
     </row>
     <row r="12" spans="1:18" s="43" customFormat="1" ht="121.05" customHeight="1" outlineLevel="1">
       <c r="A12" s="38" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>37</v>
@@ -16178,19 +16206,19 @@
     </row>
     <row r="13" spans="1:18" ht="52.8" outlineLevel="1">
       <c r="A13" s="38" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>38</v>
@@ -16212,19 +16240,19 @@
     </row>
     <row r="14" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A14" s="38" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>37</v>
@@ -16242,19 +16270,19 @@
     </row>
     <row r="15" spans="1:18" s="28" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="146" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B15" s="147" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C15" s="148" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D15" s="148" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="E15" s="148" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="F15" s="148" t="s">
         <v>37</v>
@@ -16272,19 +16300,19 @@
     </row>
     <row r="16" spans="1:18" ht="39.6" outlineLevel="1">
       <c r="A16" s="38" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>38</v>
@@ -16306,19 +16334,19 @@
     </row>
     <row r="17" spans="1:17" ht="39.6" outlineLevel="1">
       <c r="A17" s="38" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>37</v>
@@ -16377,8 +16405,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{0128A1D6-7853-4DFE-9599-E3D5B31E9DD8}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{2F20B551-F7DD-4EBD-828F-EBDC61BE220C}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{85A723E5-4129-48B1-A1C5-796F061C32DF}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{E1E2F25B-6C80-407E-A6E7-7B3634F2D23E}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -16464,7 +16492,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="138" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D5" s="138"/>
       <c r="E5" s="139" t="s">
@@ -16482,7 +16510,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="140" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="D6" s="140"/>
       <c r="E6" s="140"/>
@@ -17046,7 +17074,7 @@
       </c>
       <c r="D28" s="67">
         <f>'F-18'!B6</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="67">
         <f>'F-18'!C6</f>
@@ -17062,7 +17090,7 @@
       </c>
       <c r="H28" s="69">
         <f>'F-18'!B4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -17071,7 +17099,7 @@
         <v>19</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D29" s="67">
         <f>Workflows!B6</f>
@@ -17100,7 +17128,7 @@
         <v>20</v>
       </c>
       <c r="C30" s="66" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D30" s="67">
         <f>'State transitions'!B6</f>
@@ -17129,7 +17157,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D31" s="67">
         <f>NFRs!B6</f>
@@ -17170,7 +17198,7 @@
       </c>
       <c r="D33" s="72">
         <f>SUM(D9:D32)</f>
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E33" s="72">
         <f>SUM(E9:E32)</f>
@@ -17186,7 +17214,7 @@
       </c>
       <c r="H33" s="73">
         <f>SUM(H9:H32)</f>
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -17208,7 +17236,7 @@
       <c r="D35" s="57"/>
       <c r="E35" s="78">
         <f>(D33+E33)*100/(H33-G33)</f>
-        <v>88.095238095238102</v>
+        <v>88.165680473372788</v>
       </c>
       <c r="F35" s="57" t="s">
         <v>32</v>
@@ -17225,7 +17253,7 @@
       <c r="D36" s="57"/>
       <c r="E36" s="78">
         <f>D33*100/(H33-G33)</f>
-        <v>88.095238095238102</v>
+        <v>88.165680473372788</v>
       </c>
       <c r="F36" s="57" t="s">
         <v>32</v>
@@ -17258,7 +17286,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65046C1-AEDC-4601-ABE6-50D0620A57CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE1C8B3-A143-40D5-851B-275D0D0D4C3E}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17791,8 +17819,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{3E5727E3-83F9-461A-BDAB-74EB2500FEC7}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{72274148-639E-4F92-BE1A-F924F8A4B130}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{2CCA3D7E-DF60-4151-B721-3EFCE06A0061}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{B6741C5E-B41D-40B8-B563-30B446E370B3}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17808,7 +17836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B1D2F4-559D-4B0C-A9EE-D8B2AA8E4FAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B74D36B-D08E-4D7E-9898-40BCF62BF451}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18373,8 +18401,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{77EBECE8-783C-4052-8036-38D189331400}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{DD4381F0-31A0-49D5-9C88-F40DBF070903}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{EEAB3EAA-BC1C-4F07-B10A-AEE4B88C6458}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{994D89F4-6888-4620-B9F2-0B2C4BEFFE03}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18390,7 +18418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B37E75-7915-4CFC-B5DD-F18E53AAA0F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15573D2-7FE9-4CBD-9D24-6640E54589B8}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18939,8 +18967,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{A132BA27-C31A-46D7-9B15-A326059E1BBF}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{32798AEB-2AD1-41B0-B5B9-C39966DFC863}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{1459867C-B2C3-4A8B-A738-75EA8F928686}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{65A098D9-752E-48F1-9AB2-2A833DF81378}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18956,7 +18984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBEA2CF9-A371-444A-9A0E-622740B07CA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D576969C-2A29-47A7-A519-7CD2E60C02D8}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19505,8 +19533,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{E725B495-42B3-4434-8212-D4C0F28191CB}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{F4078083-7E2A-469B-9E17-4958A8AB5356}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{83F83DD2-87DB-446E-A6F7-6010EBD6C6D4}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{9EFB1FD1-0961-4A32-987E-9260F50E8BE5}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19522,7 +19550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3ED9A9-CB17-489E-9B52-7B89AEC579B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E7AD45-C722-420E-83DF-DB6978C6D1FF}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -20055,8 +20083,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{92ACEC7D-C7FE-41B8-BB58-A7D818D62522}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{8BFA14D0-3F28-4CD4-82BB-7870641DF960}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{6F570BBF-DE1E-4454-AA5A-A46551AD0B93}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{233AA60F-2955-458A-ABFD-24DDD4D32E2B}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -20072,7 +20100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3AC68-D69B-44B7-ADCE-4B2A4F641540}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2D0D5E-237F-4F8A-919F-CD80CD41D6CD}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -20669,8 +20697,8 @@
     <mergeCell ref="B4:E4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{EAD0E251-818D-42AD-B2C8-460C595ABEBB}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{9E1189CA-B09B-4C0D-AC3C-138FAB4D1E06}">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="F10 I10 L10" xr:uid="{7A038C91-6842-4886-827E-1B0C093FED4B}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G3 G9 G20:G147 I12:I19 J2:J3 J9 J20:J147 F12:F19 M2:M3 M9 M20:M147 L12:L19" xr:uid="{3036A36E-D58D-4E67-8B1D-F5E5D2B6B862}">
       <formula1>$R$2:$R$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
